--- a/data/git/file/git.o.xlsx
+++ b/data/git/file/git.o.xlsx
@@ -5,28 +5,31 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/jryans/Projects/git/debug-info/file/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/jryans/Research/Papers/oopsla-2023/data/git/file/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ADEAD5D0-C865-544F-A92E-7E9C7ABB405D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3E171DE1-08B2-0040-AB2C-6C0ABBED9C9C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="19180" yWindow="500" windowWidth="34400" windowHeight="28280" xr2:uid="{1069CAA2-7C27-E54E-B88A-C9343E41429C}"/>
+    <workbookView xWindow="9040" yWindow="500" windowWidth="34400" windowHeight="28280" activeTab="2" xr2:uid="{1069CAA2-7C27-E54E-B88A-C9343E41429C}"/>
   </bookViews>
   <sheets>
-    <sheet name="Normalised" sheetId="1" r:id="rId1"/>
+    <sheet name="Wide" sheetId="1" r:id="rId1"/>
     <sheet name="Average" sheetId="3" r:id="rId2"/>
-    <sheet name="Flattened" sheetId="2" r:id="rId3"/>
+    <sheet name="Long" sheetId="2" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="git.o" localSheetId="0">Normalised!#REF!</definedName>
-    <definedName name="git.o.O013m2r" localSheetId="2">Flattened!$A$1:$F$105</definedName>
-    <definedName name="git.o.O013m2r" localSheetId="0">Normalised!$A$1:$B$105</definedName>
-    <definedName name="git.o.O112" localSheetId="2">Flattened!$G$1:$G$105</definedName>
-    <definedName name="git.o.O112" localSheetId="0">Normalised!$C$1:$C$105</definedName>
-    <definedName name="git.o.O113" localSheetId="2">Flattened!$H$1:$H$106</definedName>
-    <definedName name="git.o.O113" localSheetId="0">Normalised!$D$1:$D$106</definedName>
-    <definedName name="git.o.O114" localSheetId="2">Flattened!$I$1:$I$106</definedName>
-    <definedName name="git.o.O114" localSheetId="0">Normalised!$E$1:$E$106</definedName>
+    <definedName name="git.o" localSheetId="0">Wide!$B$1:$B$105</definedName>
+    <definedName name="git.o_1" localSheetId="0">Wide!$C$1:$C$105</definedName>
+    <definedName name="git.o_2" localSheetId="0">Wide!$D$1:$D$105</definedName>
+    <definedName name="git.o_3" localSheetId="0">Wide!$E$1:$E$105</definedName>
+    <definedName name="git.o.O013m2r" localSheetId="2">Long!$A$1:$F$105</definedName>
+    <definedName name="git.o.O013m2r" localSheetId="0">Wide!$A$1:$A$105</definedName>
+    <definedName name="git.o.O112" localSheetId="2">Long!$G$1:$G$105</definedName>
+    <definedName name="git.o.O112" localSheetId="0">Wide!#REF!</definedName>
+    <definedName name="git.o.O113" localSheetId="2">Long!$H$1:$H$106</definedName>
+    <definedName name="git.o.O113" localSheetId="0">Wide!#REF!</definedName>
+    <definedName name="git.o.O114" localSheetId="2">Long!$I$1:$I$106</definedName>
+    <definedName name="git.o.O114" localSheetId="0">Wide!#REF!</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -50,7 +53,20 @@
 
 <file path=xl/connections.xml><?xml version="1.0" encoding="utf-8"?>
 <connections xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr16="http://schemas.microsoft.com/office/spreadsheetml/2017/revision16" mc:Ignorable="xr16">
-  <connection id="1" xr16:uid="{61220DF1-630A-8A4E-AB1A-BE99DCE82120}" name="git.o.O013m2r" type="6" refreshedVersion="8" background="1" saveData="1">
+  <connection id="1" xr16:uid="{A6EBA501-C29F-E740-8466-46553FA1D4C6}" name="git.o" type="6" refreshedVersion="8" background="1" saveData="1">
+    <textPr codePage="10000" sourceFile="/Users/jryans/Research/Papers/oopsla-2023/data/git/file/O0-13-plus-mem2reg/git.o.tsv">
+      <textFields count="7">
+        <textField/>
+        <textField/>
+        <textField/>
+        <textField/>
+        <textField/>
+        <textField/>
+        <textField/>
+      </textFields>
+    </textPr>
+  </connection>
+  <connection id="2" xr16:uid="{61220DF1-630A-8A4E-AB1A-BE99DCE82120}" name="git.o.O013m2r" type="6" refreshedVersion="8" background="1" saveData="1">
     <textPr sourceFile="/Users/jryans/Projects/git/debug-info/file/O0-13-plus-mem2reg/git.o.O013m2r.tsv">
       <textFields count="7">
         <textField/>
@@ -63,21 +79,8 @@
       </textFields>
     </textPr>
   </connection>
-  <connection id="2" xr16:uid="{2F589104-8EE2-F047-B7F7-5B685F62B907}" name="git.o.O013m2r1" type="6" refreshedVersion="8" background="1" saveData="1">
+  <connection id="3" xr16:uid="{2F589104-8EE2-F047-B7F7-5B685F62B907}" name="git.o.O013m2r1" type="6" refreshedVersion="8" background="1" saveData="1">
     <textPr sourceFile="/Users/jryans/Projects/git/debug-info/file/O0-13-plus-mem2reg/git.o.O013m2r.tsv">
-      <textFields count="7">
-        <textField/>
-        <textField/>
-        <textField/>
-        <textField/>
-        <textField/>
-        <textField/>
-        <textField/>
-      </textFields>
-    </textPr>
-  </connection>
-  <connection id="3" xr16:uid="{739C4C2A-6CBA-DA4D-8591-4A308C57C6C4}" name="git.o.O112" type="6" refreshedVersion="8" background="1" saveData="1">
-    <textPr sourceFile="/Users/jryans/Projects/git/debug-info/file/O1-12/git.o.O112.tsv">
       <textFields count="7">
         <textField/>
         <textField/>
@@ -102,7 +105,7 @@
       </textFields>
     </textPr>
   </connection>
-  <connection id="5" xr16:uid="{7609A6FF-9B45-0C46-8979-914D8BEA6DC4}" name="git.o.O113" type="6" refreshedVersion="8" background="1" saveData="1">
+  <connection id="5" xr16:uid="{36012E3A-6058-C64C-A595-D81A12B55849}" name="git.o.O1131" type="6" refreshedVersion="8" background="1" saveData="1">
     <textPr sourceFile="/Users/jryans/Projects/git/debug-info/file/O1-13/git.o.O113.tsv">
       <textFields count="7">
         <textField/>
@@ -115,20 +118,7 @@
       </textFields>
     </textPr>
   </connection>
-  <connection id="6" xr16:uid="{36012E3A-6058-C64C-A595-D81A12B55849}" name="git.o.O1131" type="6" refreshedVersion="8" background="1" saveData="1">
-    <textPr sourceFile="/Users/jryans/Projects/git/debug-info/file/O1-13/git.o.O113.tsv">
-      <textFields count="7">
-        <textField/>
-        <textField/>
-        <textField/>
-        <textField/>
-        <textField/>
-        <textField/>
-        <textField/>
-      </textFields>
-    </textPr>
-  </connection>
-  <connection id="7" xr16:uid="{C3039A64-EA20-0841-8BF4-0DEDCA6B886F}" name="git.o.O114" type="6" refreshedVersion="8" background="1" saveData="1">
+  <connection id="6" xr16:uid="{E3C98485-DAAB-A140-BAB8-8A593BAB8486}" name="git.o.O1141" type="6" refreshedVersion="8" background="1" saveData="1">
     <textPr sourceFile="/Users/jryans/Projects/git/debug-info/file/O1-14/git.o.O114.tsv">
       <textFields count="7">
         <textField/>
@@ -141,8 +131,34 @@
       </textFields>
     </textPr>
   </connection>
-  <connection id="8" xr16:uid="{E3C98485-DAAB-A140-BAB8-8A593BAB8486}" name="git.o.O1141" type="6" refreshedVersion="8" background="1" saveData="1">
-    <textPr sourceFile="/Users/jryans/Projects/git/debug-info/file/O1-14/git.o.O114.tsv">
+  <connection id="7" xr16:uid="{B80D23E5-B713-F949-BC9A-454EF720252E}" name="git.o1" type="6" refreshedVersion="8" background="1" saveData="1">
+    <textPr codePage="10000" sourceFile="/Users/jryans/Research/Papers/oopsla-2023/data/git/file/O1-12/git.o.tsv">
+      <textFields count="7">
+        <textField/>
+        <textField/>
+        <textField/>
+        <textField/>
+        <textField/>
+        <textField/>
+        <textField/>
+      </textFields>
+    </textPr>
+  </connection>
+  <connection id="8" xr16:uid="{AAF1E2BC-A19F-0C42-A1BE-CB880467D9A9}" name="git.o2" type="6" refreshedVersion="8" background="1" saveData="1">
+    <textPr codePage="10000" sourceFile="/Users/jryans/Research/Papers/oopsla-2023/data/git/file/O1-13/git.o.tsv">
+      <textFields count="7">
+        <textField/>
+        <textField/>
+        <textField/>
+        <textField/>
+        <textField/>
+        <textField/>
+        <textField/>
+      </textFields>
+    </textPr>
+  </connection>
+  <connection id="9" xr16:uid="{9A563075-C387-EB47-9C75-5216A598DF10}" name="git.o3" type="6" refreshedVersion="8" background="1" saveData="1">
+    <textPr codePage="10000" sourceFile="/Users/jryans/Research/Papers/oopsla-2023/data/git/file/O1-14/git.o.tsv">
       <textFields count="7">
         <textField/>
         <textField/>
@@ -493,16 +509,16 @@
     <t>Average Coverage</t>
   </si>
   <si>
-    <t>CL / SL (O0-13, m2r, LE)</t>
-  </si>
-  <si>
-    <t>CL / SL (O1-12, LE)</t>
-  </si>
-  <si>
-    <t>CL / SL (O1-13, LE)</t>
-  </si>
-  <si>
-    <t>CL / SL (O1-14, LE)</t>
+    <t xml:space="preserve">CL / SL (O0-13, m2r)    </t>
+  </si>
+  <si>
+    <t>CL / SL (O1-12)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CL / SL (O1-13)   </t>
+  </si>
+  <si>
+    <t>CL / SL (O1-14)</t>
   </si>
 </sst>
 </file>
@@ -550,7 +566,17 @@
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="1">
+  <dxfs count="2">
+    <dxf>
+      <font>
+        <color rgb="FF9C5700"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFEB9C"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <font>
         <color rgb="FF9C5700"/>
@@ -575,35 +601,39 @@
 </file>
 
 <file path=xl/queryTables/queryTable1.xml><?xml version="1.0" encoding="utf-8"?>
-<queryTable xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr16="http://schemas.microsoft.com/office/spreadsheetml/2017/revision16" mc:Ignorable="xr16" name="git.o.O112" connectionId="3" xr16:uid="{1127F4D9-039F-4E48-9309-3F78397E0B63}" autoFormatId="16" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="1" applyPatternFormats="1" applyAlignmentFormats="0" applyWidthHeightFormats="0"/>
+<queryTable xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr16="http://schemas.microsoft.com/office/spreadsheetml/2017/revision16" mc:Ignorable="xr16" name="git.o_3" connectionId="9" xr16:uid="{ED71FF77-6ABC-D749-8E21-C2BBC0C49B38}" autoFormatId="16" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="1" applyPatternFormats="1" applyAlignmentFormats="0" applyWidthHeightFormats="0"/>
 </file>
 
 <file path=xl/queryTables/queryTable2.xml><?xml version="1.0" encoding="utf-8"?>
-<queryTable xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr16="http://schemas.microsoft.com/office/spreadsheetml/2017/revision16" mc:Ignorable="xr16" name="git.o.O013m2r" connectionId="1" xr16:uid="{9CCAF8A0-2B7D-0548-BCF8-D231422B6B5F}" autoFormatId="16" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="1" applyPatternFormats="1" applyAlignmentFormats="0" applyWidthHeightFormats="0"/>
+<queryTable xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr16="http://schemas.microsoft.com/office/spreadsheetml/2017/revision16" mc:Ignorable="xr16" name="git.o_2" connectionId="8" xr16:uid="{577EB844-CFFF-874E-B636-A682F7CA9C09}" autoFormatId="16" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="1" applyPatternFormats="1" applyAlignmentFormats="0" applyWidthHeightFormats="0"/>
 </file>
 
 <file path=xl/queryTables/queryTable3.xml><?xml version="1.0" encoding="utf-8"?>
-<queryTable xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr16="http://schemas.microsoft.com/office/spreadsheetml/2017/revision16" mc:Ignorable="xr16" name="git.o.O114" connectionId="7" xr16:uid="{B4F9BF78-2BA6-E440-B745-2702FE44EFE6}" autoFormatId="16" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="1" applyPatternFormats="1" applyAlignmentFormats="0" applyWidthHeightFormats="0"/>
+<queryTable xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr16="http://schemas.microsoft.com/office/spreadsheetml/2017/revision16" mc:Ignorable="xr16" name="git.o_1" connectionId="7" xr16:uid="{3FDFE62B-64A1-F14C-AAB6-88B8E3E9B697}" autoFormatId="16" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="1" applyPatternFormats="1" applyAlignmentFormats="0" applyWidthHeightFormats="0"/>
 </file>
 
 <file path=xl/queryTables/queryTable4.xml><?xml version="1.0" encoding="utf-8"?>
-<queryTable xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr16="http://schemas.microsoft.com/office/spreadsheetml/2017/revision16" mc:Ignorable="xr16" name="git.o.O113" connectionId="5" xr16:uid="{F2CAE738-7C88-A24F-829C-89E872FC9554}" autoFormatId="16" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="1" applyPatternFormats="1" applyAlignmentFormats="0" applyWidthHeightFormats="0"/>
+<queryTable xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr16="http://schemas.microsoft.com/office/spreadsheetml/2017/revision16" mc:Ignorable="xr16" name="git.o" connectionId="1" xr16:uid="{3D81FA4C-8E74-3F41-ADE1-4880DE78A554}" autoFormatId="16" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="1" applyPatternFormats="1" applyAlignmentFormats="0" applyWidthHeightFormats="0"/>
 </file>
 
 <file path=xl/queryTables/queryTable5.xml><?xml version="1.0" encoding="utf-8"?>
-<queryTable xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr16="http://schemas.microsoft.com/office/spreadsheetml/2017/revision16" mc:Ignorable="xr16" name="git.o.O113" connectionId="6" xr16:uid="{7EC8FDAA-8641-7F44-A40C-DFADA06143DC}" autoFormatId="16" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="1" applyPatternFormats="1" applyAlignmentFormats="0" applyWidthHeightFormats="0"/>
+<queryTable xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr16="http://schemas.microsoft.com/office/spreadsheetml/2017/revision16" mc:Ignorable="xr16" name="git.o.O013m2r" connectionId="2" xr16:uid="{9CCAF8A0-2B7D-0548-BCF8-D231422B6B5F}" autoFormatId="16" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="1" applyPatternFormats="1" applyAlignmentFormats="0" applyWidthHeightFormats="0"/>
 </file>
 
 <file path=xl/queryTables/queryTable6.xml><?xml version="1.0" encoding="utf-8"?>
-<queryTable xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr16="http://schemas.microsoft.com/office/spreadsheetml/2017/revision16" mc:Ignorable="xr16" name="git.o.O114" connectionId="8" xr16:uid="{6DA84D36-F075-D643-87AE-9205D8C2E13B}" autoFormatId="16" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="1" applyPatternFormats="1" applyAlignmentFormats="0" applyWidthHeightFormats="0"/>
+<queryTable xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr16="http://schemas.microsoft.com/office/spreadsheetml/2017/revision16" mc:Ignorable="xr16" name="git.o.O013m2r" connectionId="3" xr16:uid="{6BD7D553-8716-684F-A112-947029E7B50E}" autoFormatId="16" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="1" applyPatternFormats="1" applyAlignmentFormats="0" applyWidthHeightFormats="0"/>
 </file>
 
 <file path=xl/queryTables/queryTable7.xml><?xml version="1.0" encoding="utf-8"?>
-<queryTable xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr16="http://schemas.microsoft.com/office/spreadsheetml/2017/revision16" mc:Ignorable="xr16" name="git.o.O013m2r" connectionId="2" xr16:uid="{6BD7D553-8716-684F-A112-947029E7B50E}" autoFormatId="16" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="1" applyPatternFormats="1" applyAlignmentFormats="0" applyWidthHeightFormats="0"/>
+<queryTable xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr16="http://schemas.microsoft.com/office/spreadsheetml/2017/revision16" mc:Ignorable="xr16" name="git.o.O112" connectionId="4" xr16:uid="{5C22DE01-5C44-7C4E-9EAF-E54F03689DF7}" autoFormatId="16" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="1" applyPatternFormats="1" applyAlignmentFormats="0" applyWidthHeightFormats="0"/>
 </file>
 
 <file path=xl/queryTables/queryTable8.xml><?xml version="1.0" encoding="utf-8"?>
-<queryTable xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr16="http://schemas.microsoft.com/office/spreadsheetml/2017/revision16" mc:Ignorable="xr16" name="git.o.O112" connectionId="4" xr16:uid="{5C22DE01-5C44-7C4E-9EAF-E54F03689DF7}" autoFormatId="16" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="1" applyPatternFormats="1" applyAlignmentFormats="0" applyWidthHeightFormats="0"/>
+<queryTable xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr16="http://schemas.microsoft.com/office/spreadsheetml/2017/revision16" mc:Ignorable="xr16" name="git.o.O113" connectionId="5" xr16:uid="{7EC8FDAA-8641-7F44-A40C-DFADA06143DC}" autoFormatId="16" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="1" applyPatternFormats="1" applyAlignmentFormats="0" applyWidthHeightFormats="0"/>
+</file>
+
+<file path=xl/queryTables/queryTable9.xml><?xml version="1.0" encoding="utf-8"?>
+<queryTable xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr16="http://schemas.microsoft.com/office/spreadsheetml/2017/revision16" mc:Ignorable="xr16" name="git.o.O114" connectionId="6" xr16:uid="{6DA84D36-F075-D643-87AE-9205D8C2E13B}" autoFormatId="16" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="1" applyPatternFormats="1" applyAlignmentFormats="0" applyWidthHeightFormats="0"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -907,8 +937,10 @@
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="34.5" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="20.83203125" bestFit="1" customWidth="1"/>
-    <col min="3" max="5" width="16.5" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="20" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="13.5" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="15" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="13.5" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:9" x14ac:dyDescent="0.2">
@@ -974,21 +1006,21 @@
         <v>1</v>
       </c>
       <c r="C3">
-        <v>0.66666999999999998</v>
+        <v>0.69443999999999995</v>
       </c>
       <c r="D3">
-        <v>0.66666999999999998</v>
+        <v>0.69443999999999995</v>
       </c>
       <c r="E3">
         <v>0.66666999999999998</v>
       </c>
       <c r="G3">
         <f t="shared" ref="G3:G66" si="0">C3-B3</f>
-        <v>-0.33333000000000002</v>
+        <v>-0.30556000000000005</v>
       </c>
       <c r="H3">
         <f t="shared" ref="H3:H66" si="1">D3-B3</f>
-        <v>-0.33333000000000002</v>
+        <v>-0.30556000000000005</v>
       </c>
       <c r="I3">
         <f t="shared" ref="I3:I66" si="2">E3-B3</f>
@@ -1003,25 +1035,25 @@
         <v>1</v>
       </c>
       <c r="C4">
-        <v>0.75309000000000004</v>
+        <v>0.80556000000000005</v>
       </c>
       <c r="D4">
-        <v>0.75309000000000004</v>
+        <v>0.80556000000000005</v>
       </c>
       <c r="E4">
-        <v>0.75309000000000004</v>
+        <v>0.80556000000000005</v>
       </c>
       <c r="G4">
         <f t="shared" si="0"/>
-        <v>-0.24690999999999996</v>
+        <v>-0.19443999999999995</v>
       </c>
       <c r="H4">
         <f t="shared" si="1"/>
-        <v>-0.24690999999999996</v>
+        <v>-0.19443999999999995</v>
       </c>
       <c r="I4">
         <f t="shared" si="2"/>
-        <v>-0.24690999999999996</v>
+        <v>-0.19443999999999995</v>
       </c>
     </row>
     <row r="5" spans="1:9" x14ac:dyDescent="0.2">
@@ -1032,25 +1064,25 @@
         <v>1</v>
       </c>
       <c r="C5">
-        <v>0.75309000000000004</v>
+        <v>0.88888999999999996</v>
       </c>
       <c r="D5">
-        <v>0.75309000000000004</v>
+        <v>0.88888999999999996</v>
       </c>
       <c r="E5">
-        <v>0.59258999999999995</v>
+        <v>0.77778000000000003</v>
       </c>
       <c r="G5">
         <f t="shared" si="0"/>
-        <v>-0.24690999999999996</v>
+        <v>-0.11111000000000004</v>
       </c>
       <c r="H5">
         <f t="shared" si="1"/>
-        <v>-0.24690999999999996</v>
+        <v>-0.11111000000000004</v>
       </c>
       <c r="I5">
         <f t="shared" si="2"/>
-        <v>-0.40741000000000005</v>
+        <v>-0.22221999999999997</v>
       </c>
     </row>
     <row r="6" spans="1:9" x14ac:dyDescent="0.2">
@@ -1058,28 +1090,28 @@
         <v>86</v>
       </c>
       <c r="B6">
-        <v>0.90122999999999998</v>
+        <v>0.97619</v>
       </c>
       <c r="C6">
-        <v>0.86419999999999997</v>
+        <v>0.97221999999999997</v>
       </c>
       <c r="D6">
-        <v>0.86419999999999997</v>
+        <v>0.97221999999999997</v>
       </c>
       <c r="E6">
-        <v>0.86419999999999997</v>
+        <v>0.97221999999999997</v>
       </c>
       <c r="G6">
         <f t="shared" si="0"/>
-        <v>-3.7030000000000007E-2</v>
+        <v>-3.9700000000000291E-3</v>
       </c>
       <c r="H6">
         <f t="shared" si="1"/>
-        <v>-3.7030000000000007E-2</v>
+        <v>-3.9700000000000291E-3</v>
       </c>
       <c r="I6">
         <f t="shared" si="2"/>
-        <v>-3.7030000000000007E-2</v>
+        <v>-3.9700000000000291E-3</v>
       </c>
     </row>
     <row r="7" spans="1:9" x14ac:dyDescent="0.2">
@@ -1116,28 +1148,28 @@
         <v>88</v>
       </c>
       <c r="B8">
-        <v>0.92857000000000001</v>
+        <v>0.90908999999999995</v>
       </c>
       <c r="C8">
-        <v>0.90908999999999995</v>
+        <v>0.625</v>
       </c>
       <c r="D8">
-        <v>0.90908999999999995</v>
+        <v>0.625</v>
       </c>
       <c r="E8">
-        <v>0.90908999999999995</v>
+        <v>0.625</v>
       </c>
       <c r="G8">
         <f t="shared" si="0"/>
-        <v>-1.9480000000000053E-2</v>
+        <v>-0.28408999999999995</v>
       </c>
       <c r="H8">
         <f t="shared" si="1"/>
-        <v>-1.9480000000000053E-2</v>
+        <v>-0.28408999999999995</v>
       </c>
       <c r="I8">
         <f t="shared" si="2"/>
-        <v>-1.9480000000000053E-2</v>
+        <v>-0.28408999999999995</v>
       </c>
     </row>
     <row r="9" spans="1:9" x14ac:dyDescent="0.2">
@@ -1261,28 +1293,28 @@
         <v>36</v>
       </c>
       <c r="B13">
-        <v>0.6</v>
+        <v>0.83333000000000002</v>
       </c>
       <c r="C13">
-        <v>0.4</v>
+        <v>0.66666999999999998</v>
       </c>
       <c r="D13">
-        <v>0.4</v>
+        <v>0.66666999999999998</v>
       </c>
       <c r="E13">
-        <v>0.4</v>
+        <v>0.66666999999999998</v>
       </c>
       <c r="G13">
         <f t="shared" si="0"/>
-        <v>-0.19999999999999996</v>
+        <v>-0.16666000000000003</v>
       </c>
       <c r="H13">
         <f t="shared" si="1"/>
-        <v>-0.19999999999999996</v>
+        <v>-0.16666000000000003</v>
       </c>
       <c r="I13">
         <f t="shared" si="2"/>
-        <v>-0.19999999999999996</v>
+        <v>-0.16666000000000003</v>
       </c>
     </row>
     <row r="14" spans="1:9" x14ac:dyDescent="0.2">
@@ -1290,16 +1322,16 @@
         <v>35</v>
       </c>
       <c r="B14">
-        <v>0.7</v>
+        <v>0.83333000000000002</v>
       </c>
       <c r="C14">
-        <v>0.7</v>
+        <v>0.83333000000000002</v>
       </c>
       <c r="D14">
-        <v>0.7</v>
+        <v>0.83333000000000002</v>
       </c>
       <c r="E14">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="G14">
         <f t="shared" si="0"/>
@@ -1311,7 +1343,7 @@
       </c>
       <c r="I14">
         <f t="shared" si="2"/>
-        <v>0.10000000000000009</v>
+        <v>0.16666999999999998</v>
       </c>
     </row>
     <row r="15" spans="1:9" x14ac:dyDescent="0.2">
@@ -1319,7 +1351,7 @@
         <v>5</v>
       </c>
       <c r="B15">
-        <v>0.93181999999999998</v>
+        <v>0.95238</v>
       </c>
       <c r="C15">
         <v>1</v>
@@ -1332,15 +1364,15 @@
       </c>
       <c r="G15">
         <f t="shared" si="0"/>
-        <v>6.8180000000000018E-2</v>
+        <v>4.7619999999999996E-2</v>
       </c>
       <c r="H15">
         <f t="shared" si="1"/>
-        <v>6.8180000000000018E-2</v>
+        <v>4.7619999999999996E-2</v>
       </c>
       <c r="I15">
         <f t="shared" si="2"/>
-        <v>6.8180000000000018E-2</v>
+        <v>4.7619999999999996E-2</v>
       </c>
     </row>
     <row r="16" spans="1:9" x14ac:dyDescent="0.2">
@@ -1377,28 +1409,28 @@
         <v>7</v>
       </c>
       <c r="B17">
-        <v>0.11364</v>
+        <v>0.23810000000000001</v>
       </c>
       <c r="C17">
-        <v>6.8180000000000004E-2</v>
+        <v>0.15789</v>
       </c>
       <c r="D17">
-        <v>6.8180000000000004E-2</v>
+        <v>0.15789</v>
       </c>
       <c r="E17">
-        <v>6.8180000000000004E-2</v>
+        <v>0.15789</v>
       </c>
       <c r="G17">
         <f t="shared" si="0"/>
-        <v>-4.546E-2</v>
+        <v>-8.0210000000000004E-2</v>
       </c>
       <c r="H17">
         <f t="shared" si="1"/>
-        <v>-4.546E-2</v>
+        <v>-8.0210000000000004E-2</v>
       </c>
       <c r="I17">
         <f t="shared" si="2"/>
-        <v>-4.546E-2</v>
+        <v>-8.0210000000000004E-2</v>
       </c>
     </row>
     <row r="18" spans="1:9" x14ac:dyDescent="0.2">
@@ -1406,28 +1438,28 @@
         <v>31</v>
       </c>
       <c r="B18">
-        <v>0.77778000000000003</v>
+        <v>0.875</v>
       </c>
       <c r="C18">
         <v>0</v>
       </c>
       <c r="D18">
-        <v>0.22222</v>
+        <v>0.5</v>
       </c>
       <c r="E18">
-        <v>0.22222</v>
+        <v>0.5</v>
       </c>
       <c r="G18">
         <f t="shared" si="0"/>
-        <v>-0.77778000000000003</v>
+        <v>-0.875</v>
       </c>
       <c r="H18">
         <f t="shared" si="1"/>
-        <v>-0.55556000000000005</v>
+        <v>-0.375</v>
       </c>
       <c r="I18">
         <f t="shared" si="2"/>
-        <v>-0.55556000000000005</v>
+        <v>-0.375</v>
       </c>
     </row>
     <row r="19" spans="1:9" x14ac:dyDescent="0.2">
@@ -1464,28 +1496,28 @@
         <v>30</v>
       </c>
       <c r="B20">
-        <v>0.77778000000000003</v>
+        <v>0.875</v>
       </c>
       <c r="C20">
-        <v>0.88888999999999996</v>
+        <v>1</v>
       </c>
       <c r="D20">
-        <v>0.88888999999999996</v>
+        <v>1</v>
       </c>
       <c r="E20">
-        <v>0.88888999999999996</v>
+        <v>1</v>
       </c>
       <c r="G20">
         <f t="shared" si="0"/>
-        <v>0.11110999999999993</v>
+        <v>0.125</v>
       </c>
       <c r="H20">
         <f t="shared" si="1"/>
-        <v>0.11110999999999993</v>
+        <v>0.125</v>
       </c>
       <c r="I20">
         <f t="shared" si="2"/>
-        <v>0.11110999999999993</v>
+        <v>0.125</v>
       </c>
     </row>
     <row r="21" spans="1:9" x14ac:dyDescent="0.2">
@@ -1580,28 +1612,28 @@
         <v>78</v>
       </c>
       <c r="B24">
-        <v>0.9</v>
+        <v>0.93877999999999995</v>
       </c>
       <c r="C24">
-        <v>0.57499999999999996</v>
+        <v>0.69564999999999999</v>
       </c>
       <c r="D24">
-        <v>0.57499999999999996</v>
+        <v>0.69564999999999999</v>
       </c>
       <c r="E24">
-        <v>0.76249999999999996</v>
+        <v>0.89129999999999998</v>
       </c>
       <c r="G24">
         <f t="shared" si="0"/>
-        <v>-0.32500000000000007</v>
+        <v>-0.24312999999999996</v>
       </c>
       <c r="H24">
         <f t="shared" si="1"/>
-        <v>-0.32500000000000007</v>
+        <v>-0.24312999999999996</v>
       </c>
       <c r="I24">
         <f t="shared" si="2"/>
-        <v>-0.13750000000000007</v>
+        <v>-4.7479999999999967E-2</v>
       </c>
     </row>
     <row r="25" spans="1:9" x14ac:dyDescent="0.2">
@@ -1609,28 +1641,28 @@
         <v>79</v>
       </c>
       <c r="B25">
-        <v>0.88749999999999996</v>
+        <v>0.91837000000000002</v>
       </c>
       <c r="C25">
-        <v>0.45</v>
+        <v>0.30435000000000001</v>
       </c>
       <c r="D25">
-        <v>0.45</v>
+        <v>0.30435000000000001</v>
       </c>
       <c r="E25">
-        <v>0.45</v>
+        <v>0.30435000000000001</v>
       </c>
       <c r="G25">
         <f t="shared" si="0"/>
-        <v>-0.43749999999999994</v>
+        <v>-0.61402000000000001</v>
       </c>
       <c r="H25">
         <f t="shared" si="1"/>
-        <v>-0.43749999999999994</v>
+        <v>-0.61402000000000001</v>
       </c>
       <c r="I25">
         <f t="shared" si="2"/>
-        <v>-0.43749999999999994</v>
+        <v>-0.61402000000000001</v>
       </c>
     </row>
     <row r="26" spans="1:9" x14ac:dyDescent="0.2">
@@ -1638,28 +1670,28 @@
         <v>71</v>
       </c>
       <c r="B26">
-        <v>0.9</v>
+        <v>0.93877999999999995</v>
       </c>
       <c r="C26">
-        <v>1</v>
+        <v>0.80435000000000001</v>
       </c>
       <c r="D26">
-        <v>1</v>
+        <v>0.80435000000000001</v>
       </c>
       <c r="E26">
-        <v>0.9375</v>
+        <v>1</v>
       </c>
       <c r="G26">
         <f t="shared" si="0"/>
-        <v>9.9999999999999978E-2</v>
+        <v>-0.13442999999999994</v>
       </c>
       <c r="H26">
         <f t="shared" si="1"/>
-        <v>9.9999999999999978E-2</v>
+        <v>-0.13442999999999994</v>
       </c>
       <c r="I26">
         <f t="shared" si="2"/>
-        <v>3.7499999999999978E-2</v>
+        <v>6.1220000000000052E-2</v>
       </c>
     </row>
     <row r="27" spans="1:9" x14ac:dyDescent="0.2">
@@ -1670,17 +1702,17 @@
         <v>1</v>
       </c>
       <c r="C27">
-        <v>1</v>
+        <v>0.84782999999999997</v>
       </c>
       <c r="D27">
         <v>1</v>
       </c>
       <c r="E27">
-        <v>0.9375</v>
+        <v>1</v>
       </c>
       <c r="G27">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>-0.15217000000000003</v>
       </c>
       <c r="H27">
         <f t="shared" si="1"/>
@@ -1688,7 +1720,7 @@
       </c>
       <c r="I27">
         <f t="shared" si="2"/>
-        <v>-6.25E-2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="28" spans="1:9" x14ac:dyDescent="0.2">
@@ -1728,25 +1760,25 @@
         <v>1</v>
       </c>
       <c r="C29">
-        <v>0.13750000000000001</v>
+        <v>0.19564999999999999</v>
       </c>
       <c r="D29">
-        <v>0.13750000000000001</v>
+        <v>0.19564999999999999</v>
       </c>
       <c r="E29">
-        <v>0.13750000000000001</v>
+        <v>0.19564999999999999</v>
       </c>
       <c r="G29">
         <f t="shared" si="0"/>
-        <v>-0.86250000000000004</v>
+        <v>-0.80435000000000001</v>
       </c>
       <c r="H29">
         <f t="shared" si="1"/>
-        <v>-0.86250000000000004</v>
+        <v>-0.80435000000000001</v>
       </c>
       <c r="I29">
         <f t="shared" si="2"/>
-        <v>-0.86250000000000004</v>
+        <v>-0.80435000000000001</v>
       </c>
     </row>
     <row r="30" spans="1:9" x14ac:dyDescent="0.2">
@@ -1757,25 +1789,25 @@
         <v>1</v>
       </c>
       <c r="C30">
-        <v>0.5625</v>
+        <v>0.58696000000000004</v>
       </c>
       <c r="D30">
-        <v>0.5625</v>
+        <v>0.58696000000000004</v>
       </c>
       <c r="E30">
-        <v>0.5625</v>
+        <v>0.58696000000000004</v>
       </c>
       <c r="G30">
         <f t="shared" si="0"/>
-        <v>-0.4375</v>
+        <v>-0.41303999999999996</v>
       </c>
       <c r="H30">
         <f t="shared" si="1"/>
-        <v>-0.4375</v>
+        <v>-0.41303999999999996</v>
       </c>
       <c r="I30">
         <f t="shared" si="2"/>
-        <v>-0.4375</v>
+        <v>-0.41303999999999996</v>
       </c>
     </row>
     <row r="31" spans="1:9" x14ac:dyDescent="0.2">
@@ -1786,25 +1818,25 @@
         <v>1</v>
       </c>
       <c r="C31">
-        <v>0.3</v>
+        <v>0.36957000000000001</v>
       </c>
       <c r="D31">
-        <v>0.3</v>
+        <v>0.36957000000000001</v>
       </c>
       <c r="E31">
-        <v>0.3</v>
+        <v>0.36957000000000001</v>
       </c>
       <c r="G31">
         <f t="shared" si="0"/>
-        <v>-0.7</v>
+        <v>-0.63043000000000005</v>
       </c>
       <c r="H31">
         <f t="shared" si="1"/>
-        <v>-0.7</v>
+        <v>-0.63043000000000005</v>
       </c>
       <c r="I31">
         <f t="shared" si="2"/>
-        <v>-0.7</v>
+        <v>-0.63043000000000005</v>
       </c>
     </row>
     <row r="32" spans="1:9" x14ac:dyDescent="0.2">
@@ -1815,25 +1847,25 @@
         <v>1</v>
       </c>
       <c r="C32">
-        <v>0.83333000000000002</v>
+        <v>0.93332999999999999</v>
       </c>
       <c r="D32">
-        <v>0.83333000000000002</v>
+        <v>0.93332999999999999</v>
       </c>
       <c r="E32">
-        <v>0.83333000000000002</v>
+        <v>0.93332999999999999</v>
       </c>
       <c r="G32">
         <f t="shared" si="0"/>
-        <v>-0.16666999999999998</v>
+        <v>-6.6670000000000007E-2</v>
       </c>
       <c r="H32">
         <f t="shared" si="1"/>
-        <v>-0.16666999999999998</v>
+        <v>-6.6670000000000007E-2</v>
       </c>
       <c r="I32">
         <f t="shared" si="2"/>
-        <v>-0.16666999999999998</v>
+        <v>-6.6670000000000007E-2</v>
       </c>
     </row>
     <row r="33" spans="1:9" x14ac:dyDescent="0.2">
@@ -1841,28 +1873,28 @@
         <v>80</v>
       </c>
       <c r="B33">
-        <v>0.33750000000000002</v>
+        <v>0.32652999999999999</v>
       </c>
       <c r="C33">
-        <v>6.25E-2</v>
+        <v>6.522E-2</v>
       </c>
       <c r="D33">
-        <v>6.25E-2</v>
+        <v>6.522E-2</v>
       </c>
       <c r="E33">
-        <v>6.25E-2</v>
+        <v>6.522E-2</v>
       </c>
       <c r="G33">
         <f t="shared" si="0"/>
-        <v>-0.27500000000000002</v>
+        <v>-0.26130999999999999</v>
       </c>
       <c r="H33">
         <f t="shared" si="1"/>
-        <v>-0.27500000000000002</v>
+        <v>-0.26130999999999999</v>
       </c>
       <c r="I33">
         <f t="shared" si="2"/>
-        <v>-0.27500000000000002</v>
+        <v>-0.26130999999999999</v>
       </c>
     </row>
     <row r="34" spans="1:9" x14ac:dyDescent="0.2">
@@ -1870,28 +1902,28 @@
         <v>76</v>
       </c>
       <c r="B34">
-        <v>0.92500000000000004</v>
+        <v>0.97958999999999996</v>
       </c>
       <c r="C34">
-        <v>0.9375</v>
+        <v>0.97826000000000002</v>
       </c>
       <c r="D34">
-        <v>0.9375</v>
+        <v>0.97826000000000002</v>
       </c>
       <c r="E34">
-        <v>0.9375</v>
+        <v>0.97826000000000002</v>
       </c>
       <c r="G34">
         <f t="shared" si="0"/>
-        <v>1.2499999999999956E-2</v>
+        <v>-1.3299999999999423E-3</v>
       </c>
       <c r="H34">
         <f t="shared" si="1"/>
-        <v>1.2499999999999956E-2</v>
+        <v>-1.3299999999999423E-3</v>
       </c>
       <c r="I34">
         <f t="shared" si="2"/>
-        <v>1.2499999999999956E-2</v>
+        <v>-1.3299999999999423E-3</v>
       </c>
     </row>
     <row r="35" spans="1:9" x14ac:dyDescent="0.2">
@@ -1899,28 +1931,28 @@
         <v>77</v>
       </c>
       <c r="B35">
-        <v>0.9</v>
+        <v>0.93877999999999995</v>
       </c>
       <c r="C35">
-        <v>0.9</v>
+        <v>0.80435000000000001</v>
       </c>
       <c r="D35">
-        <v>0.9</v>
+        <v>0.80435000000000001</v>
       </c>
       <c r="E35">
-        <v>0.875</v>
+        <v>0.80435000000000001</v>
       </c>
       <c r="G35">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>-0.13442999999999994</v>
       </c>
       <c r="H35">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>-0.13442999999999994</v>
       </c>
       <c r="I35">
         <f t="shared" si="2"/>
-        <v>-2.5000000000000022E-2</v>
+        <v>-0.13442999999999994</v>
       </c>
     </row>
     <row r="36" spans="1:9" x14ac:dyDescent="0.2">
@@ -1928,28 +1960,28 @@
         <v>15</v>
       </c>
       <c r="B36">
-        <v>0.9</v>
+        <v>0.94443999999999995</v>
       </c>
       <c r="C36">
-        <v>0.86667000000000005</v>
+        <v>0.94118000000000002</v>
       </c>
       <c r="D36">
-        <v>0.86667000000000005</v>
+        <v>0.94118000000000002</v>
       </c>
       <c r="E36">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="G36">
         <f t="shared" si="0"/>
-        <v>-3.3329999999999971E-2</v>
+        <v>-3.2599999999999296E-3</v>
       </c>
       <c r="H36">
         <f t="shared" si="1"/>
-        <v>-3.3329999999999971E-2</v>
+        <v>-3.2599999999999296E-3</v>
       </c>
       <c r="I36">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>5.5560000000000054E-2</v>
       </c>
     </row>
     <row r="37" spans="1:9" x14ac:dyDescent="0.2">
@@ -1986,7 +2018,7 @@
         <v>16</v>
       </c>
       <c r="B38">
-        <v>0.9</v>
+        <v>0.94443999999999995</v>
       </c>
       <c r="C38">
         <v>1</v>
@@ -1999,15 +2031,15 @@
       </c>
       <c r="G38">
         <f t="shared" si="0"/>
-        <v>9.9999999999999978E-2</v>
+        <v>5.5560000000000054E-2</v>
       </c>
       <c r="H38">
         <f t="shared" si="1"/>
-        <v>9.9999999999999978E-2</v>
+        <v>5.5560000000000054E-2</v>
       </c>
       <c r="I38">
         <f t="shared" si="2"/>
-        <v>9.9999999999999978E-2</v>
+        <v>5.5560000000000054E-2</v>
       </c>
     </row>
     <row r="39" spans="1:9" x14ac:dyDescent="0.2">
@@ -2015,28 +2047,28 @@
         <v>19</v>
       </c>
       <c r="B39">
-        <v>0.13333</v>
+        <v>0.22222</v>
       </c>
       <c r="C39">
-        <v>0.1</v>
+        <v>0.17646999999999999</v>
       </c>
       <c r="D39">
-        <v>0.1</v>
+        <v>0.17646999999999999</v>
       </c>
       <c r="E39">
-        <v>0.1</v>
+        <v>0.17646999999999999</v>
       </c>
       <c r="G39">
         <f t="shared" si="0"/>
-        <v>-3.3329999999999999E-2</v>
+        <v>-4.5750000000000013E-2</v>
       </c>
       <c r="H39">
         <f t="shared" si="1"/>
-        <v>-3.3329999999999999E-2</v>
+        <v>-4.5750000000000013E-2</v>
       </c>
       <c r="I39">
         <f t="shared" si="2"/>
-        <v>-3.3329999999999999E-2</v>
+        <v>-4.5750000000000013E-2</v>
       </c>
     </row>
     <row r="40" spans="1:9" x14ac:dyDescent="0.2">
@@ -2044,28 +2076,28 @@
         <v>18</v>
       </c>
       <c r="B40">
-        <v>0.5</v>
+        <v>0.61111000000000004</v>
       </c>
       <c r="C40">
-        <v>0.7</v>
+        <v>0.82352999999999998</v>
       </c>
       <c r="D40">
-        <v>0.7</v>
+        <v>0.82352999999999998</v>
       </c>
       <c r="E40">
-        <v>0.7</v>
+        <v>0.82352999999999998</v>
       </c>
       <c r="G40">
         <f t="shared" si="0"/>
-        <v>0.19999999999999996</v>
+        <v>0.21241999999999994</v>
       </c>
       <c r="H40">
         <f t="shared" si="1"/>
-        <v>0.19999999999999996</v>
+        <v>0.21241999999999994</v>
       </c>
       <c r="I40">
         <f t="shared" si="2"/>
-        <v>0.19999999999999996</v>
+        <v>0.21241999999999994</v>
       </c>
     </row>
     <row r="41" spans="1:9" x14ac:dyDescent="0.2">
@@ -2073,28 +2105,28 @@
         <v>20</v>
       </c>
       <c r="B41">
-        <v>0.63636000000000004</v>
+        <v>0.77778000000000003</v>
       </c>
       <c r="C41">
-        <v>0.36364000000000002</v>
+        <v>0.5</v>
       </c>
       <c r="D41">
-        <v>0.36364000000000002</v>
+        <v>0.5</v>
       </c>
       <c r="E41">
-        <v>0.36364000000000002</v>
+        <v>0.5</v>
       </c>
       <c r="G41">
         <f t="shared" si="0"/>
-        <v>-0.27272000000000002</v>
+        <v>-0.27778000000000003</v>
       </c>
       <c r="H41">
         <f t="shared" si="1"/>
-        <v>-0.27272000000000002</v>
+        <v>-0.27778000000000003</v>
       </c>
       <c r="I41">
         <f t="shared" si="2"/>
-        <v>-0.27272000000000002</v>
+        <v>-0.27778000000000003</v>
       </c>
     </row>
     <row r="42" spans="1:9" x14ac:dyDescent="0.2">
@@ -2102,28 +2134,28 @@
         <v>90</v>
       </c>
       <c r="B42">
-        <v>0.98995</v>
+        <v>0.99414999999999998</v>
       </c>
       <c r="C42">
-        <v>0.98995</v>
+        <v>0.97248000000000001</v>
       </c>
       <c r="D42">
-        <v>0.98995</v>
+        <v>0.97248000000000001</v>
       </c>
       <c r="E42">
-        <v>0.99497000000000002</v>
+        <v>1</v>
       </c>
       <c r="G42">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>-2.1669999999999967E-2</v>
       </c>
       <c r="H42">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>-2.1669999999999967E-2</v>
       </c>
       <c r="I42">
         <f t="shared" si="2"/>
-        <v>5.0200000000000244E-3</v>
+        <v>5.8500000000000218E-3</v>
       </c>
     </row>
     <row r="43" spans="1:9" x14ac:dyDescent="0.2">
@@ -2131,7 +2163,7 @@
         <v>89</v>
       </c>
       <c r="B43">
-        <v>0.98995</v>
+        <v>0.99414999999999998</v>
       </c>
       <c r="C43">
         <v>1</v>
@@ -2144,15 +2176,15 @@
       </c>
       <c r="G43">
         <f t="shared" si="0"/>
-        <v>1.0050000000000003E-2</v>
+        <v>5.8500000000000218E-3</v>
       </c>
       <c r="H43">
         <f t="shared" si="1"/>
-        <v>1.0050000000000003E-2</v>
+        <v>5.8500000000000218E-3</v>
       </c>
       <c r="I43">
         <f t="shared" si="2"/>
-        <v>1.0050000000000003E-2</v>
+        <v>5.8500000000000218E-3</v>
       </c>
     </row>
     <row r="44" spans="1:9" x14ac:dyDescent="0.2">
@@ -2163,25 +2195,25 @@
         <v>1</v>
       </c>
       <c r="C44">
-        <v>0.88083</v>
+        <v>0.91429000000000005</v>
       </c>
       <c r="D44">
-        <v>0.88083</v>
+        <v>0.91429000000000005</v>
       </c>
       <c r="E44">
-        <v>0.88083</v>
+        <v>0.91429000000000005</v>
       </c>
       <c r="G44">
         <f t="shared" si="0"/>
-        <v>-0.11917</v>
+        <v>-8.5709999999999953E-2</v>
       </c>
       <c r="H44">
         <f t="shared" si="1"/>
-        <v>-0.11917</v>
+        <v>-8.5709999999999953E-2</v>
       </c>
       <c r="I44">
         <f t="shared" si="2"/>
-        <v>-0.11917</v>
+        <v>-8.5709999999999953E-2</v>
       </c>
     </row>
     <row r="45" spans="1:9" x14ac:dyDescent="0.2">
@@ -2218,7 +2250,7 @@
         <v>91</v>
       </c>
       <c r="B46">
-        <v>0.98995</v>
+        <v>0.99414999999999998</v>
       </c>
       <c r="C46">
         <v>1</v>
@@ -2231,15 +2263,15 @@
       </c>
       <c r="G46">
         <f t="shared" si="0"/>
-        <v>1.0050000000000003E-2</v>
+        <v>5.8500000000000218E-3</v>
       </c>
       <c r="H46">
         <f t="shared" si="1"/>
-        <v>1.0050000000000003E-2</v>
+        <v>5.8500000000000218E-3</v>
       </c>
       <c r="I46">
         <f t="shared" si="2"/>
-        <v>1.0050000000000003E-2</v>
+        <v>5.8500000000000218E-3</v>
       </c>
     </row>
     <row r="47" spans="1:9" x14ac:dyDescent="0.2">
@@ -2247,28 +2279,28 @@
         <v>96</v>
       </c>
       <c r="B47">
-        <v>0.5</v>
+        <v>0.66666999999999998</v>
       </c>
       <c r="C47">
-        <v>0.25</v>
+        <v>0.33333000000000002</v>
       </c>
       <c r="D47">
-        <v>0.25</v>
+        <v>0.33333000000000002</v>
       </c>
       <c r="E47">
-        <v>0.25</v>
+        <v>0.33333000000000002</v>
       </c>
       <c r="G47">
         <f t="shared" si="0"/>
-        <v>-0.25</v>
+        <v>-0.33333999999999997</v>
       </c>
       <c r="H47">
         <f t="shared" si="1"/>
-        <v>-0.25</v>
+        <v>-0.33333999999999997</v>
       </c>
       <c r="I47">
         <f t="shared" si="2"/>
-        <v>-0.25</v>
+        <v>-0.33333999999999997</v>
       </c>
     </row>
     <row r="48" spans="1:9" x14ac:dyDescent="0.2">
@@ -2305,28 +2337,28 @@
         <v>92</v>
       </c>
       <c r="B49">
-        <v>0.98492000000000002</v>
+        <v>0.98829999999999996</v>
       </c>
       <c r="C49">
-        <v>0.98492000000000002</v>
+        <v>0.98165000000000002</v>
       </c>
       <c r="D49">
-        <v>0.98492000000000002</v>
+        <v>0.98165000000000002</v>
       </c>
       <c r="E49">
-        <v>0.98492000000000002</v>
+        <v>0.98165000000000002</v>
       </c>
       <c r="G49">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>-6.6499999999999337E-3</v>
       </c>
       <c r="H49">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>-6.6499999999999337E-3</v>
       </c>
       <c r="I49">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>-6.6499999999999337E-3</v>
       </c>
     </row>
     <row r="50" spans="1:9" x14ac:dyDescent="0.2">
@@ -2363,28 +2395,28 @@
         <v>64</v>
       </c>
       <c r="B51">
-        <v>0.77778000000000003</v>
+        <v>0.85714000000000001</v>
       </c>
       <c r="C51">
-        <v>0.88888999999999996</v>
+        <v>1</v>
       </c>
       <c r="D51">
-        <v>0.88888999999999996</v>
+        <v>1</v>
       </c>
       <c r="E51">
-        <v>0.88888999999999996</v>
+        <v>1</v>
       </c>
       <c r="G51">
         <f t="shared" si="0"/>
-        <v>0.11110999999999993</v>
+        <v>0.14285999999999999</v>
       </c>
       <c r="H51">
         <f t="shared" si="1"/>
-        <v>0.11110999999999993</v>
+        <v>0.14285999999999999</v>
       </c>
       <c r="I51">
         <f t="shared" si="2"/>
-        <v>0.11110999999999993</v>
+        <v>0.14285999999999999</v>
       </c>
     </row>
     <row r="52" spans="1:9" x14ac:dyDescent="0.2">
@@ -2392,28 +2424,28 @@
         <v>65</v>
       </c>
       <c r="B52">
+        <v>0.85714000000000001</v>
+      </c>
+      <c r="C52">
+        <v>0</v>
+      </c>
+      <c r="D52">
         <v>0.66666999999999998</v>
       </c>
-      <c r="C52">
-        <v>0</v>
-      </c>
-      <c r="D52">
-        <v>0.44444</v>
-      </c>
       <c r="E52">
-        <v>0.44444</v>
+        <v>0.66666999999999998</v>
       </c>
       <c r="G52">
         <f t="shared" si="0"/>
-        <v>-0.66666999999999998</v>
+        <v>-0.85714000000000001</v>
       </c>
       <c r="H52">
         <f t="shared" si="1"/>
-        <v>-0.22222999999999998</v>
+        <v>-0.19047000000000003</v>
       </c>
       <c r="I52">
         <f t="shared" si="2"/>
-        <v>-0.22222999999999998</v>
+        <v>-0.19047000000000003</v>
       </c>
     </row>
     <row r="53" spans="1:9" x14ac:dyDescent="0.2">
@@ -2421,28 +2453,28 @@
         <v>63</v>
       </c>
       <c r="B53">
-        <v>0.77778000000000003</v>
+        <v>0.85714000000000001</v>
       </c>
       <c r="C53">
-        <v>0.88888999999999996</v>
+        <v>1</v>
       </c>
       <c r="D53">
-        <v>0.88888999999999996</v>
+        <v>1</v>
       </c>
       <c r="E53">
-        <v>0.88888999999999996</v>
+        <v>1</v>
       </c>
       <c r="G53">
         <f t="shared" si="0"/>
-        <v>0.11110999999999993</v>
+        <v>0.14285999999999999</v>
       </c>
       <c r="H53">
         <f t="shared" si="1"/>
-        <v>0.11110999999999993</v>
+        <v>0.14285999999999999</v>
       </c>
       <c r="I53">
         <f t="shared" si="2"/>
-        <v>0.11110999999999993</v>
+        <v>0.14285999999999999</v>
       </c>
     </row>
     <row r="54" spans="1:9" x14ac:dyDescent="0.2">
@@ -2450,28 +2482,28 @@
         <v>11</v>
       </c>
       <c r="B54">
-        <v>9.0910000000000005E-2</v>
+        <v>0.125</v>
       </c>
       <c r="C54">
-        <v>4.5449999999999997E-2</v>
+        <v>6.6669999999999993E-2</v>
       </c>
       <c r="D54">
-        <v>4.5449999999999997E-2</v>
+        <v>6.6669999999999993E-2</v>
       </c>
       <c r="E54">
-        <v>4.5449999999999997E-2</v>
+        <v>6.6669999999999993E-2</v>
       </c>
       <c r="G54">
         <f t="shared" si="0"/>
-        <v>-4.5460000000000007E-2</v>
+        <v>-5.8330000000000007E-2</v>
       </c>
       <c r="H54">
         <f t="shared" si="1"/>
-        <v>-4.5460000000000007E-2</v>
+        <v>-5.8330000000000007E-2</v>
       </c>
       <c r="I54">
         <f t="shared" si="2"/>
-        <v>-4.5460000000000007E-2</v>
+        <v>-5.8330000000000007E-2</v>
       </c>
     </row>
     <row r="55" spans="1:9" x14ac:dyDescent="0.2">
@@ -2479,28 +2511,28 @@
         <v>13</v>
       </c>
       <c r="B55">
-        <v>0.88888999999999996</v>
+        <v>0.91666999999999998</v>
       </c>
       <c r="C55">
-        <v>0.88461999999999996</v>
+        <v>0.90908999999999995</v>
       </c>
       <c r="D55">
-        <v>0.88461999999999996</v>
+        <v>0.90908999999999995</v>
       </c>
       <c r="E55">
-        <v>0.88461999999999996</v>
+        <v>0.90908999999999995</v>
       </c>
       <c r="G55">
         <f t="shared" si="0"/>
-        <v>-4.269999999999996E-3</v>
+        <v>-7.5800000000000312E-3</v>
       </c>
       <c r="H55">
         <f t="shared" si="1"/>
-        <v>-4.269999999999996E-3</v>
+        <v>-7.5800000000000312E-3</v>
       </c>
       <c r="I55">
         <f t="shared" si="2"/>
-        <v>-4.269999999999996E-3</v>
+        <v>-7.5800000000000312E-3</v>
       </c>
     </row>
     <row r="56" spans="1:9" x14ac:dyDescent="0.2">
@@ -2540,25 +2572,25 @@
         <v>1</v>
       </c>
       <c r="C57">
-        <v>0.79544999999999999</v>
+        <v>0.93332999999999999</v>
       </c>
       <c r="D57">
-        <v>0.79544999999999999</v>
+        <v>0.93332999999999999</v>
       </c>
       <c r="E57">
-        <v>0.79544999999999999</v>
+        <v>0.93332999999999999</v>
       </c>
       <c r="G57">
         <f t="shared" si="0"/>
-        <v>-0.20455000000000001</v>
+        <v>-6.6670000000000007E-2</v>
       </c>
       <c r="H57">
         <f t="shared" si="1"/>
-        <v>-0.20455000000000001</v>
+        <v>-6.6670000000000007E-2</v>
       </c>
       <c r="I57">
         <f t="shared" si="2"/>
-        <v>-0.20455000000000001</v>
+        <v>-6.6670000000000007E-2</v>
       </c>
     </row>
     <row r="58" spans="1:9" x14ac:dyDescent="0.2">
@@ -2595,28 +2627,28 @@
         <v>12</v>
       </c>
       <c r="B59">
-        <v>3.7039999999999997E-2</v>
+        <v>4.1669999999999999E-2</v>
       </c>
       <c r="C59">
-        <v>3.8460000000000001E-2</v>
+        <v>4.5449999999999997E-2</v>
       </c>
       <c r="D59">
-        <v>3.8460000000000001E-2</v>
+        <v>4.5449999999999997E-2</v>
       </c>
       <c r="E59">
-        <v>7.6920000000000002E-2</v>
+        <v>9.0910000000000005E-2</v>
       </c>
       <c r="G59">
         <f t="shared" si="0"/>
-        <v>1.4200000000000046E-3</v>
+        <v>3.7799999999999986E-3</v>
       </c>
       <c r="H59">
         <f t="shared" si="1"/>
-        <v>1.4200000000000046E-3</v>
+        <v>3.7799999999999986E-3</v>
       </c>
       <c r="I59">
         <f t="shared" si="2"/>
-        <v>3.9880000000000006E-2</v>
+        <v>4.9240000000000006E-2</v>
       </c>
     </row>
     <row r="60" spans="1:9" x14ac:dyDescent="0.2">
@@ -2624,28 +2656,28 @@
         <v>8</v>
       </c>
       <c r="B60">
-        <v>0.93181999999999998</v>
+        <v>0.96875</v>
       </c>
       <c r="C60">
-        <v>0.93181999999999998</v>
+        <v>0.9</v>
       </c>
       <c r="D60">
-        <v>0.93181999999999998</v>
+        <v>0.9</v>
       </c>
       <c r="E60">
-        <v>0.77273000000000003</v>
+        <v>0.9</v>
       </c>
       <c r="G60">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>-6.8749999999999978E-2</v>
       </c>
       <c r="H60">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>-6.8749999999999978E-2</v>
       </c>
       <c r="I60">
         <f t="shared" si="2"/>
-        <v>-0.15908999999999995</v>
+        <v>-6.8749999999999978E-2</v>
       </c>
     </row>
     <row r="61" spans="1:9" x14ac:dyDescent="0.2">
@@ -2653,28 +2685,28 @@
         <v>60</v>
       </c>
       <c r="B61">
-        <v>0.41176000000000001</v>
+        <v>0.85714000000000001</v>
       </c>
       <c r="C61">
-        <v>0.47059000000000001</v>
+        <v>1</v>
       </c>
       <c r="D61">
-        <v>0.47059000000000001</v>
+        <v>1</v>
       </c>
       <c r="E61">
-        <v>0.47059000000000001</v>
+        <v>1</v>
       </c>
       <c r="G61">
         <f t="shared" si="0"/>
-        <v>5.8829999999999993E-2</v>
+        <v>0.14285999999999999</v>
       </c>
       <c r="H61">
         <f t="shared" si="1"/>
-        <v>5.8829999999999993E-2</v>
+        <v>0.14285999999999999</v>
       </c>
       <c r="I61">
         <f t="shared" si="2"/>
-        <v>5.8829999999999993E-2</v>
+        <v>0.14285999999999999</v>
       </c>
     </row>
     <row r="62" spans="1:9" x14ac:dyDescent="0.2">
@@ -2682,28 +2714,28 @@
         <v>62</v>
       </c>
       <c r="B62">
-        <v>0.23529</v>
+        <v>0.57142999999999999</v>
       </c>
       <c r="C62">
         <v>0</v>
       </c>
       <c r="D62">
-        <v>0.17646999999999999</v>
+        <v>0.42857000000000001</v>
       </c>
       <c r="E62">
-        <v>0.17646999999999999</v>
+        <v>0.42857000000000001</v>
       </c>
       <c r="G62">
         <f t="shared" si="0"/>
-        <v>-0.23529</v>
+        <v>-0.57142999999999999</v>
       </c>
       <c r="H62">
         <f t="shared" si="1"/>
-        <v>-5.8820000000000011E-2</v>
+        <v>-0.14285999999999999</v>
       </c>
       <c r="I62">
         <f t="shared" si="2"/>
-        <v>-5.8820000000000011E-2</v>
+        <v>-0.14285999999999999</v>
       </c>
     </row>
     <row r="63" spans="1:9" x14ac:dyDescent="0.2">
@@ -2714,25 +2746,25 @@
         <v>1</v>
       </c>
       <c r="C63">
-        <v>0.11765</v>
+        <v>0.28571000000000002</v>
       </c>
       <c r="D63">
-        <v>0.11765</v>
+        <v>0.28571000000000002</v>
       </c>
       <c r="E63">
-        <v>0.11765</v>
+        <v>0.28571000000000002</v>
       </c>
       <c r="G63">
         <f t="shared" si="0"/>
-        <v>-0.88234999999999997</v>
+        <v>-0.71428999999999998</v>
       </c>
       <c r="H63">
         <f t="shared" si="1"/>
-        <v>-0.88234999999999997</v>
+        <v>-0.71428999999999998</v>
       </c>
       <c r="I63">
         <f t="shared" si="2"/>
-        <v>-0.88234999999999997</v>
+        <v>-0.71428999999999998</v>
       </c>
     </row>
     <row r="64" spans="1:9" x14ac:dyDescent="0.2">
@@ -2743,25 +2775,25 @@
         <v>1</v>
       </c>
       <c r="C64">
-        <v>0.41176000000000001</v>
+        <v>1</v>
       </c>
       <c r="D64">
-        <v>0.41176000000000001</v>
+        <v>1</v>
       </c>
       <c r="E64">
-        <v>0.41176000000000001</v>
+        <v>1</v>
       </c>
       <c r="G64">
         <f t="shared" si="0"/>
-        <v>-0.58823999999999999</v>
+        <v>0</v>
       </c>
       <c r="H64">
         <f t="shared" si="1"/>
-        <v>-0.58823999999999999</v>
+        <v>0</v>
       </c>
       <c r="I64">
         <f t="shared" si="2"/>
-        <v>-0.58823999999999999</v>
+        <v>0</v>
       </c>
     </row>
     <row r="65" spans="1:9" x14ac:dyDescent="0.2">
@@ -2778,7 +2810,7 @@
         <v>1</v>
       </c>
       <c r="E65">
-        <v>0.75</v>
+        <v>1</v>
       </c>
       <c r="G65">
         <f t="shared" si="0"/>
@@ -2790,7 +2822,7 @@
       </c>
       <c r="I65">
         <f t="shared" si="2"/>
-        <v>-0.25</v>
+        <v>0</v>
       </c>
     </row>
     <row r="66" spans="1:9" x14ac:dyDescent="0.2">
@@ -2798,7 +2830,7 @@
         <v>1</v>
       </c>
       <c r="B66">
-        <v>0.5</v>
+        <v>0.66666999999999998</v>
       </c>
       <c r="C66">
         <v>1</v>
@@ -2807,19 +2839,19 @@
         <v>1</v>
       </c>
       <c r="E66">
-        <v>0.75</v>
+        <v>1</v>
       </c>
       <c r="G66">
         <f t="shared" si="0"/>
-        <v>0.5</v>
+        <v>0.33333000000000002</v>
       </c>
       <c r="H66">
         <f t="shared" si="1"/>
-        <v>0.5</v>
+        <v>0.33333000000000002</v>
       </c>
       <c r="I66">
         <f t="shared" si="2"/>
-        <v>0.25</v>
+        <v>0.33333000000000002</v>
       </c>
     </row>
     <row r="67" spans="1:9" x14ac:dyDescent="0.2">
@@ -2827,7 +2859,7 @@
         <v>3</v>
       </c>
       <c r="B67">
-        <v>0.5</v>
+        <v>0.66666999999999998</v>
       </c>
       <c r="C67">
         <v>1</v>
@@ -2836,19 +2868,19 @@
         <v>1</v>
       </c>
       <c r="E67">
-        <v>0.75</v>
+        <v>1</v>
       </c>
       <c r="G67">
         <f t="shared" ref="G67:G101" si="3">C67-B67</f>
-        <v>0.5</v>
+        <v>0.33333000000000002</v>
       </c>
       <c r="H67">
         <f t="shared" ref="H67:H101" si="4">D67-B67</f>
-        <v>0.5</v>
+        <v>0.33333000000000002</v>
       </c>
       <c r="I67">
         <f t="shared" ref="I67:I101" si="5">E67-B67</f>
-        <v>0.25</v>
+        <v>0.33333000000000002</v>
       </c>
     </row>
     <row r="68" spans="1:9" x14ac:dyDescent="0.2">
@@ -2856,16 +2888,16 @@
         <v>4</v>
       </c>
       <c r="B68">
-        <v>0.25</v>
+        <v>0.33333000000000002</v>
       </c>
       <c r="C68">
-        <v>0.25</v>
+        <v>0.33333000000000002</v>
       </c>
       <c r="D68">
-        <v>0.25</v>
+        <v>0.33333000000000002</v>
       </c>
       <c r="E68">
-        <v>0.25</v>
+        <v>0.33333000000000002</v>
       </c>
       <c r="G68">
         <f t="shared" si="3"/>
@@ -3001,28 +3033,28 @@
         <v>40</v>
       </c>
       <c r="B73">
-        <v>0.95555999999999996</v>
+        <v>0.97619</v>
       </c>
       <c r="C73">
-        <v>0.98889000000000005</v>
+        <v>0.82857000000000003</v>
       </c>
       <c r="D73">
-        <v>0.98889000000000005</v>
+        <v>0.82857000000000003</v>
       </c>
       <c r="E73">
-        <v>0.86667000000000005</v>
+        <v>1</v>
       </c>
       <c r="G73">
         <f t="shared" si="3"/>
-        <v>3.3330000000000082E-2</v>
+        <v>-0.14761999999999997</v>
       </c>
       <c r="H73">
         <f t="shared" si="4"/>
-        <v>3.3330000000000082E-2</v>
+        <v>-0.14761999999999997</v>
       </c>
       <c r="I73">
         <f t="shared" si="5"/>
-        <v>-8.8889999999999914E-2</v>
+        <v>2.3809999999999998E-2</v>
       </c>
     </row>
     <row r="74" spans="1:9" x14ac:dyDescent="0.2">
@@ -3030,28 +3062,28 @@
         <v>41</v>
       </c>
       <c r="B74">
-        <v>0.95555999999999996</v>
+        <v>0.97619</v>
       </c>
       <c r="C74">
-        <v>0.98889000000000005</v>
+        <v>0.82857000000000003</v>
       </c>
       <c r="D74">
-        <v>0.98889000000000005</v>
+        <v>0.94286000000000003</v>
       </c>
       <c r="E74">
-        <v>0.86667000000000005</v>
+        <v>1</v>
       </c>
       <c r="G74">
         <f t="shared" si="3"/>
-        <v>3.3330000000000082E-2</v>
+        <v>-0.14761999999999997</v>
       </c>
       <c r="H74">
         <f t="shared" si="4"/>
-        <v>3.3330000000000082E-2</v>
+        <v>-3.3329999999999971E-2</v>
       </c>
       <c r="I74">
         <f t="shared" si="5"/>
-        <v>-8.8889999999999914E-2</v>
+        <v>2.3809999999999998E-2</v>
       </c>
     </row>
     <row r="75" spans="1:9" x14ac:dyDescent="0.2">
@@ -3117,28 +3149,28 @@
         <v>43</v>
       </c>
       <c r="B77">
-        <v>0.82221999999999995</v>
+        <v>0.97619</v>
       </c>
       <c r="C77">
-        <v>0.84443999999999997</v>
+        <v>0.57142999999999999</v>
       </c>
       <c r="D77">
-        <v>0.84443999999999997</v>
+        <v>0.57142999999999999</v>
       </c>
       <c r="E77">
-        <v>0.84443999999999997</v>
+        <v>0.57142999999999999</v>
       </c>
       <c r="G77">
         <f t="shared" si="3"/>
-        <v>2.2220000000000018E-2</v>
+        <v>-0.40476000000000001</v>
       </c>
       <c r="H77">
         <f t="shared" si="4"/>
-        <v>2.2220000000000018E-2</v>
+        <v>-0.40476000000000001</v>
       </c>
       <c r="I77">
         <f t="shared" si="5"/>
-        <v>2.2220000000000018E-2</v>
+        <v>-0.40476000000000001</v>
       </c>
     </row>
     <row r="78" spans="1:9" x14ac:dyDescent="0.2">
@@ -3146,28 +3178,28 @@
         <v>46</v>
       </c>
       <c r="B78">
-        <v>0.45713999999999999</v>
+        <v>0.64705999999999997</v>
       </c>
       <c r="C78">
-        <v>0.14285999999999999</v>
+        <v>0.33333000000000002</v>
       </c>
       <c r="D78">
-        <v>0.14285999999999999</v>
+        <v>0.33333000000000002</v>
       </c>
       <c r="E78">
-        <v>0.14285999999999999</v>
+        <v>0.33333000000000002</v>
       </c>
       <c r="G78">
         <f t="shared" si="3"/>
-        <v>-0.31428</v>
+        <v>-0.31372999999999995</v>
       </c>
       <c r="H78">
         <f t="shared" si="4"/>
-        <v>-0.31428</v>
+        <v>-0.31372999999999995</v>
       </c>
       <c r="I78">
         <f t="shared" si="5"/>
-        <v>-0.31428</v>
+        <v>-0.31372999999999995</v>
       </c>
     </row>
     <row r="79" spans="1:9" x14ac:dyDescent="0.2">
@@ -3175,28 +3207,28 @@
         <v>48</v>
       </c>
       <c r="B79">
-        <v>0.91666999999999998</v>
+        <v>0.90908999999999995</v>
       </c>
       <c r="C79">
-        <v>0.58333000000000002</v>
+        <v>0.625</v>
       </c>
       <c r="D79">
-        <v>0.58333000000000002</v>
+        <v>0.625</v>
       </c>
       <c r="E79">
-        <v>0.58333000000000002</v>
+        <v>0.625</v>
       </c>
       <c r="G79">
         <f t="shared" si="3"/>
-        <v>-0.33333999999999997</v>
+        <v>-0.28408999999999995</v>
       </c>
       <c r="H79">
         <f t="shared" si="4"/>
-        <v>-0.33333999999999997</v>
+        <v>-0.28408999999999995</v>
       </c>
       <c r="I79">
         <f t="shared" si="5"/>
-        <v>-0.33333999999999997</v>
+        <v>-0.28408999999999995</v>
       </c>
     </row>
     <row r="80" spans="1:9" x14ac:dyDescent="0.2">
@@ -3204,7 +3236,7 @@
         <v>49</v>
       </c>
       <c r="B80">
-        <v>0.75</v>
+        <v>0.85714000000000001</v>
       </c>
       <c r="C80">
         <v>0</v>
@@ -3217,15 +3249,15 @@
       </c>
       <c r="G80">
         <f t="shared" si="3"/>
-        <v>-0.75</v>
+        <v>-0.85714000000000001</v>
       </c>
       <c r="H80">
         <f t="shared" si="4"/>
-        <v>-0.75</v>
+        <v>-0.85714000000000001</v>
       </c>
       <c r="I80">
         <f t="shared" si="5"/>
-        <v>-0.75</v>
+        <v>-0.85714000000000001</v>
       </c>
     </row>
     <row r="81" spans="1:9" x14ac:dyDescent="0.2">
@@ -3262,28 +3294,28 @@
         <v>44</v>
       </c>
       <c r="B82">
-        <v>0.94443999999999995</v>
+        <v>0.42857000000000001</v>
       </c>
       <c r="C82">
-        <v>0.18889</v>
+        <v>0.28571000000000002</v>
       </c>
       <c r="D82">
-        <v>0.18889</v>
+        <v>0.28571000000000002</v>
       </c>
       <c r="E82">
-        <v>0.18889</v>
+        <v>0.28571000000000002</v>
       </c>
       <c r="G82">
         <f t="shared" si="3"/>
-        <v>-0.75554999999999994</v>
+        <v>-0.14285999999999999</v>
       </c>
       <c r="H82">
         <f t="shared" si="4"/>
-        <v>-0.75554999999999994</v>
+        <v>-0.14285999999999999</v>
       </c>
       <c r="I82">
         <f t="shared" si="5"/>
-        <v>-0.75554999999999994</v>
+        <v>-0.14285999999999999</v>
       </c>
     </row>
     <row r="83" spans="1:9" x14ac:dyDescent="0.2">
@@ -3291,28 +3323,28 @@
         <v>51</v>
       </c>
       <c r="B83">
-        <v>0.94030000000000002</v>
+        <v>0.97872000000000003</v>
       </c>
       <c r="C83">
-        <v>0.98507</v>
+        <v>1</v>
       </c>
       <c r="D83">
-        <v>0.98507</v>
+        <v>1</v>
       </c>
       <c r="E83">
-        <v>0.98507</v>
+        <v>1</v>
       </c>
       <c r="G83">
         <f t="shared" si="3"/>
-        <v>4.4769999999999976E-2</v>
+        <v>2.1279999999999966E-2</v>
       </c>
       <c r="H83">
         <f t="shared" si="4"/>
-        <v>4.4769999999999976E-2</v>
+        <v>2.1279999999999966E-2</v>
       </c>
       <c r="I83">
         <f t="shared" si="5"/>
-        <v>4.4769999999999976E-2</v>
+        <v>2.1279999999999966E-2</v>
       </c>
     </row>
     <row r="84" spans="1:9" x14ac:dyDescent="0.2">
@@ -3320,28 +3352,28 @@
         <v>52</v>
       </c>
       <c r="B84">
-        <v>0.94030000000000002</v>
+        <v>0.97872000000000003</v>
       </c>
       <c r="C84">
-        <v>0.10448</v>
+        <v>7.4999999999999997E-2</v>
       </c>
       <c r="D84">
-        <v>0.10448</v>
+        <v>7.4999999999999997E-2</v>
       </c>
       <c r="E84">
         <v>1</v>
       </c>
       <c r="G84">
         <f t="shared" si="3"/>
-        <v>-0.83582000000000001</v>
+        <v>-0.90372000000000008</v>
       </c>
       <c r="H84">
         <f t="shared" si="4"/>
-        <v>-0.83582000000000001</v>
+        <v>-0.90372000000000008</v>
       </c>
       <c r="I84">
         <f t="shared" si="5"/>
-        <v>5.9699999999999975E-2</v>
+        <v>2.1279999999999966E-2</v>
       </c>
     </row>
     <row r="85" spans="1:9" x14ac:dyDescent="0.2">
@@ -3349,28 +3381,28 @@
         <v>55</v>
       </c>
       <c r="B85">
-        <v>0.89551999999999998</v>
+        <v>0.93616999999999995</v>
       </c>
       <c r="C85">
-        <v>0.49253999999999998</v>
+        <v>0.52500000000000002</v>
       </c>
       <c r="D85">
-        <v>0.49253999999999998</v>
+        <v>0.52500000000000002</v>
       </c>
       <c r="E85">
-        <v>0.49253999999999998</v>
+        <v>0.52500000000000002</v>
       </c>
       <c r="G85">
         <f t="shared" si="3"/>
-        <v>-0.40298</v>
+        <v>-0.41116999999999992</v>
       </c>
       <c r="H85">
         <f t="shared" si="4"/>
-        <v>-0.40298</v>
+        <v>-0.41116999999999992</v>
       </c>
       <c r="I85">
         <f t="shared" si="5"/>
-        <v>-0.40298</v>
+        <v>-0.41116999999999992</v>
       </c>
     </row>
     <row r="86" spans="1:9" x14ac:dyDescent="0.2">
@@ -3407,28 +3439,28 @@
         <v>50</v>
       </c>
       <c r="B87">
-        <v>0.94030000000000002</v>
+        <v>0.97872000000000003</v>
       </c>
       <c r="C87">
-        <v>0.95521999999999996</v>
+        <v>1</v>
       </c>
       <c r="D87">
-        <v>0.95521999999999996</v>
+        <v>1</v>
       </c>
       <c r="E87">
         <v>1</v>
       </c>
       <c r="G87">
         <f t="shared" si="3"/>
-        <v>1.4919999999999933E-2</v>
+        <v>2.1279999999999966E-2</v>
       </c>
       <c r="H87">
         <f t="shared" si="4"/>
-        <v>1.4919999999999933E-2</v>
+        <v>2.1279999999999966E-2</v>
       </c>
       <c r="I87">
         <f t="shared" si="5"/>
-        <v>5.9699999999999975E-2</v>
+        <v>2.1279999999999966E-2</v>
       </c>
     </row>
     <row r="88" spans="1:9" x14ac:dyDescent="0.2">
@@ -3436,28 +3468,28 @@
         <v>56</v>
       </c>
       <c r="B88">
-        <v>0.74626999999999999</v>
+        <v>0.82979000000000003</v>
       </c>
       <c r="C88">
-        <v>0.71641999999999995</v>
+        <v>0.8</v>
       </c>
       <c r="D88">
-        <v>0.71641999999999995</v>
+        <v>0.8</v>
       </c>
       <c r="E88">
-        <v>0.71641999999999995</v>
+        <v>0.8</v>
       </c>
       <c r="G88">
         <f t="shared" si="3"/>
-        <v>-2.9850000000000043E-2</v>
+        <v>-2.9789999999999983E-2</v>
       </c>
       <c r="H88">
         <f t="shared" si="4"/>
-        <v>-2.9850000000000043E-2</v>
+        <v>-2.9789999999999983E-2</v>
       </c>
       <c r="I88">
         <f t="shared" si="5"/>
-        <v>-2.9850000000000043E-2</v>
+        <v>-2.9789999999999983E-2</v>
       </c>
     </row>
     <row r="89" spans="1:9" x14ac:dyDescent="0.2">
@@ -3465,28 +3497,28 @@
         <v>54</v>
       </c>
       <c r="B89">
-        <v>0.88060000000000005</v>
+        <v>0.95745000000000002</v>
       </c>
       <c r="C89">
-        <v>0.55223999999999995</v>
+        <v>0.67500000000000004</v>
       </c>
       <c r="D89">
-        <v>0.55223999999999995</v>
+        <v>0.67500000000000004</v>
       </c>
       <c r="E89">
-        <v>0.55223999999999995</v>
+        <v>0.67500000000000004</v>
       </c>
       <c r="G89">
         <f t="shared" si="3"/>
-        <v>-0.3283600000000001</v>
+        <v>-0.28244999999999998</v>
       </c>
       <c r="H89">
         <f t="shared" si="4"/>
-        <v>-0.3283600000000001</v>
+        <v>-0.28244999999999998</v>
       </c>
       <c r="I89">
         <f t="shared" si="5"/>
-        <v>-0.3283600000000001</v>
+        <v>-0.28244999999999998</v>
       </c>
     </row>
     <row r="90" spans="1:9" x14ac:dyDescent="0.2">
@@ -3523,28 +3555,28 @@
         <v>57</v>
       </c>
       <c r="B91">
-        <v>0.31342999999999999</v>
+        <v>0.31914999999999999</v>
       </c>
       <c r="C91">
-        <v>0.10448</v>
+        <v>7.4999999999999997E-2</v>
       </c>
       <c r="D91">
-        <v>0.10448</v>
+        <v>7.4999999999999997E-2</v>
       </c>
       <c r="E91">
-        <v>0.10448</v>
+        <v>7.4999999999999997E-2</v>
       </c>
       <c r="G91">
         <f t="shared" si="3"/>
-        <v>-0.20894999999999997</v>
+        <v>-0.24414999999999998</v>
       </c>
       <c r="H91">
         <f t="shared" si="4"/>
-        <v>-0.20894999999999997</v>
+        <v>-0.24414999999999998</v>
       </c>
       <c r="I91">
         <f t="shared" si="5"/>
-        <v>-0.20894999999999997</v>
+        <v>-0.24414999999999998</v>
       </c>
     </row>
     <row r="92" spans="1:9" x14ac:dyDescent="0.2">
@@ -3555,21 +3587,21 @@
         <v>0.875</v>
       </c>
       <c r="C92">
-        <v>0.875</v>
+        <v>0.83333000000000002</v>
       </c>
       <c r="D92">
-        <v>0.875</v>
+        <v>0.83333000000000002</v>
       </c>
       <c r="E92">
         <v>1</v>
       </c>
       <c r="G92">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>-4.1669999999999985E-2</v>
       </c>
       <c r="H92">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>-4.1669999999999985E-2</v>
       </c>
       <c r="I92">
         <f t="shared" si="5"/>
@@ -3584,25 +3616,25 @@
         <v>0.875</v>
       </c>
       <c r="C93">
-        <v>0.75</v>
+        <v>0.83333000000000002</v>
       </c>
       <c r="D93">
-        <v>0.75</v>
+        <v>0.83333000000000002</v>
       </c>
       <c r="E93">
-        <v>0.875</v>
+        <v>1</v>
       </c>
       <c r="G93">
         <f t="shared" si="3"/>
-        <v>-0.125</v>
+        <v>-4.1669999999999985E-2</v>
       </c>
       <c r="H93">
         <f t="shared" si="4"/>
-        <v>-0.125</v>
+        <v>-4.1669999999999985E-2</v>
       </c>
       <c r="I93">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>0.125</v>
       </c>
     </row>
     <row r="94" spans="1:9" x14ac:dyDescent="0.2">
@@ -3610,7 +3642,7 @@
         <v>70</v>
       </c>
       <c r="B94">
-        <v>0.88888999999999996</v>
+        <v>0.875</v>
       </c>
       <c r="C94">
         <v>1</v>
@@ -3623,15 +3655,15 @@
       </c>
       <c r="G94">
         <f t="shared" si="3"/>
-        <v>0.11111000000000004</v>
+        <v>0.125</v>
       </c>
       <c r="H94">
         <f t="shared" si="4"/>
-        <v>0.11111000000000004</v>
+        <v>0.125</v>
       </c>
       <c r="I94">
         <f t="shared" si="5"/>
-        <v>0.11111000000000004</v>
+        <v>0.125</v>
       </c>
     </row>
     <row r="95" spans="1:9" x14ac:dyDescent="0.2">
@@ -3639,7 +3671,7 @@
         <v>69</v>
       </c>
       <c r="B95">
-        <v>0.77778000000000003</v>
+        <v>0.75</v>
       </c>
       <c r="C95">
         <v>1</v>
@@ -3652,15 +3684,15 @@
       </c>
       <c r="G95">
         <f t="shared" si="3"/>
-        <v>0.22221999999999997</v>
+        <v>0.25</v>
       </c>
       <c r="H95">
         <f t="shared" si="4"/>
-        <v>0.22221999999999997</v>
+        <v>0.25</v>
       </c>
       <c r="I95">
         <f t="shared" si="5"/>
-        <v>0.22221999999999997</v>
+        <v>0.25</v>
       </c>
     </row>
     <row r="96" spans="1:9" x14ac:dyDescent="0.2">
@@ -3668,7 +3700,7 @@
         <v>68</v>
       </c>
       <c r="B96">
-        <v>0.77778000000000003</v>
+        <v>0.75</v>
       </c>
       <c r="C96">
         <v>1</v>
@@ -3681,15 +3713,15 @@
       </c>
       <c r="G96">
         <f t="shared" si="3"/>
-        <v>0.22221999999999997</v>
+        <v>0.25</v>
       </c>
       <c r="H96">
         <f t="shared" si="4"/>
-        <v>0.22221999999999997</v>
+        <v>0.25</v>
       </c>
       <c r="I96">
         <f t="shared" si="5"/>
-        <v>0.22221999999999997</v>
+        <v>0.25</v>
       </c>
     </row>
     <row r="97" spans="1:9" x14ac:dyDescent="0.2">
@@ -3697,7 +3729,7 @@
         <v>37</v>
       </c>
       <c r="B97">
-        <v>0.8</v>
+        <v>0.75</v>
       </c>
       <c r="C97">
         <v>1</v>
@@ -3710,15 +3742,15 @@
       </c>
       <c r="G97">
         <f t="shared" si="3"/>
-        <v>0.19999999999999996</v>
+        <v>0.25</v>
       </c>
       <c r="H97">
         <f t="shared" si="4"/>
-        <v>0.19999999999999996</v>
+        <v>0.25</v>
       </c>
       <c r="I97">
         <f t="shared" si="5"/>
-        <v>0.19999999999999996</v>
+        <v>0.25</v>
       </c>
     </row>
     <row r="98" spans="1:9" x14ac:dyDescent="0.2">
@@ -3726,7 +3758,7 @@
         <v>38</v>
       </c>
       <c r="B98">
-        <v>0.8</v>
+        <v>0.75</v>
       </c>
       <c r="C98">
         <v>1</v>
@@ -3739,15 +3771,15 @@
       </c>
       <c r="G98">
         <f t="shared" si="3"/>
-        <v>0.19999999999999996</v>
+        <v>0.25</v>
       </c>
       <c r="H98">
         <f t="shared" si="4"/>
-        <v>0.19999999999999996</v>
+        <v>0.25</v>
       </c>
       <c r="I98">
         <f t="shared" si="5"/>
-        <v>0.19999999999999996</v>
+        <v>0.25</v>
       </c>
     </row>
     <row r="99" spans="1:9" x14ac:dyDescent="0.2">
@@ -3869,8 +3901,8 @@
         <v>105</v>
       </c>
       <c r="B2">
-        <f>1+AVERAGE(Normalised!G1:G101)</f>
-        <v>0.90509569999999995</v>
+        <f>1+AVERAGE(Wide!G2:G101)</f>
+        <v>0.89913409999999994</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.2">
@@ -3878,8 +3910,8 @@
         <v>104</v>
       </c>
       <c r="B3">
-        <f>1+AVERAGE(Normalised!H1:H101)</f>
-        <v>0.91686029999999996</v>
+        <f>1+AVERAGE(Wide!H2:H101)</f>
+        <v>0.92108440000000003</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.2">
@@ -3887,8 +3919,8 @@
         <v>106</v>
       </c>
       <c r="B4">
-        <f>1+AVERAGE(Normalised!I1:I101)</f>
-        <v>0.93276610000000004</v>
+        <f>1+AVERAGE(Wide!I2:I101)</f>
+        <v>0.95646240000000005</v>
       </c>
     </row>
   </sheetData>
@@ -3925,6 +3957,7 @@
         <v>29</v>
       </c>
       <c r="B2">
+        <f>Wide!B2</f>
         <v>0.8</v>
       </c>
       <c r="C2" t="s">
@@ -3936,6 +3969,7 @@
         <v>83</v>
       </c>
       <c r="B3">
+        <f>Wide!B3</f>
         <v>1</v>
       </c>
       <c r="C3" t="s">
@@ -3947,6 +3981,7 @@
         <v>84</v>
       </c>
       <c r="B4">
+        <f>Wide!B4</f>
         <v>1</v>
       </c>
       <c r="C4" t="s">
@@ -3958,6 +3993,7 @@
         <v>85</v>
       </c>
       <c r="B5">
+        <f>Wide!B5</f>
         <v>1</v>
       </c>
       <c r="C5" t="s">
@@ -3969,7 +4005,8 @@
         <v>86</v>
       </c>
       <c r="B6">
-        <v>0.90122999999999998</v>
+        <f>Wide!B6</f>
+        <v>0.97619</v>
       </c>
       <c r="C6" t="s">
         <v>103</v>
@@ -3980,6 +4017,7 @@
         <v>87</v>
       </c>
       <c r="B7">
+        <f>Wide!B7</f>
         <v>0.66666999999999998</v>
       </c>
       <c r="C7" t="s">
@@ -3991,7 +4029,8 @@
         <v>88</v>
       </c>
       <c r="B8">
-        <v>0.92857000000000001</v>
+        <f>Wide!B8</f>
+        <v>0.90908999999999995</v>
       </c>
       <c r="C8" t="s">
         <v>103</v>
@@ -4002,6 +4041,7 @@
         <v>25</v>
       </c>
       <c r="B9">
+        <f>Wide!B9</f>
         <v>0.75</v>
       </c>
       <c r="C9" t="s">
@@ -4013,6 +4053,7 @@
         <v>27</v>
       </c>
       <c r="B10">
+        <f>Wide!B10</f>
         <v>0.75</v>
       </c>
       <c r="C10" t="s">
@@ -4024,6 +4065,7 @@
         <v>28</v>
       </c>
       <c r="B11">
+        <f>Wide!B11</f>
         <v>0.75</v>
       </c>
       <c r="C11" t="s">
@@ -4035,6 +4077,7 @@
         <v>26</v>
       </c>
       <c r="B12">
+        <f>Wide!B12</f>
         <v>0.75</v>
       </c>
       <c r="C12" t="s">
@@ -4046,7 +4089,8 @@
         <v>36</v>
       </c>
       <c r="B13">
-        <v>0.6</v>
+        <f>Wide!B13</f>
+        <v>0.83333000000000002</v>
       </c>
       <c r="C13" t="s">
         <v>103</v>
@@ -4057,7 +4101,8 @@
         <v>35</v>
       </c>
       <c r="B14">
-        <v>0.7</v>
+        <f>Wide!B14</f>
+        <v>0.83333000000000002</v>
       </c>
       <c r="C14" t="s">
         <v>103</v>
@@ -4068,7 +4113,8 @@
         <v>5</v>
       </c>
       <c r="B15">
-        <v>0.93181999999999998</v>
+        <f>Wide!B15</f>
+        <v>0.95238</v>
       </c>
       <c r="C15" t="s">
         <v>103</v>
@@ -4079,6 +4125,7 @@
         <v>6</v>
       </c>
       <c r="B16">
+        <f>Wide!B16</f>
         <v>1</v>
       </c>
       <c r="C16" t="s">
@@ -4090,7 +4137,8 @@
         <v>7</v>
       </c>
       <c r="B17">
-        <v>0.11364</v>
+        <f>Wide!B17</f>
+        <v>0.23810000000000001</v>
       </c>
       <c r="C17" t="s">
         <v>103</v>
@@ -4101,7 +4149,8 @@
         <v>31</v>
       </c>
       <c r="B18">
-        <v>0.77778000000000003</v>
+        <f>Wide!B18</f>
+        <v>0.875</v>
       </c>
       <c r="C18" t="s">
         <v>103</v>
@@ -4112,6 +4161,7 @@
         <v>32</v>
       </c>
       <c r="B19">
+        <f>Wide!B19</f>
         <v>0.75</v>
       </c>
       <c r="C19" t="s">
@@ -4123,7 +4173,8 @@
         <v>30</v>
       </c>
       <c r="B20">
-        <v>0.77778000000000003</v>
+        <f>Wide!B20</f>
+        <v>0.875</v>
       </c>
       <c r="C20" t="s">
         <v>103</v>
@@ -4134,6 +4185,7 @@
         <v>100</v>
       </c>
       <c r="B21">
+        <f>Wide!B21</f>
         <v>1</v>
       </c>
       <c r="C21" t="s">
@@ -4145,6 +4197,7 @@
         <v>67</v>
       </c>
       <c r="B22">
+        <f>Wide!B22</f>
         <v>0.75</v>
       </c>
       <c r="C22" t="s">
@@ -4156,6 +4209,7 @@
         <v>66</v>
       </c>
       <c r="B23">
+        <f>Wide!B23</f>
         <v>0.75</v>
       </c>
       <c r="C23" t="s">
@@ -4167,7 +4221,8 @@
         <v>78</v>
       </c>
       <c r="B24">
-        <v>0.9</v>
+        <f>Wide!B24</f>
+        <v>0.93877999999999995</v>
       </c>
       <c r="C24" t="s">
         <v>103</v>
@@ -4178,7 +4233,8 @@
         <v>79</v>
       </c>
       <c r="B25">
-        <v>0.88749999999999996</v>
+        <f>Wide!B25</f>
+        <v>0.91837000000000002</v>
       </c>
       <c r="C25" t="s">
         <v>103</v>
@@ -4189,7 +4245,8 @@
         <v>71</v>
       </c>
       <c r="B26">
-        <v>0.9</v>
+        <f>Wide!B26</f>
+        <v>0.93877999999999995</v>
       </c>
       <c r="C26" t="s">
         <v>103</v>
@@ -4200,6 +4257,7 @@
         <v>72</v>
       </c>
       <c r="B27">
+        <f>Wide!B27</f>
         <v>1</v>
       </c>
       <c r="C27" t="s">
@@ -4211,6 +4269,7 @@
         <v>81</v>
       </c>
       <c r="B28">
+        <f>Wide!B28</f>
         <v>1</v>
       </c>
       <c r="C28" t="s">
@@ -4222,6 +4281,7 @@
         <v>74</v>
       </c>
       <c r="B29">
+        <f>Wide!B29</f>
         <v>1</v>
       </c>
       <c r="C29" t="s">
@@ -4233,6 +4293,7 @@
         <v>73</v>
       </c>
       <c r="B30">
+        <f>Wide!B30</f>
         <v>1</v>
       </c>
       <c r="C30" t="s">
@@ -4244,6 +4305,7 @@
         <v>75</v>
       </c>
       <c r="B31">
+        <f>Wide!B31</f>
         <v>1</v>
       </c>
       <c r="C31" t="s">
@@ -4255,6 +4317,7 @@
         <v>82</v>
       </c>
       <c r="B32">
+        <f>Wide!B32</f>
         <v>1</v>
       </c>
       <c r="C32" t="s">
@@ -4266,7 +4329,8 @@
         <v>80</v>
       </c>
       <c r="B33">
-        <v>0.33750000000000002</v>
+        <f>Wide!B33</f>
+        <v>0.32652999999999999</v>
       </c>
       <c r="C33" t="s">
         <v>103</v>
@@ -4277,7 +4341,8 @@
         <v>76</v>
       </c>
       <c r="B34">
-        <v>0.92500000000000004</v>
+        <f>Wide!B34</f>
+        <v>0.97958999999999996</v>
       </c>
       <c r="C34" t="s">
         <v>103</v>
@@ -4288,7 +4353,8 @@
         <v>77</v>
       </c>
       <c r="B35">
-        <v>0.9</v>
+        <f>Wide!B35</f>
+        <v>0.93877999999999995</v>
       </c>
       <c r="C35" t="s">
         <v>103</v>
@@ -4299,7 +4365,8 @@
         <v>15</v>
       </c>
       <c r="B36">
-        <v>0.9</v>
+        <f>Wide!B36</f>
+        <v>0.94443999999999995</v>
       </c>
       <c r="C36" t="s">
         <v>103</v>
@@ -4310,6 +4377,7 @@
         <v>17</v>
       </c>
       <c r="B37">
+        <f>Wide!B37</f>
         <v>1</v>
       </c>
       <c r="C37" t="s">
@@ -4321,7 +4389,8 @@
         <v>16</v>
       </c>
       <c r="B38">
-        <v>0.9</v>
+        <f>Wide!B38</f>
+        <v>0.94443999999999995</v>
       </c>
       <c r="C38" t="s">
         <v>103</v>
@@ -4332,7 +4401,8 @@
         <v>19</v>
       </c>
       <c r="B39">
-        <v>0.13333</v>
+        <f>Wide!B39</f>
+        <v>0.22222</v>
       </c>
       <c r="C39" t="s">
         <v>103</v>
@@ -4343,7 +4413,8 @@
         <v>18</v>
       </c>
       <c r="B40">
-        <v>0.5</v>
+        <f>Wide!B40</f>
+        <v>0.61111000000000004</v>
       </c>
       <c r="C40" t="s">
         <v>103</v>
@@ -4354,7 +4425,8 @@
         <v>20</v>
       </c>
       <c r="B41">
-        <v>0.63636000000000004</v>
+        <f>Wide!B41</f>
+        <v>0.77778000000000003</v>
       </c>
       <c r="C41" t="s">
         <v>103</v>
@@ -4365,7 +4437,8 @@
         <v>90</v>
       </c>
       <c r="B42">
-        <v>0.98995</v>
+        <f>Wide!B42</f>
+        <v>0.99414999999999998</v>
       </c>
       <c r="C42" t="s">
         <v>103</v>
@@ -4376,7 +4449,8 @@
         <v>89</v>
       </c>
       <c r="B43">
-        <v>0.98995</v>
+        <f>Wide!B43</f>
+        <v>0.99414999999999998</v>
       </c>
       <c r="C43" t="s">
         <v>103</v>
@@ -4387,6 +4461,7 @@
         <v>93</v>
       </c>
       <c r="B44">
+        <f>Wide!B44</f>
         <v>1</v>
       </c>
       <c r="C44" t="s">
@@ -4398,6 +4473,7 @@
         <v>94</v>
       </c>
       <c r="B45">
+        <f>Wide!B45</f>
         <v>0.875</v>
       </c>
       <c r="C45" t="s">
@@ -4409,7 +4485,8 @@
         <v>91</v>
       </c>
       <c r="B46">
-        <v>0.98995</v>
+        <f>Wide!B46</f>
+        <v>0.99414999999999998</v>
       </c>
       <c r="C46" t="s">
         <v>103</v>
@@ -4420,7 +4497,8 @@
         <v>96</v>
       </c>
       <c r="B47">
-        <v>0.5</v>
+        <f>Wide!B47</f>
+        <v>0.66666999999999998</v>
       </c>
       <c r="C47" t="s">
         <v>103</v>
@@ -4431,6 +4509,7 @@
         <v>95</v>
       </c>
       <c r="B48">
+        <f>Wide!B48</f>
         <v>1</v>
       </c>
       <c r="C48" t="s">
@@ -4442,7 +4521,8 @@
         <v>92</v>
       </c>
       <c r="B49">
-        <v>0.98492000000000002</v>
+        <f>Wide!B49</f>
+        <v>0.98829999999999996</v>
       </c>
       <c r="C49" t="s">
         <v>103</v>
@@ -4453,6 +4533,7 @@
         <v>99</v>
       </c>
       <c r="B50">
+        <f>Wide!B50</f>
         <v>1</v>
       </c>
       <c r="C50" t="s">
@@ -4464,7 +4545,8 @@
         <v>64</v>
       </c>
       <c r="B51">
-        <v>0.77778000000000003</v>
+        <f>Wide!B51</f>
+        <v>0.85714000000000001</v>
       </c>
       <c r="C51" t="s">
         <v>103</v>
@@ -4475,7 +4557,8 @@
         <v>65</v>
       </c>
       <c r="B52">
-        <v>0.66666999999999998</v>
+        <f>Wide!B52</f>
+        <v>0.85714000000000001</v>
       </c>
       <c r="C52" t="s">
         <v>103</v>
@@ -4486,7 +4569,8 @@
         <v>63</v>
       </c>
       <c r="B53">
-        <v>0.77778000000000003</v>
+        <f>Wide!B53</f>
+        <v>0.85714000000000001</v>
       </c>
       <c r="C53" t="s">
         <v>103</v>
@@ -4497,7 +4581,8 @@
         <v>11</v>
       </c>
       <c r="B54">
-        <v>9.0910000000000005E-2</v>
+        <f>Wide!B54</f>
+        <v>0.125</v>
       </c>
       <c r="C54" t="s">
         <v>103</v>
@@ -4508,7 +4593,8 @@
         <v>13</v>
       </c>
       <c r="B55">
-        <v>0.88888999999999996</v>
+        <f>Wide!B55</f>
+        <v>0.91666999999999998</v>
       </c>
       <c r="C55" t="s">
         <v>103</v>
@@ -4519,6 +4605,7 @@
         <v>9</v>
       </c>
       <c r="B56">
+        <f>Wide!B56</f>
         <v>1</v>
       </c>
       <c r="C56" t="s">
@@ -4530,6 +4617,7 @@
         <v>10</v>
       </c>
       <c r="B57">
+        <f>Wide!B57</f>
         <v>1</v>
       </c>
       <c r="C57" t="s">
@@ -4541,6 +4629,7 @@
         <v>14</v>
       </c>
       <c r="B58">
+        <f>Wide!B58</f>
         <v>1</v>
       </c>
       <c r="C58" t="s">
@@ -4552,7 +4641,8 @@
         <v>12</v>
       </c>
       <c r="B59">
-        <v>3.7039999999999997E-2</v>
+        <f>Wide!B59</f>
+        <v>4.1669999999999999E-2</v>
       </c>
       <c r="C59" t="s">
         <v>103</v>
@@ -4563,7 +4653,8 @@
         <v>8</v>
       </c>
       <c r="B60">
-        <v>0.93181999999999998</v>
+        <f>Wide!B60</f>
+        <v>0.96875</v>
       </c>
       <c r="C60" t="s">
         <v>103</v>
@@ -4574,7 +4665,8 @@
         <v>60</v>
       </c>
       <c r="B61">
-        <v>0.41176000000000001</v>
+        <f>Wide!B61</f>
+        <v>0.85714000000000001</v>
       </c>
       <c r="C61" t="s">
         <v>103</v>
@@ -4585,7 +4677,8 @@
         <v>62</v>
       </c>
       <c r="B62">
-        <v>0.23529</v>
+        <f>Wide!B62</f>
+        <v>0.57142999999999999</v>
       </c>
       <c r="C62" t="s">
         <v>103</v>
@@ -4596,6 +4689,7 @@
         <v>61</v>
       </c>
       <c r="B63">
+        <f>Wide!B63</f>
         <v>1</v>
       </c>
       <c r="C63" t="s">
@@ -4607,6 +4701,7 @@
         <v>59</v>
       </c>
       <c r="B64">
+        <f>Wide!B64</f>
         <v>1</v>
       </c>
       <c r="C64" t="s">
@@ -4618,6 +4713,7 @@
         <v>2</v>
       </c>
       <c r="B65">
+        <f>Wide!B65</f>
         <v>1</v>
       </c>
       <c r="C65" t="s">
@@ -4629,7 +4725,8 @@
         <v>1</v>
       </c>
       <c r="B66">
-        <v>0.5</v>
+        <f>Wide!B66</f>
+        <v>0.66666999999999998</v>
       </c>
       <c r="C66" t="s">
         <v>103</v>
@@ -4640,7 +4737,8 @@
         <v>3</v>
       </c>
       <c r="B67">
-        <v>0.5</v>
+        <f>Wide!B67</f>
+        <v>0.66666999999999998</v>
       </c>
       <c r="C67" t="s">
         <v>103</v>
@@ -4651,7 +4749,8 @@
         <v>4</v>
       </c>
       <c r="B68">
-        <v>0.25</v>
+        <f>Wide!B68</f>
+        <v>0.33333000000000002</v>
       </c>
       <c r="C68" t="s">
         <v>103</v>
@@ -4662,6 +4761,7 @@
         <v>21</v>
       </c>
       <c r="B69">
+        <f>Wide!B69</f>
         <v>0.75</v>
       </c>
       <c r="C69" t="s">
@@ -4673,6 +4773,7 @@
         <v>23</v>
       </c>
       <c r="B70">
+        <f>Wide!B70</f>
         <v>0.75</v>
       </c>
       <c r="C70" t="s">
@@ -4684,6 +4785,7 @@
         <v>24</v>
       </c>
       <c r="B71">
+        <f>Wide!B71</f>
         <v>0.75</v>
       </c>
       <c r="C71" t="s">
@@ -4695,6 +4797,7 @@
         <v>22</v>
       </c>
       <c r="B72">
+        <f>Wide!B72</f>
         <v>0.75</v>
       </c>
       <c r="C72" t="s">
@@ -4706,7 +4809,8 @@
         <v>40</v>
       </c>
       <c r="B73">
-        <v>0.95555999999999996</v>
+        <f>Wide!B73</f>
+        <v>0.97619</v>
       </c>
       <c r="C73" t="s">
         <v>103</v>
@@ -4717,7 +4821,8 @@
         <v>41</v>
       </c>
       <c r="B74">
-        <v>0.95555999999999996</v>
+        <f>Wide!B74</f>
+        <v>0.97619</v>
       </c>
       <c r="C74" t="s">
         <v>103</v>
@@ -4728,6 +4833,7 @@
         <v>45</v>
       </c>
       <c r="B75">
+        <f>Wide!B75</f>
         <v>1</v>
       </c>
       <c r="C75" t="s">
@@ -4739,6 +4845,7 @@
         <v>42</v>
       </c>
       <c r="B76">
+        <f>Wide!B76</f>
         <v>1</v>
       </c>
       <c r="C76" t="s">
@@ -4750,7 +4857,8 @@
         <v>43</v>
       </c>
       <c r="B77">
-        <v>0.82221999999999995</v>
+        <f>Wide!B77</f>
+        <v>0.97619</v>
       </c>
       <c r="C77" t="s">
         <v>103</v>
@@ -4761,7 +4869,8 @@
         <v>46</v>
       </c>
       <c r="B78">
-        <v>0.45713999999999999</v>
+        <f>Wide!B78</f>
+        <v>0.64705999999999997</v>
       </c>
       <c r="C78" t="s">
         <v>103</v>
@@ -4772,7 +4881,8 @@
         <v>48</v>
       </c>
       <c r="B79">
-        <v>0.91666999999999998</v>
+        <f>Wide!B79</f>
+        <v>0.90908999999999995</v>
       </c>
       <c r="C79" t="s">
         <v>103</v>
@@ -4783,7 +4893,8 @@
         <v>49</v>
       </c>
       <c r="B80">
-        <v>0.75</v>
+        <f>Wide!B80</f>
+        <v>0.85714000000000001</v>
       </c>
       <c r="C80" t="s">
         <v>103</v>
@@ -4794,6 +4905,7 @@
         <v>47</v>
       </c>
       <c r="B81">
+        <f>Wide!B81</f>
         <v>1</v>
       </c>
       <c r="C81" t="s">
@@ -4805,7 +4917,8 @@
         <v>44</v>
       </c>
       <c r="B82">
-        <v>0.94443999999999995</v>
+        <f>Wide!B82</f>
+        <v>0.42857000000000001</v>
       </c>
       <c r="C82" t="s">
         <v>103</v>
@@ -4816,7 +4929,8 @@
         <v>51</v>
       </c>
       <c r="B83">
-        <v>0.94030000000000002</v>
+        <f>Wide!B83</f>
+        <v>0.97872000000000003</v>
       </c>
       <c r="C83" t="s">
         <v>103</v>
@@ -4827,7 +4941,8 @@
         <v>52</v>
       </c>
       <c r="B84">
-        <v>0.94030000000000002</v>
+        <f>Wide!B84</f>
+        <v>0.97872000000000003</v>
       </c>
       <c r="C84" t="s">
         <v>103</v>
@@ -4838,7 +4953,8 @@
         <v>55</v>
       </c>
       <c r="B85">
-        <v>0.89551999999999998</v>
+        <f>Wide!B85</f>
+        <v>0.93616999999999995</v>
       </c>
       <c r="C85" t="s">
         <v>103</v>
@@ -4849,6 +4965,7 @@
         <v>58</v>
       </c>
       <c r="B86">
+        <f>Wide!B86</f>
         <v>1</v>
       </c>
       <c r="C86" t="s">
@@ -4860,7 +4977,8 @@
         <v>50</v>
       </c>
       <c r="B87">
-        <v>0.94030000000000002</v>
+        <f>Wide!B87</f>
+        <v>0.97872000000000003</v>
       </c>
       <c r="C87" t="s">
         <v>103</v>
@@ -4871,7 +4989,8 @@
         <v>56</v>
       </c>
       <c r="B88">
-        <v>0.74626999999999999</v>
+        <f>Wide!B88</f>
+        <v>0.82979000000000003</v>
       </c>
       <c r="C88" t="s">
         <v>103</v>
@@ -4882,7 +5001,8 @@
         <v>54</v>
       </c>
       <c r="B89">
-        <v>0.88060000000000005</v>
+        <f>Wide!B89</f>
+        <v>0.95745000000000002</v>
       </c>
       <c r="C89" t="s">
         <v>103</v>
@@ -4893,6 +5013,7 @@
         <v>53</v>
       </c>
       <c r="B90">
+        <f>Wide!B90</f>
         <v>1</v>
       </c>
       <c r="C90" t="s">
@@ -4904,7 +5025,8 @@
         <v>57</v>
       </c>
       <c r="B91">
-        <v>0.31342999999999999</v>
+        <f>Wide!B91</f>
+        <v>0.31914999999999999</v>
       </c>
       <c r="C91" t="s">
         <v>103</v>
@@ -4915,6 +5037,7 @@
         <v>33</v>
       </c>
       <c r="B92">
+        <f>Wide!B92</f>
         <v>0.875</v>
       </c>
       <c r="C92" t="s">
@@ -4926,6 +5049,7 @@
         <v>34</v>
       </c>
       <c r="B93">
+        <f>Wide!B93</f>
         <v>0.875</v>
       </c>
       <c r="C93" t="s">
@@ -4937,7 +5061,8 @@
         <v>70</v>
       </c>
       <c r="B94">
-        <v>0.88888999999999996</v>
+        <f>Wide!B94</f>
+        <v>0.875</v>
       </c>
       <c r="C94" t="s">
         <v>103</v>
@@ -4948,7 +5073,8 @@
         <v>69</v>
       </c>
       <c r="B95">
-        <v>0.77778000000000003</v>
+        <f>Wide!B95</f>
+        <v>0.75</v>
       </c>
       <c r="C95" t="s">
         <v>103</v>
@@ -4959,7 +5085,8 @@
         <v>68</v>
       </c>
       <c r="B96">
-        <v>0.77778000000000003</v>
+        <f>Wide!B96</f>
+        <v>0.75</v>
       </c>
       <c r="C96" t="s">
         <v>103</v>
@@ -4970,7 +5097,8 @@
         <v>37</v>
       </c>
       <c r="B97">
-        <v>0.8</v>
+        <f>Wide!B97</f>
+        <v>0.75</v>
       </c>
       <c r="C97" t="s">
         <v>103</v>
@@ -4981,7 +5109,8 @@
         <v>38</v>
       </c>
       <c r="B98">
-        <v>0.8</v>
+        <f>Wide!B98</f>
+        <v>0.75</v>
       </c>
       <c r="C98" t="s">
         <v>103</v>
@@ -4992,6 +5121,7 @@
         <v>98</v>
       </c>
       <c r="B99">
+        <f>Wide!B99</f>
         <v>1</v>
       </c>
       <c r="C99" t="s">
@@ -5003,6 +5133,7 @@
         <v>97</v>
       </c>
       <c r="B100">
+        <f>Wide!B100</f>
         <v>1</v>
       </c>
       <c r="C100" t="s">
@@ -5014,6 +5145,7 @@
         <v>39</v>
       </c>
       <c r="B101">
+        <f>Wide!B101</f>
         <v>0.5</v>
       </c>
       <c r="C101" t="s">
@@ -5025,6 +5157,7 @@
         <v>29</v>
       </c>
       <c r="B102">
+        <f>Wide!C2</f>
         <v>1</v>
       </c>
       <c r="C102" t="s">
@@ -5036,7 +5169,8 @@
         <v>83</v>
       </c>
       <c r="B103">
-        <v>0.66666999999999998</v>
+        <f>Wide!C3</f>
+        <v>0.69443999999999995</v>
       </c>
       <c r="C103" t="s">
         <v>105</v>
@@ -5047,7 +5181,8 @@
         <v>84</v>
       </c>
       <c r="B104">
-        <v>0.75309000000000004</v>
+        <f>Wide!C4</f>
+        <v>0.80556000000000005</v>
       </c>
       <c r="C104" t="s">
         <v>105</v>
@@ -5058,7 +5193,8 @@
         <v>85</v>
       </c>
       <c r="B105">
-        <v>0.75309000000000004</v>
+        <f>Wide!C5</f>
+        <v>0.88888999999999996</v>
       </c>
       <c r="C105" t="s">
         <v>105</v>
@@ -5069,7 +5205,8 @@
         <v>86</v>
       </c>
       <c r="B106">
-        <v>0.86419999999999997</v>
+        <f>Wide!C6</f>
+        <v>0.97221999999999997</v>
       </c>
       <c r="C106" t="s">
         <v>105</v>
@@ -5080,6 +5217,7 @@
         <v>87</v>
       </c>
       <c r="B107">
+        <f>Wide!C7</f>
         <v>0.66666999999999998</v>
       </c>
       <c r="C107" t="s">
@@ -5091,7 +5229,8 @@
         <v>88</v>
       </c>
       <c r="B108">
-        <v>0.90908999999999995</v>
+        <f>Wide!C8</f>
+        <v>0.625</v>
       </c>
       <c r="C108" t="s">
         <v>105</v>
@@ -5102,6 +5241,7 @@
         <v>25</v>
       </c>
       <c r="B109">
+        <f>Wide!C9</f>
         <v>0.75</v>
       </c>
       <c r="C109" t="s">
@@ -5113,6 +5253,7 @@
         <v>27</v>
       </c>
       <c r="B110">
+        <f>Wide!C10</f>
         <v>0.75</v>
       </c>
       <c r="C110" t="s">
@@ -5124,6 +5265,7 @@
         <v>28</v>
       </c>
       <c r="B111">
+        <f>Wide!C11</f>
         <v>1</v>
       </c>
       <c r="C111" t="s">
@@ -5135,6 +5277,7 @@
         <v>26</v>
       </c>
       <c r="B112">
+        <f>Wide!C12</f>
         <v>0.75</v>
       </c>
       <c r="C112" t="s">
@@ -5146,7 +5289,8 @@
         <v>36</v>
       </c>
       <c r="B113">
-        <v>0.4</v>
+        <f>Wide!C13</f>
+        <v>0.66666999999999998</v>
       </c>
       <c r="C113" t="s">
         <v>105</v>
@@ -5157,7 +5301,8 @@
         <v>35</v>
       </c>
       <c r="B114">
-        <v>0.7</v>
+        <f>Wide!C14</f>
+        <v>0.83333000000000002</v>
       </c>
       <c r="C114" t="s">
         <v>105</v>
@@ -5168,6 +5313,7 @@
         <v>5</v>
       </c>
       <c r="B115">
+        <f>Wide!C15</f>
         <v>1</v>
       </c>
       <c r="C115" t="s">
@@ -5179,6 +5325,7 @@
         <v>6</v>
       </c>
       <c r="B116">
+        <f>Wide!C16</f>
         <v>1</v>
       </c>
       <c r="C116" t="s">
@@ -5190,7 +5337,8 @@
         <v>7</v>
       </c>
       <c r="B117">
-        <v>6.8180000000000004E-2</v>
+        <f>Wide!C17</f>
+        <v>0.15789</v>
       </c>
       <c r="C117" t="s">
         <v>105</v>
@@ -5201,6 +5349,7 @@
         <v>31</v>
       </c>
       <c r="B118">
+        <f>Wide!C18</f>
         <v>0</v>
       </c>
       <c r="C118" t="s">
@@ -5212,6 +5361,7 @@
         <v>32</v>
       </c>
       <c r="B119">
+        <f>Wide!C19</f>
         <v>0</v>
       </c>
       <c r="C119" t="s">
@@ -5223,7 +5373,8 @@
         <v>30</v>
       </c>
       <c r="B120">
-        <v>0.88888999999999996</v>
+        <f>Wide!C20</f>
+        <v>1</v>
       </c>
       <c r="C120" t="s">
         <v>105</v>
@@ -5234,6 +5385,7 @@
         <v>100</v>
       </c>
       <c r="B121">
+        <f>Wide!C21</f>
         <v>1</v>
       </c>
       <c r="C121" t="s">
@@ -5245,6 +5397,7 @@
         <v>67</v>
       </c>
       <c r="B122">
+        <f>Wide!C22</f>
         <v>1</v>
       </c>
       <c r="C122" t="s">
@@ -5256,6 +5409,7 @@
         <v>66</v>
       </c>
       <c r="B123">
+        <f>Wide!C23</f>
         <v>1</v>
       </c>
       <c r="C123" t="s">
@@ -5267,7 +5421,8 @@
         <v>78</v>
       </c>
       <c r="B124">
-        <v>0.57499999999999996</v>
+        <f>Wide!C24</f>
+        <v>0.69564999999999999</v>
       </c>
       <c r="C124" t="s">
         <v>105</v>
@@ -5278,7 +5433,8 @@
         <v>79</v>
       </c>
       <c r="B125">
-        <v>0.45</v>
+        <f>Wide!C25</f>
+        <v>0.30435000000000001</v>
       </c>
       <c r="C125" t="s">
         <v>105</v>
@@ -5289,7 +5445,8 @@
         <v>71</v>
       </c>
       <c r="B126">
-        <v>1</v>
+        <f>Wide!C26</f>
+        <v>0.80435000000000001</v>
       </c>
       <c r="C126" t="s">
         <v>105</v>
@@ -5300,7 +5457,8 @@
         <v>72</v>
       </c>
       <c r="B127">
-        <v>1</v>
+        <f>Wide!C27</f>
+        <v>0.84782999999999997</v>
       </c>
       <c r="C127" t="s">
         <v>105</v>
@@ -5311,6 +5469,7 @@
         <v>81</v>
       </c>
       <c r="B128">
+        <f>Wide!C28</f>
         <v>1</v>
       </c>
       <c r="C128" t="s">
@@ -5322,7 +5481,8 @@
         <v>74</v>
       </c>
       <c r="B129">
-        <v>0.13750000000000001</v>
+        <f>Wide!C29</f>
+        <v>0.19564999999999999</v>
       </c>
       <c r="C129" t="s">
         <v>105</v>
@@ -5333,7 +5493,8 @@
         <v>73</v>
       </c>
       <c r="B130">
-        <v>0.5625</v>
+        <f>Wide!C30</f>
+        <v>0.58696000000000004</v>
       </c>
       <c r="C130" t="s">
         <v>105</v>
@@ -5344,7 +5505,8 @@
         <v>75</v>
       </c>
       <c r="B131">
-        <v>0.3</v>
+        <f>Wide!C31</f>
+        <v>0.36957000000000001</v>
       </c>
       <c r="C131" t="s">
         <v>105</v>
@@ -5355,7 +5517,8 @@
         <v>82</v>
       </c>
       <c r="B132">
-        <v>0.83333000000000002</v>
+        <f>Wide!C32</f>
+        <v>0.93332999999999999</v>
       </c>
       <c r="C132" t="s">
         <v>105</v>
@@ -5366,7 +5529,8 @@
         <v>80</v>
       </c>
       <c r="B133">
-        <v>6.25E-2</v>
+        <f>Wide!C33</f>
+        <v>6.522E-2</v>
       </c>
       <c r="C133" t="s">
         <v>105</v>
@@ -5377,7 +5541,8 @@
         <v>76</v>
       </c>
       <c r="B134">
-        <v>0.9375</v>
+        <f>Wide!C34</f>
+        <v>0.97826000000000002</v>
       </c>
       <c r="C134" t="s">
         <v>105</v>
@@ -5388,7 +5553,8 @@
         <v>77</v>
       </c>
       <c r="B135">
-        <v>0.9</v>
+        <f>Wide!C35</f>
+        <v>0.80435000000000001</v>
       </c>
       <c r="C135" t="s">
         <v>105</v>
@@ -5399,7 +5565,8 @@
         <v>15</v>
       </c>
       <c r="B136">
-        <v>0.86667000000000005</v>
+        <f>Wide!C36</f>
+        <v>0.94118000000000002</v>
       </c>
       <c r="C136" t="s">
         <v>105</v>
@@ -5410,6 +5577,7 @@
         <v>17</v>
       </c>
       <c r="B137">
+        <f>Wide!C37</f>
         <v>1</v>
       </c>
       <c r="C137" t="s">
@@ -5421,6 +5589,7 @@
         <v>16</v>
       </c>
       <c r="B138">
+        <f>Wide!C38</f>
         <v>1</v>
       </c>
       <c r="C138" t="s">
@@ -5432,7 +5601,8 @@
         <v>19</v>
       </c>
       <c r="B139">
-        <v>0.1</v>
+        <f>Wide!C39</f>
+        <v>0.17646999999999999</v>
       </c>
       <c r="C139" t="s">
         <v>105</v>
@@ -5443,7 +5613,8 @@
         <v>18</v>
       </c>
       <c r="B140">
-        <v>0.7</v>
+        <f>Wide!C40</f>
+        <v>0.82352999999999998</v>
       </c>
       <c r="C140" t="s">
         <v>105</v>
@@ -5454,7 +5625,8 @@
         <v>20</v>
       </c>
       <c r="B141">
-        <v>0.36364000000000002</v>
+        <f>Wide!C41</f>
+        <v>0.5</v>
       </c>
       <c r="C141" t="s">
         <v>105</v>
@@ -5465,7 +5637,8 @@
         <v>90</v>
       </c>
       <c r="B142">
-        <v>0.98995</v>
+        <f>Wide!C42</f>
+        <v>0.97248000000000001</v>
       </c>
       <c r="C142" t="s">
         <v>105</v>
@@ -5476,6 +5649,7 @@
         <v>89</v>
       </c>
       <c r="B143">
+        <f>Wide!C43</f>
         <v>1</v>
       </c>
       <c r="C143" t="s">
@@ -5487,7 +5661,8 @@
         <v>93</v>
       </c>
       <c r="B144">
-        <v>0.88083</v>
+        <f>Wide!C44</f>
+        <v>0.91429000000000005</v>
       </c>
       <c r="C144" t="s">
         <v>105</v>
@@ -5498,6 +5673,7 @@
         <v>94</v>
       </c>
       <c r="B145">
+        <f>Wide!C45</f>
         <v>0.8</v>
       </c>
       <c r="C145" t="s">
@@ -5509,6 +5685,7 @@
         <v>91</v>
       </c>
       <c r="B146">
+        <f>Wide!C46</f>
         <v>1</v>
       </c>
       <c r="C146" t="s">
@@ -5520,7 +5697,8 @@
         <v>96</v>
       </c>
       <c r="B147">
-        <v>0.25</v>
+        <f>Wide!C47</f>
+        <v>0.33333000000000002</v>
       </c>
       <c r="C147" t="s">
         <v>105</v>
@@ -5531,6 +5709,7 @@
         <v>95</v>
       </c>
       <c r="B148">
+        <f>Wide!C48</f>
         <v>1</v>
       </c>
       <c r="C148" t="s">
@@ -5542,7 +5721,8 @@
         <v>92</v>
       </c>
       <c r="B149">
-        <v>0.98492000000000002</v>
+        <f>Wide!C49</f>
+        <v>0.98165000000000002</v>
       </c>
       <c r="C149" t="s">
         <v>105</v>
@@ -5553,6 +5733,7 @@
         <v>99</v>
       </c>
       <c r="B150">
+        <f>Wide!C50</f>
         <v>1</v>
       </c>
       <c r="C150" t="s">
@@ -5564,7 +5745,8 @@
         <v>64</v>
       </c>
       <c r="B151">
-        <v>0.88888999999999996</v>
+        <f>Wide!C51</f>
+        <v>1</v>
       </c>
       <c r="C151" t="s">
         <v>105</v>
@@ -5575,6 +5757,7 @@
         <v>65</v>
       </c>
       <c r="B152">
+        <f>Wide!C52</f>
         <v>0</v>
       </c>
       <c r="C152" t="s">
@@ -5586,7 +5769,8 @@
         <v>63</v>
       </c>
       <c r="B153">
-        <v>0.88888999999999996</v>
+        <f>Wide!C53</f>
+        <v>1</v>
       </c>
       <c r="C153" t="s">
         <v>105</v>
@@ -5597,7 +5781,8 @@
         <v>11</v>
       </c>
       <c r="B154">
-        <v>4.5449999999999997E-2</v>
+        <f>Wide!C54</f>
+        <v>6.6669999999999993E-2</v>
       </c>
       <c r="C154" t="s">
         <v>105</v>
@@ -5608,7 +5793,8 @@
         <v>13</v>
       </c>
       <c r="B155">
-        <v>0.88461999999999996</v>
+        <f>Wide!C55</f>
+        <v>0.90908999999999995</v>
       </c>
       <c r="C155" t="s">
         <v>105</v>
@@ -5619,6 +5805,7 @@
         <v>9</v>
       </c>
       <c r="B156">
+        <f>Wide!C56</f>
         <v>1</v>
       </c>
       <c r="C156" t="s">
@@ -5630,7 +5817,8 @@
         <v>10</v>
       </c>
       <c r="B157">
-        <v>0.79544999999999999</v>
+        <f>Wide!C57</f>
+        <v>0.93332999999999999</v>
       </c>
       <c r="C157" t="s">
         <v>105</v>
@@ -5641,6 +5829,7 @@
         <v>14</v>
       </c>
       <c r="B158">
+        <f>Wide!C58</f>
         <v>1</v>
       </c>
       <c r="C158" t="s">
@@ -5652,7 +5841,8 @@
         <v>12</v>
       </c>
       <c r="B159">
-        <v>3.8460000000000001E-2</v>
+        <f>Wide!C59</f>
+        <v>4.5449999999999997E-2</v>
       </c>
       <c r="C159" t="s">
         <v>105</v>
@@ -5663,7 +5853,8 @@
         <v>8</v>
       </c>
       <c r="B160">
-        <v>0.93181999999999998</v>
+        <f>Wide!C60</f>
+        <v>0.9</v>
       </c>
       <c r="C160" t="s">
         <v>105</v>
@@ -5674,7 +5865,8 @@
         <v>60</v>
       </c>
       <c r="B161">
-        <v>0.47059000000000001</v>
+        <f>Wide!C61</f>
+        <v>1</v>
       </c>
       <c r="C161" t="s">
         <v>105</v>
@@ -5685,6 +5877,7 @@
         <v>62</v>
       </c>
       <c r="B162">
+        <f>Wide!C62</f>
         <v>0</v>
       </c>
       <c r="C162" t="s">
@@ -5696,7 +5889,8 @@
         <v>61</v>
       </c>
       <c r="B163">
-        <v>0.11765</v>
+        <f>Wide!C63</f>
+        <v>0.28571000000000002</v>
       </c>
       <c r="C163" t="s">
         <v>105</v>
@@ -5707,7 +5901,8 @@
         <v>59</v>
       </c>
       <c r="B164">
-        <v>0.41176000000000001</v>
+        <f>Wide!C64</f>
+        <v>1</v>
       </c>
       <c r="C164" t="s">
         <v>105</v>
@@ -5718,6 +5913,7 @@
         <v>2</v>
       </c>
       <c r="B165">
+        <f>Wide!C65</f>
         <v>1</v>
       </c>
       <c r="C165" t="s">
@@ -5729,6 +5925,7 @@
         <v>1</v>
       </c>
       <c r="B166">
+        <f>Wide!C66</f>
         <v>1</v>
       </c>
       <c r="C166" t="s">
@@ -5740,6 +5937,7 @@
         <v>3</v>
       </c>
       <c r="B167">
+        <f>Wide!C67</f>
         <v>1</v>
       </c>
       <c r="C167" t="s">
@@ -5751,7 +5949,8 @@
         <v>4</v>
       </c>
       <c r="B168">
-        <v>0.25</v>
+        <f>Wide!C68</f>
+        <v>0.33333000000000002</v>
       </c>
       <c r="C168" t="s">
         <v>105</v>
@@ -5762,6 +5961,7 @@
         <v>21</v>
       </c>
       <c r="B169">
+        <f>Wide!C69</f>
         <v>0.75</v>
       </c>
       <c r="C169" t="s">
@@ -5773,6 +5973,7 @@
         <v>23</v>
       </c>
       <c r="B170">
+        <f>Wide!C70</f>
         <v>0.75</v>
       </c>
       <c r="C170" t="s">
@@ -5784,6 +5985,7 @@
         <v>24</v>
       </c>
       <c r="B171">
+        <f>Wide!C71</f>
         <v>1</v>
       </c>
       <c r="C171" t="s">
@@ -5795,6 +5997,7 @@
         <v>22</v>
       </c>
       <c r="B172">
+        <f>Wide!C72</f>
         <v>0.75</v>
       </c>
       <c r="C172" t="s">
@@ -5806,7 +6009,8 @@
         <v>40</v>
       </c>
       <c r="B173">
-        <v>0.98889000000000005</v>
+        <f>Wide!C73</f>
+        <v>0.82857000000000003</v>
       </c>
       <c r="C173" t="s">
         <v>105</v>
@@ -5817,7 +6021,8 @@
         <v>41</v>
       </c>
       <c r="B174">
-        <v>0.98889000000000005</v>
+        <f>Wide!C74</f>
+        <v>0.82857000000000003</v>
       </c>
       <c r="C174" t="s">
         <v>105</v>
@@ -5828,6 +6033,7 @@
         <v>45</v>
       </c>
       <c r="B175">
+        <f>Wide!C75</f>
         <v>1</v>
       </c>
       <c r="C175" t="s">
@@ -5839,6 +6045,7 @@
         <v>42</v>
       </c>
       <c r="B176">
+        <f>Wide!C76</f>
         <v>1</v>
       </c>
       <c r="C176" t="s">
@@ -5850,7 +6057,8 @@
         <v>43</v>
       </c>
       <c r="B177">
-        <v>0.84443999999999997</v>
+        <f>Wide!C77</f>
+        <v>0.57142999999999999</v>
       </c>
       <c r="C177" t="s">
         <v>105</v>
@@ -5861,7 +6069,8 @@
         <v>46</v>
       </c>
       <c r="B178">
-        <v>0.14285999999999999</v>
+        <f>Wide!C78</f>
+        <v>0.33333000000000002</v>
       </c>
       <c r="C178" t="s">
         <v>105</v>
@@ -5872,7 +6081,8 @@
         <v>48</v>
       </c>
       <c r="B179">
-        <v>0.58333000000000002</v>
+        <f>Wide!C79</f>
+        <v>0.625</v>
       </c>
       <c r="C179" t="s">
         <v>105</v>
@@ -5883,6 +6093,7 @@
         <v>49</v>
       </c>
       <c r="B180">
+        <f>Wide!C80</f>
         <v>0</v>
       </c>
       <c r="C180" t="s">
@@ -5894,6 +6105,7 @@
         <v>47</v>
       </c>
       <c r="B181">
+        <f>Wide!C81</f>
         <v>1</v>
       </c>
       <c r="C181" t="s">
@@ -5905,7 +6117,8 @@
         <v>44</v>
       </c>
       <c r="B182">
-        <v>0.18889</v>
+        <f>Wide!C82</f>
+        <v>0.28571000000000002</v>
       </c>
       <c r="C182" t="s">
         <v>105</v>
@@ -5916,7 +6129,8 @@
         <v>51</v>
       </c>
       <c r="B183">
-        <v>0.98507</v>
+        <f>Wide!C83</f>
+        <v>1</v>
       </c>
       <c r="C183" t="s">
         <v>105</v>
@@ -5927,7 +6141,8 @@
         <v>52</v>
       </c>
       <c r="B184">
-        <v>0.10448</v>
+        <f>Wide!C84</f>
+        <v>7.4999999999999997E-2</v>
       </c>
       <c r="C184" t="s">
         <v>105</v>
@@ -5938,7 +6153,8 @@
         <v>55</v>
       </c>
       <c r="B185">
-        <v>0.49253999999999998</v>
+        <f>Wide!C85</f>
+        <v>0.52500000000000002</v>
       </c>
       <c r="C185" t="s">
         <v>105</v>
@@ -5949,6 +6165,7 @@
         <v>58</v>
       </c>
       <c r="B186">
+        <f>Wide!C86</f>
         <v>1</v>
       </c>
       <c r="C186" t="s">
@@ -5960,7 +6177,8 @@
         <v>50</v>
       </c>
       <c r="B187">
-        <v>0.95521999999999996</v>
+        <f>Wide!C87</f>
+        <v>1</v>
       </c>
       <c r="C187" t="s">
         <v>105</v>
@@ -5971,7 +6189,8 @@
         <v>56</v>
       </c>
       <c r="B188">
-        <v>0.71641999999999995</v>
+        <f>Wide!C88</f>
+        <v>0.8</v>
       </c>
       <c r="C188" t="s">
         <v>105</v>
@@ -5982,7 +6201,8 @@
         <v>54</v>
       </c>
       <c r="B189">
-        <v>0.55223999999999995</v>
+        <f>Wide!C89</f>
+        <v>0.67500000000000004</v>
       </c>
       <c r="C189" t="s">
         <v>105</v>
@@ -5993,6 +6213,7 @@
         <v>53</v>
       </c>
       <c r="B190">
+        <f>Wide!C90</f>
         <v>1</v>
       </c>
       <c r="C190" t="s">
@@ -6004,7 +6225,8 @@
         <v>57</v>
       </c>
       <c r="B191">
-        <v>0.10448</v>
+        <f>Wide!C91</f>
+        <v>7.4999999999999997E-2</v>
       </c>
       <c r="C191" t="s">
         <v>105</v>
@@ -6015,7 +6237,8 @@
         <v>33</v>
       </c>
       <c r="B192">
-        <v>0.875</v>
+        <f>Wide!C92</f>
+        <v>0.83333000000000002</v>
       </c>
       <c r="C192" t="s">
         <v>105</v>
@@ -6026,7 +6249,8 @@
         <v>34</v>
       </c>
       <c r="B193">
-        <v>0.75</v>
+        <f>Wide!C93</f>
+        <v>0.83333000000000002</v>
       </c>
       <c r="C193" t="s">
         <v>105</v>
@@ -6037,6 +6261,7 @@
         <v>70</v>
       </c>
       <c r="B194">
+        <f>Wide!C94</f>
         <v>1</v>
       </c>
       <c r="C194" t="s">
@@ -6048,6 +6273,7 @@
         <v>69</v>
       </c>
       <c r="B195">
+        <f>Wide!C95</f>
         <v>1</v>
       </c>
       <c r="C195" t="s">
@@ -6059,6 +6285,7 @@
         <v>68</v>
       </c>
       <c r="B196">
+        <f>Wide!C96</f>
         <v>1</v>
       </c>
       <c r="C196" t="s">
@@ -6070,6 +6297,7 @@
         <v>37</v>
       </c>
       <c r="B197">
+        <f>Wide!C97</f>
         <v>1</v>
       </c>
       <c r="C197" t="s">
@@ -6081,6 +6309,7 @@
         <v>38</v>
       </c>
       <c r="B198">
+        <f>Wide!C98</f>
         <v>1</v>
       </c>
       <c r="C198" t="s">
@@ -6092,6 +6321,7 @@
         <v>98</v>
       </c>
       <c r="B199">
+        <f>Wide!C99</f>
         <v>1</v>
       </c>
       <c r="C199" t="s">
@@ -6103,6 +6333,7 @@
         <v>97</v>
       </c>
       <c r="B200">
+        <f>Wide!C100</f>
         <v>0.66666999999999998</v>
       </c>
       <c r="C200" t="s">
@@ -6114,6 +6345,7 @@
         <v>39</v>
       </c>
       <c r="B201">
+        <f>Wide!C101</f>
         <v>0.5</v>
       </c>
       <c r="C201" t="s">
@@ -6125,6 +6357,7 @@
         <v>29</v>
       </c>
       <c r="B202">
+        <f>Wide!D2</f>
         <v>1</v>
       </c>
       <c r="C202" t="s">
@@ -6136,7 +6369,8 @@
         <v>83</v>
       </c>
       <c r="B203">
-        <v>0.66666999999999998</v>
+        <f>Wide!D3</f>
+        <v>0.69443999999999995</v>
       </c>
       <c r="C203" t="s">
         <v>104</v>
@@ -6147,7 +6381,8 @@
         <v>84</v>
       </c>
       <c r="B204">
-        <v>0.75309000000000004</v>
+        <f>Wide!D4</f>
+        <v>0.80556000000000005</v>
       </c>
       <c r="C204" t="s">
         <v>104</v>
@@ -6158,7 +6393,8 @@
         <v>85</v>
       </c>
       <c r="B205">
-        <v>0.75309000000000004</v>
+        <f>Wide!D5</f>
+        <v>0.88888999999999996</v>
       </c>
       <c r="C205" t="s">
         <v>104</v>
@@ -6169,7 +6405,8 @@
         <v>86</v>
       </c>
       <c r="B206">
-        <v>0.86419999999999997</v>
+        <f>Wide!D6</f>
+        <v>0.97221999999999997</v>
       </c>
       <c r="C206" t="s">
         <v>104</v>
@@ -6180,6 +6417,7 @@
         <v>87</v>
       </c>
       <c r="B207">
+        <f>Wide!D7</f>
         <v>0.66666999999999998</v>
       </c>
       <c r="C207" t="s">
@@ -6191,7 +6429,8 @@
         <v>88</v>
       </c>
       <c r="B208">
-        <v>0.90908999999999995</v>
+        <f>Wide!D8</f>
+        <v>0.625</v>
       </c>
       <c r="C208" t="s">
         <v>104</v>
@@ -6202,6 +6441,7 @@
         <v>25</v>
       </c>
       <c r="B209">
+        <f>Wide!D9</f>
         <v>0.75</v>
       </c>
       <c r="C209" t="s">
@@ -6213,6 +6453,7 @@
         <v>27</v>
       </c>
       <c r="B210">
+        <f>Wide!D10</f>
         <v>0.75</v>
       </c>
       <c r="C210" t="s">
@@ -6224,6 +6465,7 @@
         <v>28</v>
       </c>
       <c r="B211">
+        <f>Wide!D11</f>
         <v>1</v>
       </c>
       <c r="C211" t="s">
@@ -6235,6 +6477,7 @@
         <v>26</v>
       </c>
       <c r="B212">
+        <f>Wide!D12</f>
         <v>0.75</v>
       </c>
       <c r="C212" t="s">
@@ -6246,7 +6489,8 @@
         <v>36</v>
       </c>
       <c r="B213">
-        <v>0.4</v>
+        <f>Wide!D13</f>
+        <v>0.66666999999999998</v>
       </c>
       <c r="C213" t="s">
         <v>104</v>
@@ -6257,7 +6501,8 @@
         <v>35</v>
       </c>
       <c r="B214">
-        <v>0.7</v>
+        <f>Wide!D14</f>
+        <v>0.83333000000000002</v>
       </c>
       <c r="C214" t="s">
         <v>104</v>
@@ -6268,6 +6513,7 @@
         <v>5</v>
       </c>
       <c r="B215">
+        <f>Wide!D15</f>
         <v>1</v>
       </c>
       <c r="C215" t="s">
@@ -6279,6 +6525,7 @@
         <v>6</v>
       </c>
       <c r="B216">
+        <f>Wide!D16</f>
         <v>1</v>
       </c>
       <c r="C216" t="s">
@@ -6290,7 +6537,8 @@
         <v>7</v>
       </c>
       <c r="B217">
-        <v>6.8180000000000004E-2</v>
+        <f>Wide!D17</f>
+        <v>0.15789</v>
       </c>
       <c r="C217" t="s">
         <v>104</v>
@@ -6301,7 +6549,8 @@
         <v>31</v>
       </c>
       <c r="B218">
-        <v>0.22222</v>
+        <f>Wide!D18</f>
+        <v>0.5</v>
       </c>
       <c r="C218" t="s">
         <v>104</v>
@@ -6312,6 +6561,7 @@
         <v>32</v>
       </c>
       <c r="B219">
+        <f>Wide!D19</f>
         <v>0</v>
       </c>
       <c r="C219" t="s">
@@ -6323,7 +6573,8 @@
         <v>30</v>
       </c>
       <c r="B220">
-        <v>0.88888999999999996</v>
+        <f>Wide!D20</f>
+        <v>1</v>
       </c>
       <c r="C220" t="s">
         <v>104</v>
@@ -6334,6 +6585,7 @@
         <v>100</v>
       </c>
       <c r="B221">
+        <f>Wide!D21</f>
         <v>1</v>
       </c>
       <c r="C221" t="s">
@@ -6345,6 +6597,7 @@
         <v>67</v>
       </c>
       <c r="B222">
+        <f>Wide!D22</f>
         <v>1</v>
       </c>
       <c r="C222" t="s">
@@ -6356,6 +6609,7 @@
         <v>66</v>
       </c>
       <c r="B223">
+        <f>Wide!D23</f>
         <v>1</v>
       </c>
       <c r="C223" t="s">
@@ -6367,7 +6621,8 @@
         <v>78</v>
       </c>
       <c r="B224">
-        <v>0.57499999999999996</v>
+        <f>Wide!D24</f>
+        <v>0.69564999999999999</v>
       </c>
       <c r="C224" t="s">
         <v>104</v>
@@ -6378,7 +6633,8 @@
         <v>79</v>
       </c>
       <c r="B225">
-        <v>0.45</v>
+        <f>Wide!D25</f>
+        <v>0.30435000000000001</v>
       </c>
       <c r="C225" t="s">
         <v>104</v>
@@ -6389,7 +6645,8 @@
         <v>71</v>
       </c>
       <c r="B226">
-        <v>1</v>
+        <f>Wide!D26</f>
+        <v>0.80435000000000001</v>
       </c>
       <c r="C226" t="s">
         <v>104</v>
@@ -6400,6 +6657,7 @@
         <v>72</v>
       </c>
       <c r="B227">
+        <f>Wide!D27</f>
         <v>1</v>
       </c>
       <c r="C227" t="s">
@@ -6411,6 +6669,7 @@
         <v>81</v>
       </c>
       <c r="B228">
+        <f>Wide!D28</f>
         <v>1</v>
       </c>
       <c r="C228" t="s">
@@ -6422,7 +6681,8 @@
         <v>74</v>
       </c>
       <c r="B229">
-        <v>0.13750000000000001</v>
+        <f>Wide!D29</f>
+        <v>0.19564999999999999</v>
       </c>
       <c r="C229" t="s">
         <v>104</v>
@@ -6433,7 +6693,8 @@
         <v>73</v>
       </c>
       <c r="B230">
-        <v>0.5625</v>
+        <f>Wide!D30</f>
+        <v>0.58696000000000004</v>
       </c>
       <c r="C230" t="s">
         <v>104</v>
@@ -6444,7 +6705,8 @@
         <v>75</v>
       </c>
       <c r="B231">
-        <v>0.3</v>
+        <f>Wide!D31</f>
+        <v>0.36957000000000001</v>
       </c>
       <c r="C231" t="s">
         <v>104</v>
@@ -6455,7 +6717,8 @@
         <v>82</v>
       </c>
       <c r="B232">
-        <v>0.83333000000000002</v>
+        <f>Wide!D32</f>
+        <v>0.93332999999999999</v>
       </c>
       <c r="C232" t="s">
         <v>104</v>
@@ -6466,7 +6729,8 @@
         <v>80</v>
       </c>
       <c r="B233">
-        <v>6.25E-2</v>
+        <f>Wide!D33</f>
+        <v>6.522E-2</v>
       </c>
       <c r="C233" t="s">
         <v>104</v>
@@ -6477,7 +6741,8 @@
         <v>76</v>
       </c>
       <c r="B234">
-        <v>0.9375</v>
+        <f>Wide!D34</f>
+        <v>0.97826000000000002</v>
       </c>
       <c r="C234" t="s">
         <v>104</v>
@@ -6488,7 +6753,8 @@
         <v>77</v>
       </c>
       <c r="B235">
-        <v>0.9</v>
+        <f>Wide!D35</f>
+        <v>0.80435000000000001</v>
       </c>
       <c r="C235" t="s">
         <v>104</v>
@@ -6499,7 +6765,8 @@
         <v>15</v>
       </c>
       <c r="B236">
-        <v>0.86667000000000005</v>
+        <f>Wide!D36</f>
+        <v>0.94118000000000002</v>
       </c>
       <c r="C236" t="s">
         <v>104</v>
@@ -6510,6 +6777,7 @@
         <v>17</v>
       </c>
       <c r="B237">
+        <f>Wide!D37</f>
         <v>1</v>
       </c>
       <c r="C237" t="s">
@@ -6521,6 +6789,7 @@
         <v>16</v>
       </c>
       <c r="B238">
+        <f>Wide!D38</f>
         <v>1</v>
       </c>
       <c r="C238" t="s">
@@ -6532,7 +6801,8 @@
         <v>19</v>
       </c>
       <c r="B239">
-        <v>0.1</v>
+        <f>Wide!D39</f>
+        <v>0.17646999999999999</v>
       </c>
       <c r="C239" t="s">
         <v>104</v>
@@ -6543,7 +6813,8 @@
         <v>18</v>
       </c>
       <c r="B240">
-        <v>0.7</v>
+        <f>Wide!D40</f>
+        <v>0.82352999999999998</v>
       </c>
       <c r="C240" t="s">
         <v>104</v>
@@ -6554,7 +6825,8 @@
         <v>20</v>
       </c>
       <c r="B241">
-        <v>0.36364000000000002</v>
+        <f>Wide!D41</f>
+        <v>0.5</v>
       </c>
       <c r="C241" t="s">
         <v>104</v>
@@ -6565,7 +6837,8 @@
         <v>90</v>
       </c>
       <c r="B242">
-        <v>0.98995</v>
+        <f>Wide!D42</f>
+        <v>0.97248000000000001</v>
       </c>
       <c r="C242" t="s">
         <v>104</v>
@@ -6576,6 +6849,7 @@
         <v>89</v>
       </c>
       <c r="B243">
+        <f>Wide!D43</f>
         <v>1</v>
       </c>
       <c r="C243" t="s">
@@ -6587,7 +6861,8 @@
         <v>93</v>
       </c>
       <c r="B244">
-        <v>0.88083</v>
+        <f>Wide!D44</f>
+        <v>0.91429000000000005</v>
       </c>
       <c r="C244" t="s">
         <v>104</v>
@@ -6598,6 +6873,7 @@
         <v>94</v>
       </c>
       <c r="B245">
+        <f>Wide!D45</f>
         <v>0.8</v>
       </c>
       <c r="C245" t="s">
@@ -6609,6 +6885,7 @@
         <v>91</v>
       </c>
       <c r="B246">
+        <f>Wide!D46</f>
         <v>1</v>
       </c>
       <c r="C246" t="s">
@@ -6620,7 +6897,8 @@
         <v>96</v>
       </c>
       <c r="B247">
-        <v>0.25</v>
+        <f>Wide!D47</f>
+        <v>0.33333000000000002</v>
       </c>
       <c r="C247" t="s">
         <v>104</v>
@@ -6631,6 +6909,7 @@
         <v>95</v>
       </c>
       <c r="B248">
+        <f>Wide!D48</f>
         <v>1</v>
       </c>
       <c r="C248" t="s">
@@ -6642,7 +6921,8 @@
         <v>92</v>
       </c>
       <c r="B249">
-        <v>0.98492000000000002</v>
+        <f>Wide!D49</f>
+        <v>0.98165000000000002</v>
       </c>
       <c r="C249" t="s">
         <v>104</v>
@@ -6653,6 +6933,7 @@
         <v>99</v>
       </c>
       <c r="B250">
+        <f>Wide!D50</f>
         <v>1</v>
       </c>
       <c r="C250" t="s">
@@ -6664,7 +6945,8 @@
         <v>64</v>
       </c>
       <c r="B251">
-        <v>0.88888999999999996</v>
+        <f>Wide!D51</f>
+        <v>1</v>
       </c>
       <c r="C251" t="s">
         <v>104</v>
@@ -6675,7 +6957,8 @@
         <v>65</v>
       </c>
       <c r="B252">
-        <v>0.44444</v>
+        <f>Wide!D52</f>
+        <v>0.66666999999999998</v>
       </c>
       <c r="C252" t="s">
         <v>104</v>
@@ -6686,7 +6969,8 @@
         <v>63</v>
       </c>
       <c r="B253">
-        <v>0.88888999999999996</v>
+        <f>Wide!D53</f>
+        <v>1</v>
       </c>
       <c r="C253" t="s">
         <v>104</v>
@@ -6697,7 +6981,8 @@
         <v>11</v>
       </c>
       <c r="B254">
-        <v>4.5449999999999997E-2</v>
+        <f>Wide!D54</f>
+        <v>6.6669999999999993E-2</v>
       </c>
       <c r="C254" t="s">
         <v>104</v>
@@ -6708,7 +6993,8 @@
         <v>13</v>
       </c>
       <c r="B255">
-        <v>0.88461999999999996</v>
+        <f>Wide!D55</f>
+        <v>0.90908999999999995</v>
       </c>
       <c r="C255" t="s">
         <v>104</v>
@@ -6719,6 +7005,7 @@
         <v>9</v>
       </c>
       <c r="B256">
+        <f>Wide!D56</f>
         <v>1</v>
       </c>
       <c r="C256" t="s">
@@ -6730,7 +7017,8 @@
         <v>10</v>
       </c>
       <c r="B257">
-        <v>0.79544999999999999</v>
+        <f>Wide!D57</f>
+        <v>0.93332999999999999</v>
       </c>
       <c r="C257" t="s">
         <v>104</v>
@@ -6741,6 +7029,7 @@
         <v>14</v>
       </c>
       <c r="B258">
+        <f>Wide!D58</f>
         <v>1</v>
       </c>
       <c r="C258" t="s">
@@ -6752,7 +7041,8 @@
         <v>12</v>
       </c>
       <c r="B259">
-        <v>3.8460000000000001E-2</v>
+        <f>Wide!D59</f>
+        <v>4.5449999999999997E-2</v>
       </c>
       <c r="C259" t="s">
         <v>104</v>
@@ -6763,7 +7053,8 @@
         <v>8</v>
       </c>
       <c r="B260">
-        <v>0.93181999999999998</v>
+        <f>Wide!D60</f>
+        <v>0.9</v>
       </c>
       <c r="C260" t="s">
         <v>104</v>
@@ -6774,7 +7065,8 @@
         <v>60</v>
       </c>
       <c r="B261">
-        <v>0.47059000000000001</v>
+        <f>Wide!D61</f>
+        <v>1</v>
       </c>
       <c r="C261" t="s">
         <v>104</v>
@@ -6785,7 +7077,8 @@
         <v>62</v>
       </c>
       <c r="B262">
-        <v>0.17646999999999999</v>
+        <f>Wide!D62</f>
+        <v>0.42857000000000001</v>
       </c>
       <c r="C262" t="s">
         <v>104</v>
@@ -6796,7 +7089,8 @@
         <v>61</v>
       </c>
       <c r="B263">
-        <v>0.11765</v>
+        <f>Wide!D63</f>
+        <v>0.28571000000000002</v>
       </c>
       <c r="C263" t="s">
         <v>104</v>
@@ -6807,7 +7101,8 @@
         <v>59</v>
       </c>
       <c r="B264">
-        <v>0.41176000000000001</v>
+        <f>Wide!D64</f>
+        <v>1</v>
       </c>
       <c r="C264" t="s">
         <v>104</v>
@@ -6818,6 +7113,7 @@
         <v>2</v>
       </c>
       <c r="B265">
+        <f>Wide!D65</f>
         <v>1</v>
       </c>
       <c r="C265" t="s">
@@ -6829,6 +7125,7 @@
         <v>1</v>
       </c>
       <c r="B266">
+        <f>Wide!D66</f>
         <v>1</v>
       </c>
       <c r="C266" t="s">
@@ -6840,6 +7137,7 @@
         <v>3</v>
       </c>
       <c r="B267">
+        <f>Wide!D67</f>
         <v>1</v>
       </c>
       <c r="C267" t="s">
@@ -6851,7 +7149,8 @@
         <v>4</v>
       </c>
       <c r="B268">
-        <v>0.25</v>
+        <f>Wide!D68</f>
+        <v>0.33333000000000002</v>
       </c>
       <c r="C268" t="s">
         <v>104</v>
@@ -6862,6 +7161,7 @@
         <v>21</v>
       </c>
       <c r="B269">
+        <f>Wide!D69</f>
         <v>0.75</v>
       </c>
       <c r="C269" t="s">
@@ -6873,6 +7173,7 @@
         <v>23</v>
       </c>
       <c r="B270">
+        <f>Wide!D70</f>
         <v>0.75</v>
       </c>
       <c r="C270" t="s">
@@ -6884,6 +7185,7 @@
         <v>24</v>
       </c>
       <c r="B271">
+        <f>Wide!D71</f>
         <v>1</v>
       </c>
       <c r="C271" t="s">
@@ -6895,6 +7197,7 @@
         <v>22</v>
       </c>
       <c r="B272">
+        <f>Wide!D72</f>
         <v>0.75</v>
       </c>
       <c r="C272" t="s">
@@ -6906,7 +7209,8 @@
         <v>40</v>
       </c>
       <c r="B273">
-        <v>0.98889000000000005</v>
+        <f>Wide!D73</f>
+        <v>0.82857000000000003</v>
       </c>
       <c r="C273" t="s">
         <v>104</v>
@@ -6917,7 +7221,8 @@
         <v>41</v>
       </c>
       <c r="B274">
-        <v>0.98889000000000005</v>
+        <f>Wide!D74</f>
+        <v>0.94286000000000003</v>
       </c>
       <c r="C274" t="s">
         <v>104</v>
@@ -6928,6 +7233,7 @@
         <v>45</v>
       </c>
       <c r="B275">
+        <f>Wide!D75</f>
         <v>1</v>
       </c>
       <c r="C275" t="s">
@@ -6939,6 +7245,7 @@
         <v>42</v>
       </c>
       <c r="B276">
+        <f>Wide!D76</f>
         <v>1</v>
       </c>
       <c r="C276" t="s">
@@ -6950,7 +7257,8 @@
         <v>43</v>
       </c>
       <c r="B277">
-        <v>0.84443999999999997</v>
+        <f>Wide!D77</f>
+        <v>0.57142999999999999</v>
       </c>
       <c r="C277" t="s">
         <v>104</v>
@@ -6961,7 +7269,8 @@
         <v>46</v>
       </c>
       <c r="B278">
-        <v>0.14285999999999999</v>
+        <f>Wide!D78</f>
+        <v>0.33333000000000002</v>
       </c>
       <c r="C278" t="s">
         <v>104</v>
@@ -6972,7 +7281,8 @@
         <v>48</v>
       </c>
       <c r="B279">
-        <v>0.58333000000000002</v>
+        <f>Wide!D79</f>
+        <v>0.625</v>
       </c>
       <c r="C279" t="s">
         <v>104</v>
@@ -6983,6 +7293,7 @@
         <v>49</v>
       </c>
       <c r="B280">
+        <f>Wide!D80</f>
         <v>0</v>
       </c>
       <c r="C280" t="s">
@@ -6994,6 +7305,7 @@
         <v>47</v>
       </c>
       <c r="B281">
+        <f>Wide!D81</f>
         <v>1</v>
       </c>
       <c r="C281" t="s">
@@ -7005,7 +7317,8 @@
         <v>44</v>
       </c>
       <c r="B282">
-        <v>0.18889</v>
+        <f>Wide!D82</f>
+        <v>0.28571000000000002</v>
       </c>
       <c r="C282" t="s">
         <v>104</v>
@@ -7016,7 +7329,8 @@
         <v>51</v>
       </c>
       <c r="B283">
-        <v>0.98507</v>
+        <f>Wide!D83</f>
+        <v>1</v>
       </c>
       <c r="C283" t="s">
         <v>104</v>
@@ -7027,7 +7341,8 @@
         <v>52</v>
       </c>
       <c r="B284">
-        <v>0.10448</v>
+        <f>Wide!D84</f>
+        <v>7.4999999999999997E-2</v>
       </c>
       <c r="C284" t="s">
         <v>104</v>
@@ -7038,7 +7353,8 @@
         <v>55</v>
       </c>
       <c r="B285">
-        <v>0.49253999999999998</v>
+        <f>Wide!D85</f>
+        <v>0.52500000000000002</v>
       </c>
       <c r="C285" t="s">
         <v>104</v>
@@ -7049,6 +7365,7 @@
         <v>58</v>
       </c>
       <c r="B286">
+        <f>Wide!D86</f>
         <v>1</v>
       </c>
       <c r="C286" t="s">
@@ -7060,7 +7377,8 @@
         <v>50</v>
       </c>
       <c r="B287">
-        <v>0.95521999999999996</v>
+        <f>Wide!D87</f>
+        <v>1</v>
       </c>
       <c r="C287" t="s">
         <v>104</v>
@@ -7071,7 +7389,8 @@
         <v>56</v>
       </c>
       <c r="B288">
-        <v>0.71641999999999995</v>
+        <f>Wide!D88</f>
+        <v>0.8</v>
       </c>
       <c r="C288" t="s">
         <v>104</v>
@@ -7082,7 +7401,8 @@
         <v>54</v>
       </c>
       <c r="B289">
-        <v>0.55223999999999995</v>
+        <f>Wide!D89</f>
+        <v>0.67500000000000004</v>
       </c>
       <c r="C289" t="s">
         <v>104</v>
@@ -7093,6 +7413,7 @@
         <v>53</v>
       </c>
       <c r="B290">
+        <f>Wide!D90</f>
         <v>1</v>
       </c>
       <c r="C290" t="s">
@@ -7104,7 +7425,8 @@
         <v>57</v>
       </c>
       <c r="B291">
-        <v>0.10448</v>
+        <f>Wide!D91</f>
+        <v>7.4999999999999997E-2</v>
       </c>
       <c r="C291" t="s">
         <v>104</v>
@@ -7115,7 +7437,8 @@
         <v>33</v>
       </c>
       <c r="B292">
-        <v>0.875</v>
+        <f>Wide!D92</f>
+        <v>0.83333000000000002</v>
       </c>
       <c r="C292" t="s">
         <v>104</v>
@@ -7126,7 +7449,8 @@
         <v>34</v>
       </c>
       <c r="B293">
-        <v>0.75</v>
+        <f>Wide!D93</f>
+        <v>0.83333000000000002</v>
       </c>
       <c r="C293" t="s">
         <v>104</v>
@@ -7137,6 +7461,7 @@
         <v>70</v>
       </c>
       <c r="B294">
+        <f>Wide!D94</f>
         <v>1</v>
       </c>
       <c r="C294" t="s">
@@ -7148,6 +7473,7 @@
         <v>69</v>
       </c>
       <c r="B295">
+        <f>Wide!D95</f>
         <v>1</v>
       </c>
       <c r="C295" t="s">
@@ -7159,6 +7485,7 @@
         <v>68</v>
       </c>
       <c r="B296">
+        <f>Wide!D96</f>
         <v>1</v>
       </c>
       <c r="C296" t="s">
@@ -7170,6 +7497,7 @@
         <v>37</v>
       </c>
       <c r="B297">
+        <f>Wide!D97</f>
         <v>1</v>
       </c>
       <c r="C297" t="s">
@@ -7181,6 +7509,7 @@
         <v>38</v>
       </c>
       <c r="B298">
+        <f>Wide!D98</f>
         <v>1</v>
       </c>
       <c r="C298" t="s">
@@ -7192,6 +7521,7 @@
         <v>98</v>
       </c>
       <c r="B299">
+        <f>Wide!D99</f>
         <v>1</v>
       </c>
       <c r="C299" t="s">
@@ -7203,6 +7533,7 @@
         <v>97</v>
       </c>
       <c r="B300">
+        <f>Wide!D100</f>
         <v>1</v>
       </c>
       <c r="C300" t="s">
@@ -7214,6 +7545,7 @@
         <v>39</v>
       </c>
       <c r="B301">
+        <f>Wide!D101</f>
         <v>0.5</v>
       </c>
       <c r="C301" t="s">
@@ -7225,6 +7557,7 @@
         <v>29</v>
       </c>
       <c r="B302">
+        <f>Wide!E2</f>
         <v>1</v>
       </c>
       <c r="C302" t="s">
@@ -7236,6 +7569,7 @@
         <v>83</v>
       </c>
       <c r="B303">
+        <f>Wide!E3</f>
         <v>0.66666999999999998</v>
       </c>
       <c r="C303" t="s">
@@ -7247,7 +7581,8 @@
         <v>84</v>
       </c>
       <c r="B304">
-        <v>0.75309000000000004</v>
+        <f>Wide!E4</f>
+        <v>0.80556000000000005</v>
       </c>
       <c r="C304" t="s">
         <v>106</v>
@@ -7258,7 +7593,8 @@
         <v>85</v>
       </c>
       <c r="B305">
-        <v>0.59258999999999995</v>
+        <f>Wide!E5</f>
+        <v>0.77778000000000003</v>
       </c>
       <c r="C305" t="s">
         <v>106</v>
@@ -7269,7 +7605,8 @@
         <v>86</v>
       </c>
       <c r="B306">
-        <v>0.86419999999999997</v>
+        <f>Wide!E6</f>
+        <v>0.97221999999999997</v>
       </c>
       <c r="C306" t="s">
         <v>106</v>
@@ -7280,6 +7617,7 @@
         <v>87</v>
       </c>
       <c r="B307">
+        <f>Wide!E7</f>
         <v>0.66666999999999998</v>
       </c>
       <c r="C307" t="s">
@@ -7291,7 +7629,8 @@
         <v>88</v>
       </c>
       <c r="B308">
-        <v>0.90908999999999995</v>
+        <f>Wide!E8</f>
+        <v>0.625</v>
       </c>
       <c r="C308" t="s">
         <v>106</v>
@@ -7302,6 +7641,7 @@
         <v>25</v>
       </c>
       <c r="B309">
+        <f>Wide!E9</f>
         <v>1</v>
       </c>
       <c r="C309" t="s">
@@ -7313,6 +7653,7 @@
         <v>27</v>
       </c>
       <c r="B310">
+        <f>Wide!E10</f>
         <v>1</v>
       </c>
       <c r="C310" t="s">
@@ -7324,6 +7665,7 @@
         <v>28</v>
       </c>
       <c r="B311">
+        <f>Wide!E11</f>
         <v>1</v>
       </c>
       <c r="C311" t="s">
@@ -7335,6 +7677,7 @@
         <v>26</v>
       </c>
       <c r="B312">
+        <f>Wide!E12</f>
         <v>1</v>
       </c>
       <c r="C312" t="s">
@@ -7346,7 +7689,8 @@
         <v>36</v>
       </c>
       <c r="B313">
-        <v>0.4</v>
+        <f>Wide!E13</f>
+        <v>0.66666999999999998</v>
       </c>
       <c r="C313" t="s">
         <v>106</v>
@@ -7357,7 +7701,8 @@
         <v>35</v>
       </c>
       <c r="B314">
-        <v>0.8</v>
+        <f>Wide!E14</f>
+        <v>1</v>
       </c>
       <c r="C314" t="s">
         <v>106</v>
@@ -7368,6 +7713,7 @@
         <v>5</v>
       </c>
       <c r="B315">
+        <f>Wide!E15</f>
         <v>1</v>
       </c>
       <c r="C315" t="s">
@@ -7379,6 +7725,7 @@
         <v>6</v>
       </c>
       <c r="B316">
+        <f>Wide!E16</f>
         <v>1</v>
       </c>
       <c r="C316" t="s">
@@ -7390,7 +7737,8 @@
         <v>7</v>
       </c>
       <c r="B317">
-        <v>6.8180000000000004E-2</v>
+        <f>Wide!E17</f>
+        <v>0.15789</v>
       </c>
       <c r="C317" t="s">
         <v>106</v>
@@ -7401,7 +7749,8 @@
         <v>31</v>
       </c>
       <c r="B318">
-        <v>0.22222</v>
+        <f>Wide!E18</f>
+        <v>0.5</v>
       </c>
       <c r="C318" t="s">
         <v>106</v>
@@ -7412,6 +7761,7 @@
         <v>32</v>
       </c>
       <c r="B319">
+        <f>Wide!E19</f>
         <v>0</v>
       </c>
       <c r="C319" t="s">
@@ -7423,7 +7773,8 @@
         <v>30</v>
       </c>
       <c r="B320">
-        <v>0.88888999999999996</v>
+        <f>Wide!E20</f>
+        <v>1</v>
       </c>
       <c r="C320" t="s">
         <v>106</v>
@@ -7434,6 +7785,7 @@
         <v>100</v>
       </c>
       <c r="B321">
+        <f>Wide!E21</f>
         <v>1</v>
       </c>
       <c r="C321" t="s">
@@ -7445,6 +7797,7 @@
         <v>67</v>
       </c>
       <c r="B322">
+        <f>Wide!E22</f>
         <v>1</v>
       </c>
       <c r="C322" t="s">
@@ -7456,6 +7809,7 @@
         <v>66</v>
       </c>
       <c r="B323">
+        <f>Wide!E23</f>
         <v>1</v>
       </c>
       <c r="C323" t="s">
@@ -7467,7 +7821,8 @@
         <v>78</v>
       </c>
       <c r="B324">
-        <v>0.76249999999999996</v>
+        <f>Wide!E24</f>
+        <v>0.89129999999999998</v>
       </c>
       <c r="C324" t="s">
         <v>106</v>
@@ -7478,7 +7833,8 @@
         <v>79</v>
       </c>
       <c r="B325">
-        <v>0.45</v>
+        <f>Wide!E25</f>
+        <v>0.30435000000000001</v>
       </c>
       <c r="C325" t="s">
         <v>106</v>
@@ -7489,7 +7845,8 @@
         <v>71</v>
       </c>
       <c r="B326">
-        <v>0.9375</v>
+        <f>Wide!E26</f>
+        <v>1</v>
       </c>
       <c r="C326" t="s">
         <v>106</v>
@@ -7500,7 +7857,8 @@
         <v>72</v>
       </c>
       <c r="B327">
-        <v>0.9375</v>
+        <f>Wide!E27</f>
+        <v>1</v>
       </c>
       <c r="C327" t="s">
         <v>106</v>
@@ -7511,6 +7869,7 @@
         <v>81</v>
       </c>
       <c r="B328">
+        <f>Wide!E28</f>
         <v>1</v>
       </c>
       <c r="C328" t="s">
@@ -7522,7 +7881,8 @@
         <v>74</v>
       </c>
       <c r="B329">
-        <v>0.13750000000000001</v>
+        <f>Wide!E29</f>
+        <v>0.19564999999999999</v>
       </c>
       <c r="C329" t="s">
         <v>106</v>
@@ -7533,7 +7893,8 @@
         <v>73</v>
       </c>
       <c r="B330">
-        <v>0.5625</v>
+        <f>Wide!E30</f>
+        <v>0.58696000000000004</v>
       </c>
       <c r="C330" t="s">
         <v>106</v>
@@ -7544,7 +7905,8 @@
         <v>75</v>
       </c>
       <c r="B331">
-        <v>0.3</v>
+        <f>Wide!E31</f>
+        <v>0.36957000000000001</v>
       </c>
       <c r="C331" t="s">
         <v>106</v>
@@ -7555,7 +7917,8 @@
         <v>82</v>
       </c>
       <c r="B332">
-        <v>0.83333000000000002</v>
+        <f>Wide!E32</f>
+        <v>0.93332999999999999</v>
       </c>
       <c r="C332" t="s">
         <v>106</v>
@@ -7566,7 +7929,8 @@
         <v>80</v>
       </c>
       <c r="B333">
-        <v>6.25E-2</v>
+        <f>Wide!E33</f>
+        <v>6.522E-2</v>
       </c>
       <c r="C333" t="s">
         <v>106</v>
@@ -7577,7 +7941,8 @@
         <v>76</v>
       </c>
       <c r="B334">
-        <v>0.9375</v>
+        <f>Wide!E34</f>
+        <v>0.97826000000000002</v>
       </c>
       <c r="C334" t="s">
         <v>106</v>
@@ -7588,7 +7953,8 @@
         <v>77</v>
       </c>
       <c r="B335">
-        <v>0.875</v>
+        <f>Wide!E35</f>
+        <v>0.80435000000000001</v>
       </c>
       <c r="C335" t="s">
         <v>106</v>
@@ -7599,7 +7965,8 @@
         <v>15</v>
       </c>
       <c r="B336">
-        <v>0.9</v>
+        <f>Wide!E36</f>
+        <v>1</v>
       </c>
       <c r="C336" t="s">
         <v>106</v>
@@ -7610,6 +7977,7 @@
         <v>17</v>
       </c>
       <c r="B337">
+        <f>Wide!E37</f>
         <v>1</v>
       </c>
       <c r="C337" t="s">
@@ -7621,6 +7989,7 @@
         <v>16</v>
       </c>
       <c r="B338">
+        <f>Wide!E38</f>
         <v>1</v>
       </c>
       <c r="C338" t="s">
@@ -7632,7 +8001,8 @@
         <v>19</v>
       </c>
       <c r="B339">
-        <v>0.1</v>
+        <f>Wide!E39</f>
+        <v>0.17646999999999999</v>
       </c>
       <c r="C339" t="s">
         <v>106</v>
@@ -7643,7 +8013,8 @@
         <v>18</v>
       </c>
       <c r="B340">
-        <v>0.7</v>
+        <f>Wide!E40</f>
+        <v>0.82352999999999998</v>
       </c>
       <c r="C340" t="s">
         <v>106</v>
@@ -7654,7 +8025,8 @@
         <v>20</v>
       </c>
       <c r="B341">
-        <v>0.36364000000000002</v>
+        <f>Wide!E41</f>
+        <v>0.5</v>
       </c>
       <c r="C341" t="s">
         <v>106</v>
@@ -7665,7 +8037,8 @@
         <v>90</v>
       </c>
       <c r="B342">
-        <v>0.99497000000000002</v>
+        <f>Wide!E42</f>
+        <v>1</v>
       </c>
       <c r="C342" t="s">
         <v>106</v>
@@ -7676,6 +8049,7 @@
         <v>89</v>
       </c>
       <c r="B343">
+        <f>Wide!E43</f>
         <v>1</v>
       </c>
       <c r="C343" t="s">
@@ -7687,7 +8061,8 @@
         <v>93</v>
       </c>
       <c r="B344">
-        <v>0.88083</v>
+        <f>Wide!E44</f>
+        <v>0.91429000000000005</v>
       </c>
       <c r="C344" t="s">
         <v>106</v>
@@ -7698,6 +8073,7 @@
         <v>94</v>
       </c>
       <c r="B345">
+        <f>Wide!E45</f>
         <v>0.8</v>
       </c>
       <c r="C345" t="s">
@@ -7709,6 +8085,7 @@
         <v>91</v>
       </c>
       <c r="B346">
+        <f>Wide!E46</f>
         <v>1</v>
       </c>
       <c r="C346" t="s">
@@ -7720,7 +8097,8 @@
         <v>96</v>
       </c>
       <c r="B347">
-        <v>0.25</v>
+        <f>Wide!E47</f>
+        <v>0.33333000000000002</v>
       </c>
       <c r="C347" t="s">
         <v>106</v>
@@ -7731,6 +8109,7 @@
         <v>95</v>
       </c>
       <c r="B348">
+        <f>Wide!E48</f>
         <v>1</v>
       </c>
       <c r="C348" t="s">
@@ -7742,7 +8121,8 @@
         <v>92</v>
       </c>
       <c r="B349">
-        <v>0.98492000000000002</v>
+        <f>Wide!E49</f>
+        <v>0.98165000000000002</v>
       </c>
       <c r="C349" t="s">
         <v>106</v>
@@ -7753,6 +8133,7 @@
         <v>99</v>
       </c>
       <c r="B350">
+        <f>Wide!E50</f>
         <v>1</v>
       </c>
       <c r="C350" t="s">
@@ -7764,7 +8145,8 @@
         <v>64</v>
       </c>
       <c r="B351">
-        <v>0.88888999999999996</v>
+        <f>Wide!E51</f>
+        <v>1</v>
       </c>
       <c r="C351" t="s">
         <v>106</v>
@@ -7775,7 +8157,8 @@
         <v>65</v>
       </c>
       <c r="B352">
-        <v>0.44444</v>
+        <f>Wide!E52</f>
+        <v>0.66666999999999998</v>
       </c>
       <c r="C352" t="s">
         <v>106</v>
@@ -7786,7 +8169,8 @@
         <v>63</v>
       </c>
       <c r="B353">
-        <v>0.88888999999999996</v>
+        <f>Wide!E53</f>
+        <v>1</v>
       </c>
       <c r="C353" t="s">
         <v>106</v>
@@ -7797,7 +8181,8 @@
         <v>11</v>
       </c>
       <c r="B354">
-        <v>4.5449999999999997E-2</v>
+        <f>Wide!E54</f>
+        <v>6.6669999999999993E-2</v>
       </c>
       <c r="C354" t="s">
         <v>106</v>
@@ -7808,7 +8193,8 @@
         <v>13</v>
       </c>
       <c r="B355">
-        <v>0.88461999999999996</v>
+        <f>Wide!E55</f>
+        <v>0.90908999999999995</v>
       </c>
       <c r="C355" t="s">
         <v>106</v>
@@ -7819,6 +8205,7 @@
         <v>9</v>
       </c>
       <c r="B356">
+        <f>Wide!E56</f>
         <v>1</v>
       </c>
       <c r="C356" t="s">
@@ -7830,7 +8217,8 @@
         <v>10</v>
       </c>
       <c r="B357">
-        <v>0.79544999999999999</v>
+        <f>Wide!E57</f>
+        <v>0.93332999999999999</v>
       </c>
       <c r="C357" t="s">
         <v>106</v>
@@ -7841,6 +8229,7 @@
         <v>14</v>
       </c>
       <c r="B358">
+        <f>Wide!E58</f>
         <v>1</v>
       </c>
       <c r="C358" t="s">
@@ -7852,7 +8241,8 @@
         <v>12</v>
       </c>
       <c r="B359">
-        <v>7.6920000000000002E-2</v>
+        <f>Wide!E59</f>
+        <v>9.0910000000000005E-2</v>
       </c>
       <c r="C359" t="s">
         <v>106</v>
@@ -7863,7 +8253,8 @@
         <v>8</v>
       </c>
       <c r="B360">
-        <v>0.77273000000000003</v>
+        <f>Wide!E60</f>
+        <v>0.9</v>
       </c>
       <c r="C360" t="s">
         <v>106</v>
@@ -7874,7 +8265,8 @@
         <v>60</v>
       </c>
       <c r="B361">
-        <v>0.47059000000000001</v>
+        <f>Wide!E61</f>
+        <v>1</v>
       </c>
       <c r="C361" t="s">
         <v>106</v>
@@ -7885,7 +8277,8 @@
         <v>62</v>
       </c>
       <c r="B362">
-        <v>0.17646999999999999</v>
+        <f>Wide!E62</f>
+        <v>0.42857000000000001</v>
       </c>
       <c r="C362" t="s">
         <v>106</v>
@@ -7896,7 +8289,8 @@
         <v>61</v>
       </c>
       <c r="B363">
-        <v>0.11765</v>
+        <f>Wide!E63</f>
+        <v>0.28571000000000002</v>
       </c>
       <c r="C363" t="s">
         <v>106</v>
@@ -7907,7 +8301,8 @@
         <v>59</v>
       </c>
       <c r="B364">
-        <v>0.41176000000000001</v>
+        <f>Wide!E64</f>
+        <v>1</v>
       </c>
       <c r="C364" t="s">
         <v>106</v>
@@ -7918,7 +8313,8 @@
         <v>2</v>
       </c>
       <c r="B365">
-        <v>0.75</v>
+        <f>Wide!E65</f>
+        <v>1</v>
       </c>
       <c r="C365" t="s">
         <v>106</v>
@@ -7929,7 +8325,8 @@
         <v>1</v>
       </c>
       <c r="B366">
-        <v>0.75</v>
+        <f>Wide!E66</f>
+        <v>1</v>
       </c>
       <c r="C366" t="s">
         <v>106</v>
@@ -7940,7 +8337,8 @@
         <v>3</v>
       </c>
       <c r="B367">
-        <v>0.75</v>
+        <f>Wide!E67</f>
+        <v>1</v>
       </c>
       <c r="C367" t="s">
         <v>106</v>
@@ -7951,7 +8349,8 @@
         <v>4</v>
       </c>
       <c r="B368">
-        <v>0.25</v>
+        <f>Wide!E68</f>
+        <v>0.33333000000000002</v>
       </c>
       <c r="C368" t="s">
         <v>106</v>
@@ -7962,6 +8361,7 @@
         <v>21</v>
       </c>
       <c r="B369">
+        <f>Wide!E69</f>
         <v>1</v>
       </c>
       <c r="C369" t="s">
@@ -7973,6 +8373,7 @@
         <v>23</v>
       </c>
       <c r="B370">
+        <f>Wide!E70</f>
         <v>1</v>
       </c>
       <c r="C370" t="s">
@@ -7984,6 +8385,7 @@
         <v>24</v>
       </c>
       <c r="B371">
+        <f>Wide!E71</f>
         <v>1</v>
       </c>
       <c r="C371" t="s">
@@ -7995,6 +8397,7 @@
         <v>22</v>
       </c>
       <c r="B372">
+        <f>Wide!E72</f>
         <v>1</v>
       </c>
       <c r="C372" t="s">
@@ -8006,7 +8409,8 @@
         <v>40</v>
       </c>
       <c r="B373">
-        <v>0.86667000000000005</v>
+        <f>Wide!E73</f>
+        <v>1</v>
       </c>
       <c r="C373" t="s">
         <v>106</v>
@@ -8017,7 +8421,8 @@
         <v>41</v>
       </c>
       <c r="B374">
-        <v>0.86667000000000005</v>
+        <f>Wide!E74</f>
+        <v>1</v>
       </c>
       <c r="C374" t="s">
         <v>106</v>
@@ -8028,6 +8433,7 @@
         <v>45</v>
       </c>
       <c r="B375">
+        <f>Wide!E75</f>
         <v>1</v>
       </c>
       <c r="C375" t="s">
@@ -8039,6 +8445,7 @@
         <v>42</v>
       </c>
       <c r="B376">
+        <f>Wide!E76</f>
         <v>1</v>
       </c>
       <c r="C376" t="s">
@@ -8050,7 +8457,8 @@
         <v>43</v>
       </c>
       <c r="B377">
-        <v>0.84443999999999997</v>
+        <f>Wide!E77</f>
+        <v>0.57142999999999999</v>
       </c>
       <c r="C377" t="s">
         <v>106</v>
@@ -8061,7 +8469,8 @@
         <v>46</v>
       </c>
       <c r="B378">
-        <v>0.14285999999999999</v>
+        <f>Wide!E78</f>
+        <v>0.33333000000000002</v>
       </c>
       <c r="C378" t="s">
         <v>106</v>
@@ -8072,7 +8481,8 @@
         <v>48</v>
       </c>
       <c r="B379">
-        <v>0.58333000000000002</v>
+        <f>Wide!E79</f>
+        <v>0.625</v>
       </c>
       <c r="C379" t="s">
         <v>106</v>
@@ -8083,6 +8493,7 @@
         <v>49</v>
       </c>
       <c r="B380">
+        <f>Wide!E80</f>
         <v>0</v>
       </c>
       <c r="C380" t="s">
@@ -8094,6 +8505,7 @@
         <v>47</v>
       </c>
       <c r="B381">
+        <f>Wide!E81</f>
         <v>1</v>
       </c>
       <c r="C381" t="s">
@@ -8105,7 +8517,8 @@
         <v>44</v>
       </c>
       <c r="B382">
-        <v>0.18889</v>
+        <f>Wide!E82</f>
+        <v>0.28571000000000002</v>
       </c>
       <c r="C382" t="s">
         <v>106</v>
@@ -8116,7 +8529,8 @@
         <v>51</v>
       </c>
       <c r="B383">
-        <v>0.98507</v>
+        <f>Wide!E83</f>
+        <v>1</v>
       </c>
       <c r="C383" t="s">
         <v>106</v>
@@ -8127,6 +8541,7 @@
         <v>52</v>
       </c>
       <c r="B384">
+        <f>Wide!E84</f>
         <v>1</v>
       </c>
       <c r="C384" t="s">
@@ -8138,7 +8553,8 @@
         <v>55</v>
       </c>
       <c r="B385">
-        <v>0.49253999999999998</v>
+        <f>Wide!E85</f>
+        <v>0.52500000000000002</v>
       </c>
       <c r="C385" t="s">
         <v>106</v>
@@ -8149,6 +8565,7 @@
         <v>58</v>
       </c>
       <c r="B386">
+        <f>Wide!E86</f>
         <v>1</v>
       </c>
       <c r="C386" t="s">
@@ -8160,6 +8577,7 @@
         <v>50</v>
       </c>
       <c r="B387">
+        <f>Wide!E87</f>
         <v>1</v>
       </c>
       <c r="C387" t="s">
@@ -8171,7 +8589,8 @@
         <v>56</v>
       </c>
       <c r="B388">
-        <v>0.71641999999999995</v>
+        <f>Wide!E88</f>
+        <v>0.8</v>
       </c>
       <c r="C388" t="s">
         <v>106</v>
@@ -8182,7 +8601,8 @@
         <v>54</v>
       </c>
       <c r="B389">
-        <v>0.55223999999999995</v>
+        <f>Wide!E89</f>
+        <v>0.67500000000000004</v>
       </c>
       <c r="C389" t="s">
         <v>106</v>
@@ -8193,6 +8613,7 @@
         <v>53</v>
       </c>
       <c r="B390">
+        <f>Wide!E90</f>
         <v>1</v>
       </c>
       <c r="C390" t="s">
@@ -8204,7 +8625,8 @@
         <v>57</v>
       </c>
       <c r="B391">
-        <v>0.10448</v>
+        <f>Wide!E91</f>
+        <v>7.4999999999999997E-2</v>
       </c>
       <c r="C391" t="s">
         <v>106</v>
@@ -8215,6 +8637,7 @@
         <v>33</v>
       </c>
       <c r="B392">
+        <f>Wide!E92</f>
         <v>1</v>
       </c>
       <c r="C392" t="s">
@@ -8226,7 +8649,8 @@
         <v>34</v>
       </c>
       <c r="B393">
-        <v>0.875</v>
+        <f>Wide!E93</f>
+        <v>1</v>
       </c>
       <c r="C393" t="s">
         <v>106</v>
@@ -8237,6 +8661,7 @@
         <v>70</v>
       </c>
       <c r="B394">
+        <f>Wide!E94</f>
         <v>1</v>
       </c>
       <c r="C394" t="s">
@@ -8248,6 +8673,7 @@
         <v>69</v>
       </c>
       <c r="B395">
+        <f>Wide!E95</f>
         <v>1</v>
       </c>
       <c r="C395" t="s">
@@ -8259,6 +8685,7 @@
         <v>68</v>
       </c>
       <c r="B396">
+        <f>Wide!E96</f>
         <v>1</v>
       </c>
       <c r="C396" t="s">
@@ -8270,6 +8697,7 @@
         <v>37</v>
       </c>
       <c r="B397">
+        <f>Wide!E97</f>
         <v>1</v>
       </c>
       <c r="C397" t="s">
@@ -8281,6 +8709,7 @@
         <v>38</v>
       </c>
       <c r="B398">
+        <f>Wide!E98</f>
         <v>1</v>
       </c>
       <c r="C398" t="s">
@@ -8292,6 +8721,7 @@
         <v>98</v>
       </c>
       <c r="B399">
+        <f>Wide!E99</f>
         <v>1</v>
       </c>
       <c r="C399" t="s">
@@ -8303,6 +8733,7 @@
         <v>97</v>
       </c>
       <c r="B400">
+        <f>Wide!E100</f>
         <v>1</v>
       </c>
       <c r="C400" t="s">
@@ -8314,6 +8745,7 @@
         <v>39</v>
       </c>
       <c r="B401">
+        <f>Wide!E101</f>
         <v>0.5</v>
       </c>
       <c r="C401" t="s">

--- a/data/git/file/git.o.xlsx
+++ b/data/git/file/git.o.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/jryans/Research/Papers/oopsla-2023/data/git/file/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8F4EE94F-1886-AC42-99FA-F241CAEFF560}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5E3B8E25-D8A3-F845-B160-26E10E7F6B7A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="16440" yWindow="1920" windowWidth="47060" windowHeight="24880" activeTab="2" xr2:uid="{1069CAA2-7C27-E54E-B88A-C9343E41429C}"/>
+    <workbookView xWindow="16440" yWindow="1920" windowWidth="47060" windowHeight="24880" activeTab="1" xr2:uid="{1069CAA2-7C27-E54E-B88A-C9343E41429C}"/>
   </bookViews>
   <sheets>
     <sheet name="Wide" sheetId="1" r:id="rId1"/>
@@ -658,9 +658,6 @@
     <t>O1-14 Delta</t>
   </si>
   <si>
-    <t xml:space="preserve">CL / SL (O0-13, m2r)    </t>
-  </si>
-  <si>
     <t>CL / SL (O1-12)</t>
   </si>
   <si>
@@ -673,9 +670,6 @@
     <t>CL / SL Delta</t>
   </si>
   <si>
-    <t>CL (O0-13, m2r)</t>
-  </si>
-  <si>
     <t>CL (O1-12)</t>
   </si>
   <si>
@@ -683,24 +677,6 @@
   </si>
   <si>
     <t>CL (O1-14)</t>
-  </si>
-  <si>
-    <t>CL / SL (O0-13)</t>
-  </si>
-  <si>
-    <t>CL (O0-13)</t>
-  </si>
-  <si>
-    <t>Clang 13, O0</t>
-  </si>
-  <si>
-    <t>O0-13 Delta</t>
-  </si>
-  <si>
-    <t>O0-13, m2r Delta</t>
-  </si>
-  <si>
-    <t>Clang 13, O0 + mem2reg</t>
   </si>
   <si>
     <t>Arithmetic Mean (Normalised)</t>
@@ -717,14 +693,45 @@
   <si>
     <t>Clang 14, O2</t>
   </si>
+  <si>
+    <t>CL / SL (O0-14)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CL / SL (O0-14, m2r)    </t>
+  </si>
+  <si>
+    <t>O0-14 Delta</t>
+  </si>
+  <si>
+    <t>O0-14, m2r Delta</t>
+  </si>
+  <si>
+    <t>CL (O0-14)</t>
+  </si>
+  <si>
+    <t>CL (O0-14, m2r)</t>
+  </si>
+  <si>
+    <t>Clang 14, O0</t>
+  </si>
+  <si>
+    <t>Clang 14, O0 + mem2reg</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="10" x14ac:knownFonts="1">
+  <fonts count="11" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="16"/>
       <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
@@ -814,10 +821,11 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -853,59 +861,59 @@
 </file>
 
 <file path=xl/queryTables/queryTable1.xml><?xml version="1.0" encoding="utf-8"?>
-<queryTable xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr16="http://schemas.microsoft.com/office/spreadsheetml/2017/revision16" mc:Ignorable="xr16" name="git.o_6" connectionId="17" xr16:uid="{BF097535-9BC4-8A44-8028-889020E90CD1}" autoFormatId="16" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="1" applyPatternFormats="1" applyAlignmentFormats="0" applyWidthHeightFormats="0"/>
+<queryTable xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr16="http://schemas.microsoft.com/office/spreadsheetml/2017/revision16" mc:Ignorable="xr16" name="git.o_4" connectionId="15" xr16:uid="{12472C14-9457-0C4B-85A7-6B4E9A0A4A3A}" autoFormatId="16" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="1" applyPatternFormats="1" applyAlignmentFormats="0" applyWidthHeightFormats="0"/>
 </file>
 
 <file path=xl/queryTables/queryTable10.xml><?xml version="1.0" encoding="utf-8"?>
-<queryTable xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr16="http://schemas.microsoft.com/office/spreadsheetml/2017/revision16" mc:Ignorable="xr16" name="git.o_3" connectionId="14" xr16:uid="{ED71FF77-6ABC-D749-8E21-C2BBC0C49B38}" autoFormatId="16" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="1" applyPatternFormats="1" applyAlignmentFormats="0" applyWidthHeightFormats="0"/>
+<queryTable xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr16="http://schemas.microsoft.com/office/spreadsheetml/2017/revision16" mc:Ignorable="xr16" name="git.o_2" connectionId="13" xr16:uid="{577EB844-CFFF-874E-B636-A682F7CA9C09}" autoFormatId="16" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="1" applyPatternFormats="1" applyAlignmentFormats="0" applyWidthHeightFormats="0"/>
 </file>
 
 <file path=xl/queryTables/queryTable11.xml><?xml version="1.0" encoding="utf-8"?>
-<queryTable xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr16="http://schemas.microsoft.com/office/spreadsheetml/2017/revision16" mc:Ignorable="xr16" name="git.o_10" connectionId="12" xr16:uid="{6F5AE438-0047-EF40-9065-31B57EBCFEA0}" autoFormatId="16" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="1" applyPatternFormats="1" applyAlignmentFormats="0" applyWidthHeightFormats="0"/>
+<queryTable xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr16="http://schemas.microsoft.com/office/spreadsheetml/2017/revision16" mc:Ignorable="xr16" name="git.o_9" connectionId="20" xr16:uid="{DF99720B-8FB8-1945-B82B-62174EC5794B}" autoFormatId="16" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="1" applyPatternFormats="1" applyAlignmentFormats="0" applyWidthHeightFormats="0"/>
 </file>
 
 <file path=xl/queryTables/queryTable12.xml><?xml version="1.0" encoding="utf-8"?>
-<queryTable xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr16="http://schemas.microsoft.com/office/spreadsheetml/2017/revision16" mc:Ignorable="xr16" name="git.o_9" connectionId="20" xr16:uid="{DF99720B-8FB8-1945-B82B-62174EC5794B}" autoFormatId="16" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="1" applyPatternFormats="1" applyAlignmentFormats="0" applyWidthHeightFormats="0"/>
+<queryTable xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr16="http://schemas.microsoft.com/office/spreadsheetml/2017/revision16" mc:Ignorable="xr16" name="git.o.O013m2r" connectionId="2" xr16:uid="{9CCAF8A0-2B7D-0548-BCF8-D231422B6B5F}" autoFormatId="16" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="1" applyPatternFormats="1" applyAlignmentFormats="0" applyWidthHeightFormats="0"/>
 </file>
 
 <file path=xl/queryTables/queryTable13.xml><?xml version="1.0" encoding="utf-8"?>
+<queryTable xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr16="http://schemas.microsoft.com/office/spreadsheetml/2017/revision16" mc:Ignorable="xr16" name="git.o.O113" connectionId="7" xr16:uid="{7EC8FDAA-8641-7F44-A40C-DFADA06143DC}" autoFormatId="16" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="1" applyPatternFormats="1" applyAlignmentFormats="0" applyWidthHeightFormats="0"/>
+</file>
+
+<file path=xl/queryTables/queryTable14.xml><?xml version="1.0" encoding="utf-8"?>
+<queryTable xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr16="http://schemas.microsoft.com/office/spreadsheetml/2017/revision16" mc:Ignorable="xr16" name="git.o.O114" connectionId="9" xr16:uid="{6DA84D36-F075-D643-87AE-9205D8C2E13B}" autoFormatId="16" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="1" applyPatternFormats="1" applyAlignmentFormats="0" applyWidthHeightFormats="0"/>
+</file>
+
+<file path=xl/queryTables/queryTable15.xml><?xml version="1.0" encoding="utf-8"?>
+<queryTable xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr16="http://schemas.microsoft.com/office/spreadsheetml/2017/revision16" mc:Ignorable="xr16" name="git.o.O013m2r" connectionId="3" xr16:uid="{6BD7D553-8716-684F-A112-947029E7B50E}" autoFormatId="16" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="1" applyPatternFormats="1" applyAlignmentFormats="0" applyWidthHeightFormats="0"/>
+</file>
+
+<file path=xl/queryTables/queryTable16.xml><?xml version="1.0" encoding="utf-8"?>
 <queryTable xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr16="http://schemas.microsoft.com/office/spreadsheetml/2017/revision16" mc:Ignorable="xr16" name="git.o.O112" connectionId="5" xr16:uid="{5C22DE01-5C44-7C4E-9EAF-E54F03689DF7}" autoFormatId="16" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="1" applyPatternFormats="1" applyAlignmentFormats="0" applyWidthHeightFormats="0"/>
 </file>
 
-<file path=xl/queryTables/queryTable14.xml><?xml version="1.0" encoding="utf-8"?>
-<queryTable xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr16="http://schemas.microsoft.com/office/spreadsheetml/2017/revision16" mc:Ignorable="xr16" name="git.o.O113" connectionId="7" xr16:uid="{7EC8FDAA-8641-7F44-A40C-DFADA06143DC}" autoFormatId="16" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="1" applyPatternFormats="1" applyAlignmentFormats="0" applyWidthHeightFormats="0"/>
+<file path=xl/queryTables/queryTable17.xml><?xml version="1.0" encoding="utf-8"?>
+<queryTable xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr16="http://schemas.microsoft.com/office/spreadsheetml/2017/revision16" mc:Ignorable="xr16" name="git.o.O112" connectionId="6" xr16:uid="{72FE5272-0C81-7B49-8C92-9E8FE63CCD65}" autoFormatId="16" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="1" applyPatternFormats="1" applyAlignmentFormats="0" applyWidthHeightFormats="0"/>
 </file>
 
-<file path=xl/queryTables/queryTable15.xml><?xml version="1.0" encoding="utf-8"?>
-<queryTable xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr16="http://schemas.microsoft.com/office/spreadsheetml/2017/revision16" mc:Ignorable="xr16" name="git.o.O114" connectionId="9" xr16:uid="{6DA84D36-F075-D643-87AE-9205D8C2E13B}" autoFormatId="16" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="1" applyPatternFormats="1" applyAlignmentFormats="0" applyWidthHeightFormats="0"/>
+<file path=xl/queryTables/queryTable18.xml><?xml version="1.0" encoding="utf-8"?>
+<queryTable xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr16="http://schemas.microsoft.com/office/spreadsheetml/2017/revision16" mc:Ignorable="xr16" name="git.o.O013m2r" connectionId="4" xr16:uid="{F1095D83-ED7E-9549-9DFC-EB98E00E3997}" autoFormatId="16" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="1" applyPatternFormats="1" applyAlignmentFormats="0" applyWidthHeightFormats="0"/>
 </file>
 
-<file path=xl/queryTables/queryTable16.xml><?xml version="1.0" encoding="utf-8"?>
-<queryTable xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr16="http://schemas.microsoft.com/office/spreadsheetml/2017/revision16" mc:Ignorable="xr16" name="git.o.O013m2r" connectionId="3" xr16:uid="{6BD7D553-8716-684F-A112-947029E7B50E}" autoFormatId="16" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="1" applyPatternFormats="1" applyAlignmentFormats="0" applyWidthHeightFormats="0"/>
+<file path=xl/queryTables/queryTable19.xml><?xml version="1.0" encoding="utf-8"?>
+<queryTable xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr16="http://schemas.microsoft.com/office/spreadsheetml/2017/revision16" mc:Ignorable="xr16" name="git.o.O114" connectionId="10" xr16:uid="{D34FF5A8-62F7-554D-9E92-8F5C8D099217}" autoFormatId="16" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="1" applyPatternFormats="1" applyAlignmentFormats="0" applyWidthHeightFormats="0"/>
 </file>
 
-<file path=xl/queryTables/queryTable17.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/queryTables/queryTable2.xml><?xml version="1.0" encoding="utf-8"?>
+<queryTable xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr16="http://schemas.microsoft.com/office/spreadsheetml/2017/revision16" mc:Ignorable="xr16" name="git.o_5" connectionId="16" xr16:uid="{5AF1A4D8-20C7-B944-973B-C6F106978454}" autoFormatId="16" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="1" applyPatternFormats="1" applyAlignmentFormats="0" applyWidthHeightFormats="0"/>
+</file>
+
+<file path=xl/queryTables/queryTable20.xml><?xml version="1.0" encoding="utf-8"?>
 <queryTable xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr16="http://schemas.microsoft.com/office/spreadsheetml/2017/revision16" mc:Ignorable="xr16" name="git.o.O113" connectionId="8" xr16:uid="{061FB766-530C-7F46-AA03-8A3221BEEC32}" autoFormatId="16" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="1" applyPatternFormats="1" applyAlignmentFormats="0" applyWidthHeightFormats="0"/>
 </file>
 
-<file path=xl/queryTables/queryTable18.xml><?xml version="1.0" encoding="utf-8"?>
-<queryTable xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr16="http://schemas.microsoft.com/office/spreadsheetml/2017/revision16" mc:Ignorable="xr16" name="git.o.O112" connectionId="6" xr16:uid="{72FE5272-0C81-7B49-8C92-9E8FE63CCD65}" autoFormatId="16" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="1" applyPatternFormats="1" applyAlignmentFormats="0" applyWidthHeightFormats="0"/>
-</file>
-
-<file path=xl/queryTables/queryTable19.xml><?xml version="1.0" encoding="utf-8"?>
-<queryTable xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr16="http://schemas.microsoft.com/office/spreadsheetml/2017/revision16" mc:Ignorable="xr16" name="git.o.O013m2r" connectionId="4" xr16:uid="{F1095D83-ED7E-9549-9DFC-EB98E00E3997}" autoFormatId="16" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="1" applyPatternFormats="1" applyAlignmentFormats="0" applyWidthHeightFormats="0"/>
-</file>
-
-<file path=xl/queryTables/queryTable2.xml><?xml version="1.0" encoding="utf-8"?>
-<queryTable xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr16="http://schemas.microsoft.com/office/spreadsheetml/2017/revision16" mc:Ignorable="xr16" name="git.o_2" connectionId="13" xr16:uid="{577EB844-CFFF-874E-B636-A682F7CA9C09}" autoFormatId="16" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="1" applyPatternFormats="1" applyAlignmentFormats="0" applyWidthHeightFormats="0"/>
-</file>
-
-<file path=xl/queryTables/queryTable20.xml><?xml version="1.0" encoding="utf-8"?>
-<queryTable xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr16="http://schemas.microsoft.com/office/spreadsheetml/2017/revision16" mc:Ignorable="xr16" name="git.o.O114" connectionId="10" xr16:uid="{D34FF5A8-62F7-554D-9E92-8F5C8D099217}" autoFormatId="16" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="1" applyPatternFormats="1" applyAlignmentFormats="0" applyWidthHeightFormats="0"/>
-</file>
-
 <file path=xl/queryTables/queryTable3.xml><?xml version="1.0" encoding="utf-8"?>
-<queryTable xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr16="http://schemas.microsoft.com/office/spreadsheetml/2017/revision16" mc:Ignorable="xr16" name="git.o_4" connectionId="15" xr16:uid="{12472C14-9457-0C4B-85A7-6B4E9A0A4A3A}" autoFormatId="16" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="1" applyPatternFormats="1" applyAlignmentFormats="0" applyWidthHeightFormats="0"/>
+<queryTable xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr16="http://schemas.microsoft.com/office/spreadsheetml/2017/revision16" mc:Ignorable="xr16" name="git.o_7" connectionId="18" xr16:uid="{D6E8256A-0710-A34A-80B4-71635A8A7FF9}" autoFormatId="16" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="1" applyPatternFormats="1" applyAlignmentFormats="0" applyWidthHeightFormats="0"/>
 </file>
 
 <file path=xl/queryTables/queryTable4.xml><?xml version="1.0" encoding="utf-8"?>
@@ -913,23 +921,23 @@
 </file>
 
 <file path=xl/queryTables/queryTable5.xml><?xml version="1.0" encoding="utf-8"?>
+<queryTable xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr16="http://schemas.microsoft.com/office/spreadsheetml/2017/revision16" mc:Ignorable="xr16" name="git.o_3" connectionId="14" xr16:uid="{ED71FF77-6ABC-D749-8E21-C2BBC0C49B38}" autoFormatId="16" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="1" applyPatternFormats="1" applyAlignmentFormats="0" applyWidthHeightFormats="0"/>
+</file>
+
+<file path=xl/queryTables/queryTable6.xml><?xml version="1.0" encoding="utf-8"?>
 <queryTable xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr16="http://schemas.microsoft.com/office/spreadsheetml/2017/revision16" mc:Ignorable="xr16" name="git.o_1" connectionId="11" xr16:uid="{3FDFE62B-64A1-F14C-AAB6-88B8E3E9B697}" autoFormatId="16" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="1" applyPatternFormats="1" applyAlignmentFormats="0" applyWidthHeightFormats="0"/>
 </file>
 
-<file path=xl/queryTables/queryTable6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/queryTables/queryTable7.xml><?xml version="1.0" encoding="utf-8"?>
+<queryTable xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr16="http://schemas.microsoft.com/office/spreadsheetml/2017/revision16" mc:Ignorable="xr16" name="git.o_10" connectionId="12" xr16:uid="{6F5AE438-0047-EF40-9065-31B57EBCFEA0}" autoFormatId="16" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="1" applyPatternFormats="1" applyAlignmentFormats="0" applyWidthHeightFormats="0"/>
+</file>
+
+<file path=xl/queryTables/queryTable8.xml><?xml version="1.0" encoding="utf-8"?>
 <queryTable xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr16="http://schemas.microsoft.com/office/spreadsheetml/2017/revision16" mc:Ignorable="xr16" name="git.o_8" connectionId="19" xr16:uid="{6528BD19-FD94-5B40-8D88-624F75163B95}" autoFormatId="16" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="1" applyPatternFormats="1" applyAlignmentFormats="0" applyWidthHeightFormats="0"/>
 </file>
 
-<file path=xl/queryTables/queryTable7.xml><?xml version="1.0" encoding="utf-8"?>
-<queryTable xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr16="http://schemas.microsoft.com/office/spreadsheetml/2017/revision16" mc:Ignorable="xr16" name="git.o.O013m2r" connectionId="2" xr16:uid="{9CCAF8A0-2B7D-0548-BCF8-D231422B6B5F}" autoFormatId="16" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="1" applyPatternFormats="1" applyAlignmentFormats="0" applyWidthHeightFormats="0"/>
-</file>
-
-<file path=xl/queryTables/queryTable8.xml><?xml version="1.0" encoding="utf-8"?>
-<queryTable xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr16="http://schemas.microsoft.com/office/spreadsheetml/2017/revision16" mc:Ignorable="xr16" name="git.o_5" connectionId="16" xr16:uid="{5AF1A4D8-20C7-B944-973B-C6F106978454}" autoFormatId="16" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="1" applyPatternFormats="1" applyAlignmentFormats="0" applyWidthHeightFormats="0"/>
-</file>
-
 <file path=xl/queryTables/queryTable9.xml><?xml version="1.0" encoding="utf-8"?>
-<queryTable xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr16="http://schemas.microsoft.com/office/spreadsheetml/2017/revision16" mc:Ignorable="xr16" name="git.o_7" connectionId="18" xr16:uid="{D6E8256A-0710-A34A-80B4-71635A8A7FF9}" autoFormatId="16" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="1" applyPatternFormats="1" applyAlignmentFormats="0" applyWidthHeightFormats="0"/>
+<queryTable xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr16="http://schemas.microsoft.com/office/spreadsheetml/2017/revision16" mc:Ignorable="xr16" name="git.o_6" connectionId="17" xr16:uid="{BF097535-9BC4-8A44-8028-889020E90CD1}" autoFormatId="16" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="1" applyPatternFormats="1" applyAlignmentFormats="0" applyWidthHeightFormats="0"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1255,31 +1263,31 @@
         <v>0</v>
       </c>
       <c r="B1" s="2" t="s">
+        <v>121</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>122</v>
+      </c>
+      <c r="D1" s="2" t="s">
+        <v>109</v>
+      </c>
+      <c r="E1" s="2" t="s">
+        <v>110</v>
+      </c>
+      <c r="F1" s="2" t="s">
+        <v>111</v>
+      </c>
+      <c r="G1" s="2" t="s">
         <v>118</v>
       </c>
-      <c r="C1" s="2" t="s">
-        <v>109</v>
-      </c>
-      <c r="D1" s="2" t="s">
-        <v>110</v>
-      </c>
-      <c r="E1" s="2" t="s">
-        <v>111</v>
-      </c>
-      <c r="F1" s="2" t="s">
-        <v>112</v>
-      </c>
-      <c r="G1" s="2" t="s">
-        <v>126</v>
-      </c>
       <c r="H1" s="2" t="s">
-        <v>127</v>
+        <v>119</v>
       </c>
       <c r="J1" s="2" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="K1" s="2" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="L1" s="2" t="s">
         <v>106</v>
@@ -1291,19 +1299,19 @@
         <v>108</v>
       </c>
       <c r="P1" s="2" t="s">
-        <v>119</v>
+        <v>125</v>
       </c>
       <c r="Q1" s="2" t="s">
+        <v>126</v>
+      </c>
+      <c r="R1" s="2" t="s">
+        <v>113</v>
+      </c>
+      <c r="S1" s="2" t="s">
         <v>114</v>
       </c>
-      <c r="R1" s="2" t="s">
+      <c r="T1" s="2" t="s">
         <v>115</v>
-      </c>
-      <c r="S1" s="2" t="s">
-        <v>116</v>
-      </c>
-      <c r="T1" s="2" t="s">
-        <v>117</v>
       </c>
     </row>
     <row r="2" spans="1:20" x14ac:dyDescent="0.25">
@@ -7433,15 +7441,15 @@
         <v>102</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>124</v>
+        <v>116</v>
       </c>
       <c r="C1" s="2" t="s">
-        <v>125</v>
+        <v>117</v>
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A2" s="7" t="s">
-        <v>120</v>
+      <c r="A2" s="9" t="s">
+        <v>127</v>
       </c>
       <c r="B2" s="7">
         <f>1+AVERAGE(Wide!J2:J101)</f>
@@ -7457,8 +7465,8 @@
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A3" s="7" t="s">
-        <v>123</v>
+      <c r="A3" s="9" t="s">
+        <v>128</v>
       </c>
       <c r="B3" s="7">
         <f>1+AVERAGE(Wide!K2:K101)</f>
@@ -7525,7 +7533,7 @@
       </c>
     </row>
   </sheetData>
-  <phoneticPr fontId="8" type="noConversion"/>
+  <phoneticPr fontId="9" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -7557,7 +7565,7 @@
     </row>
     <row r="2" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A2" s="5" t="s">
-        <v>120</v>
+        <v>127</v>
       </c>
       <c r="B2" s="3" t="s">
         <v>29</v>
@@ -7569,7 +7577,7 @@
     </row>
     <row r="3" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A3" s="5" t="s">
-        <v>120</v>
+        <v>127</v>
       </c>
       <c r="B3" s="3" t="s">
         <v>83</v>
@@ -7581,7 +7589,7 @@
     </row>
     <row r="4" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A4" s="5" t="s">
-        <v>120</v>
+        <v>127</v>
       </c>
       <c r="B4" s="3" t="s">
         <v>84</v>
@@ -7593,7 +7601,7 @@
     </row>
     <row r="5" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A5" s="5" t="s">
-        <v>120</v>
+        <v>127</v>
       </c>
       <c r="B5" s="3" t="s">
         <v>85</v>
@@ -7605,7 +7613,7 @@
     </row>
     <row r="6" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A6" s="5" t="s">
-        <v>120</v>
+        <v>127</v>
       </c>
       <c r="B6" s="3" t="s">
         <v>86</v>
@@ -7617,7 +7625,7 @@
     </row>
     <row r="7" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A7" s="5" t="s">
-        <v>120</v>
+        <v>127</v>
       </c>
       <c r="B7" s="3" t="s">
         <v>87</v>
@@ -7629,7 +7637,7 @@
     </row>
     <row r="8" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A8" s="5" t="s">
-        <v>120</v>
+        <v>127</v>
       </c>
       <c r="B8" s="3" t="s">
         <v>88</v>
@@ -7641,7 +7649,7 @@
     </row>
     <row r="9" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A9" s="5" t="s">
-        <v>120</v>
+        <v>127</v>
       </c>
       <c r="B9" s="3" t="s">
         <v>25</v>
@@ -7653,7 +7661,7 @@
     </row>
     <row r="10" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A10" s="5" t="s">
-        <v>120</v>
+        <v>127</v>
       </c>
       <c r="B10" s="3" t="s">
         <v>27</v>
@@ -7665,7 +7673,7 @@
     </row>
     <row r="11" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A11" s="5" t="s">
-        <v>120</v>
+        <v>127</v>
       </c>
       <c r="B11" s="3" t="s">
         <v>28</v>
@@ -7677,7 +7685,7 @@
     </row>
     <row r="12" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A12" s="5" t="s">
-        <v>120</v>
+        <v>127</v>
       </c>
       <c r="B12" s="3" t="s">
         <v>26</v>
@@ -7689,7 +7697,7 @@
     </row>
     <row r="13" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A13" s="5" t="s">
-        <v>120</v>
+        <v>127</v>
       </c>
       <c r="B13" s="3" t="s">
         <v>36</v>
@@ -7701,7 +7709,7 @@
     </row>
     <row r="14" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A14" s="5" t="s">
-        <v>120</v>
+        <v>127</v>
       </c>
       <c r="B14" s="3" t="s">
         <v>35</v>
@@ -7713,7 +7721,7 @@
     </row>
     <row r="15" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A15" s="5" t="s">
-        <v>120</v>
+        <v>127</v>
       </c>
       <c r="B15" s="3" t="s">
         <v>5</v>
@@ -7725,7 +7733,7 @@
     </row>
     <row r="16" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A16" s="5" t="s">
-        <v>120</v>
+        <v>127</v>
       </c>
       <c r="B16" s="3" t="s">
         <v>6</v>
@@ -7737,7 +7745,7 @@
     </row>
     <row r="17" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A17" s="5" t="s">
-        <v>120</v>
+        <v>127</v>
       </c>
       <c r="B17" s="3" t="s">
         <v>7</v>
@@ -7749,7 +7757,7 @@
     </row>
     <row r="18" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A18" s="5" t="s">
-        <v>120</v>
+        <v>127</v>
       </c>
       <c r="B18" s="3" t="s">
         <v>31</v>
@@ -7761,7 +7769,7 @@
     </row>
     <row r="19" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A19" s="5" t="s">
-        <v>120</v>
+        <v>127</v>
       </c>
       <c r="B19" s="3" t="s">
         <v>32</v>
@@ -7773,7 +7781,7 @@
     </row>
     <row r="20" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A20" s="5" t="s">
-        <v>120</v>
+        <v>127</v>
       </c>
       <c r="B20" s="3" t="s">
         <v>30</v>
@@ -7785,7 +7793,7 @@
     </row>
     <row r="21" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A21" s="5" t="s">
-        <v>120</v>
+        <v>127</v>
       </c>
       <c r="B21" s="3" t="s">
         <v>100</v>
@@ -7797,7 +7805,7 @@
     </row>
     <row r="22" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A22" s="5" t="s">
-        <v>120</v>
+        <v>127</v>
       </c>
       <c r="B22" s="3" t="s">
         <v>67</v>
@@ -7809,7 +7817,7 @@
     </row>
     <row r="23" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A23" s="5" t="s">
-        <v>120</v>
+        <v>127</v>
       </c>
       <c r="B23" s="3" t="s">
         <v>66</v>
@@ -7821,7 +7829,7 @@
     </row>
     <row r="24" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A24" s="5" t="s">
-        <v>120</v>
+        <v>127</v>
       </c>
       <c r="B24" s="3" t="s">
         <v>78</v>
@@ -7833,7 +7841,7 @@
     </row>
     <row r="25" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A25" s="5" t="s">
-        <v>120</v>
+        <v>127</v>
       </c>
       <c r="B25" s="3" t="s">
         <v>79</v>
@@ -7845,7 +7853,7 @@
     </row>
     <row r="26" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A26" s="5" t="s">
-        <v>120</v>
+        <v>127</v>
       </c>
       <c r="B26" s="3" t="s">
         <v>71</v>
@@ -7857,7 +7865,7 @@
     </row>
     <row r="27" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A27" s="5" t="s">
-        <v>120</v>
+        <v>127</v>
       </c>
       <c r="B27" s="3" t="s">
         <v>72</v>
@@ -7869,7 +7877,7 @@
     </row>
     <row r="28" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A28" s="5" t="s">
-        <v>120</v>
+        <v>127</v>
       </c>
       <c r="B28" s="3" t="s">
         <v>81</v>
@@ -7881,7 +7889,7 @@
     </row>
     <row r="29" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A29" s="5" t="s">
-        <v>120</v>
+        <v>127</v>
       </c>
       <c r="B29" s="3" t="s">
         <v>74</v>
@@ -7893,7 +7901,7 @@
     </row>
     <row r="30" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A30" s="5" t="s">
-        <v>120</v>
+        <v>127</v>
       </c>
       <c r="B30" s="3" t="s">
         <v>73</v>
@@ -7905,7 +7913,7 @@
     </row>
     <row r="31" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A31" s="5" t="s">
-        <v>120</v>
+        <v>127</v>
       </c>
       <c r="B31" s="3" t="s">
         <v>75</v>
@@ -7917,7 +7925,7 @@
     </row>
     <row r="32" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A32" s="5" t="s">
-        <v>120</v>
+        <v>127</v>
       </c>
       <c r="B32" s="3" t="s">
         <v>82</v>
@@ -7929,7 +7937,7 @@
     </row>
     <row r="33" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A33" s="5" t="s">
-        <v>120</v>
+        <v>127</v>
       </c>
       <c r="B33" s="3" t="s">
         <v>80</v>
@@ -7941,7 +7949,7 @@
     </row>
     <row r="34" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A34" s="5" t="s">
-        <v>120</v>
+        <v>127</v>
       </c>
       <c r="B34" s="3" t="s">
         <v>76</v>
@@ -7953,7 +7961,7 @@
     </row>
     <row r="35" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A35" s="5" t="s">
-        <v>120</v>
+        <v>127</v>
       </c>
       <c r="B35" s="3" t="s">
         <v>77</v>
@@ -7965,7 +7973,7 @@
     </row>
     <row r="36" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A36" s="5" t="s">
-        <v>120</v>
+        <v>127</v>
       </c>
       <c r="B36" s="3" t="s">
         <v>15</v>
@@ -7977,7 +7985,7 @@
     </row>
     <row r="37" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A37" s="5" t="s">
-        <v>120</v>
+        <v>127</v>
       </c>
       <c r="B37" s="3" t="s">
         <v>17</v>
@@ -7989,7 +7997,7 @@
     </row>
     <row r="38" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A38" s="5" t="s">
-        <v>120</v>
+        <v>127</v>
       </c>
       <c r="B38" s="3" t="s">
         <v>16</v>
@@ -8001,7 +8009,7 @@
     </row>
     <row r="39" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A39" s="5" t="s">
-        <v>120</v>
+        <v>127</v>
       </c>
       <c r="B39" s="3" t="s">
         <v>19</v>
@@ -8013,7 +8021,7 @@
     </row>
     <row r="40" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A40" s="5" t="s">
-        <v>120</v>
+        <v>127</v>
       </c>
       <c r="B40" s="3" t="s">
         <v>18</v>
@@ -8025,7 +8033,7 @@
     </row>
     <row r="41" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A41" s="5" t="s">
-        <v>120</v>
+        <v>127</v>
       </c>
       <c r="B41" s="3" t="s">
         <v>20</v>
@@ -8037,7 +8045,7 @@
     </row>
     <row r="42" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A42" s="5" t="s">
-        <v>120</v>
+        <v>127</v>
       </c>
       <c r="B42" s="3" t="s">
         <v>90</v>
@@ -8049,7 +8057,7 @@
     </row>
     <row r="43" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A43" s="5" t="s">
-        <v>120</v>
+        <v>127</v>
       </c>
       <c r="B43" s="3" t="s">
         <v>89</v>
@@ -8061,7 +8069,7 @@
     </row>
     <row r="44" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A44" s="5" t="s">
-        <v>120</v>
+        <v>127</v>
       </c>
       <c r="B44" s="3" t="s">
         <v>93</v>
@@ -8073,7 +8081,7 @@
     </row>
     <row r="45" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A45" s="5" t="s">
-        <v>120</v>
+        <v>127</v>
       </c>
       <c r="B45" s="3" t="s">
         <v>94</v>
@@ -8085,7 +8093,7 @@
     </row>
     <row r="46" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A46" s="5" t="s">
-        <v>120</v>
+        <v>127</v>
       </c>
       <c r="B46" s="3" t="s">
         <v>91</v>
@@ -8097,7 +8105,7 @@
     </row>
     <row r="47" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A47" s="5" t="s">
-        <v>120</v>
+        <v>127</v>
       </c>
       <c r="B47" s="3" t="s">
         <v>96</v>
@@ -8109,7 +8117,7 @@
     </row>
     <row r="48" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A48" s="5" t="s">
-        <v>120</v>
+        <v>127</v>
       </c>
       <c r="B48" s="3" t="s">
         <v>95</v>
@@ -8121,7 +8129,7 @@
     </row>
     <row r="49" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A49" s="5" t="s">
-        <v>120</v>
+        <v>127</v>
       </c>
       <c r="B49" s="3" t="s">
         <v>92</v>
@@ -8133,7 +8141,7 @@
     </row>
     <row r="50" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A50" s="5" t="s">
-        <v>120</v>
+        <v>127</v>
       </c>
       <c r="B50" s="3" t="s">
         <v>99</v>
@@ -8145,7 +8153,7 @@
     </row>
     <row r="51" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A51" s="5" t="s">
-        <v>120</v>
+        <v>127</v>
       </c>
       <c r="B51" s="3" t="s">
         <v>64</v>
@@ -8157,7 +8165,7 @@
     </row>
     <row r="52" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A52" s="5" t="s">
-        <v>120</v>
+        <v>127</v>
       </c>
       <c r="B52" s="3" t="s">
         <v>65</v>
@@ -8169,7 +8177,7 @@
     </row>
     <row r="53" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A53" s="5" t="s">
-        <v>120</v>
+        <v>127</v>
       </c>
       <c r="B53" s="3" t="s">
         <v>63</v>
@@ -8181,7 +8189,7 @@
     </row>
     <row r="54" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A54" s="5" t="s">
-        <v>120</v>
+        <v>127</v>
       </c>
       <c r="B54" s="3" t="s">
         <v>11</v>
@@ -8193,7 +8201,7 @@
     </row>
     <row r="55" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A55" s="5" t="s">
-        <v>120</v>
+        <v>127</v>
       </c>
       <c r="B55" s="3" t="s">
         <v>13</v>
@@ -8205,7 +8213,7 @@
     </row>
     <row r="56" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A56" s="5" t="s">
-        <v>120</v>
+        <v>127</v>
       </c>
       <c r="B56" s="3" t="s">
         <v>9</v>
@@ -8217,7 +8225,7 @@
     </row>
     <row r="57" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A57" s="5" t="s">
-        <v>120</v>
+        <v>127</v>
       </c>
       <c r="B57" s="3" t="s">
         <v>10</v>
@@ -8229,7 +8237,7 @@
     </row>
     <row r="58" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A58" s="5" t="s">
-        <v>120</v>
+        <v>127</v>
       </c>
       <c r="B58" s="3" t="s">
         <v>14</v>
@@ -8241,7 +8249,7 @@
     </row>
     <row r="59" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A59" s="5" t="s">
-        <v>120</v>
+        <v>127</v>
       </c>
       <c r="B59" s="3" t="s">
         <v>12</v>
@@ -8253,7 +8261,7 @@
     </row>
     <row r="60" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A60" s="5" t="s">
-        <v>120</v>
+        <v>127</v>
       </c>
       <c r="B60" s="3" t="s">
         <v>8</v>
@@ -8265,7 +8273,7 @@
     </row>
     <row r="61" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A61" s="5" t="s">
-        <v>120</v>
+        <v>127</v>
       </c>
       <c r="B61" s="3" t="s">
         <v>60</v>
@@ -8277,7 +8285,7 @@
     </row>
     <row r="62" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A62" s="5" t="s">
-        <v>120</v>
+        <v>127</v>
       </c>
       <c r="B62" s="3" t="s">
         <v>62</v>
@@ -8289,7 +8297,7 @@
     </row>
     <row r="63" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A63" s="5" t="s">
-        <v>120</v>
+        <v>127</v>
       </c>
       <c r="B63" s="3" t="s">
         <v>61</v>
@@ -8301,7 +8309,7 @@
     </row>
     <row r="64" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A64" s="5" t="s">
-        <v>120</v>
+        <v>127</v>
       </c>
       <c r="B64" s="3" t="s">
         <v>59</v>
@@ -8313,7 +8321,7 @@
     </row>
     <row r="65" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A65" s="5" t="s">
-        <v>120</v>
+        <v>127</v>
       </c>
       <c r="B65" s="3" t="s">
         <v>2</v>
@@ -8325,7 +8333,7 @@
     </row>
     <row r="66" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A66" s="5" t="s">
-        <v>120</v>
+        <v>127</v>
       </c>
       <c r="B66" s="3" t="s">
         <v>1</v>
@@ -8337,7 +8345,7 @@
     </row>
     <row r="67" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A67" s="5" t="s">
-        <v>120</v>
+        <v>127</v>
       </c>
       <c r="B67" s="3" t="s">
         <v>3</v>
@@ -8349,7 +8357,7 @@
     </row>
     <row r="68" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A68" s="5" t="s">
-        <v>120</v>
+        <v>127</v>
       </c>
       <c r="B68" s="3" t="s">
         <v>4</v>
@@ -8361,7 +8369,7 @@
     </row>
     <row r="69" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A69" s="5" t="s">
-        <v>120</v>
+        <v>127</v>
       </c>
       <c r="B69" s="3" t="s">
         <v>21</v>
@@ -8373,7 +8381,7 @@
     </row>
     <row r="70" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A70" s="5" t="s">
-        <v>120</v>
+        <v>127</v>
       </c>
       <c r="B70" s="3" t="s">
         <v>23</v>
@@ -8385,7 +8393,7 @@
     </row>
     <row r="71" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A71" s="5" t="s">
-        <v>120</v>
+        <v>127</v>
       </c>
       <c r="B71" s="3" t="s">
         <v>24</v>
@@ -8397,7 +8405,7 @@
     </row>
     <row r="72" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A72" s="5" t="s">
-        <v>120</v>
+        <v>127</v>
       </c>
       <c r="B72" s="3" t="s">
         <v>22</v>
@@ -8409,7 +8417,7 @@
     </row>
     <row r="73" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A73" s="5" t="s">
-        <v>120</v>
+        <v>127</v>
       </c>
       <c r="B73" s="3" t="s">
         <v>40</v>
@@ -8421,7 +8429,7 @@
     </row>
     <row r="74" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A74" s="5" t="s">
-        <v>120</v>
+        <v>127</v>
       </c>
       <c r="B74" s="3" t="s">
         <v>41</v>
@@ -8433,7 +8441,7 @@
     </row>
     <row r="75" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A75" s="5" t="s">
-        <v>120</v>
+        <v>127</v>
       </c>
       <c r="B75" s="3" t="s">
         <v>45</v>
@@ -8445,7 +8453,7 @@
     </row>
     <row r="76" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A76" s="5" t="s">
-        <v>120</v>
+        <v>127</v>
       </c>
       <c r="B76" s="3" t="s">
         <v>42</v>
@@ -8457,7 +8465,7 @@
     </row>
     <row r="77" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A77" s="5" t="s">
-        <v>120</v>
+        <v>127</v>
       </c>
       <c r="B77" s="3" t="s">
         <v>43</v>
@@ -8469,7 +8477,7 @@
     </row>
     <row r="78" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A78" s="5" t="s">
-        <v>120</v>
+        <v>127</v>
       </c>
       <c r="B78" s="3" t="s">
         <v>46</v>
@@ -8481,7 +8489,7 @@
     </row>
     <row r="79" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A79" s="5" t="s">
-        <v>120</v>
+        <v>127</v>
       </c>
       <c r="B79" s="3" t="s">
         <v>48</v>
@@ -8493,7 +8501,7 @@
     </row>
     <row r="80" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A80" s="5" t="s">
-        <v>120</v>
+        <v>127</v>
       </c>
       <c r="B80" s="3" t="s">
         <v>49</v>
@@ -8505,7 +8513,7 @@
     </row>
     <row r="81" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A81" s="5" t="s">
-        <v>120</v>
+        <v>127</v>
       </c>
       <c r="B81" s="3" t="s">
         <v>47</v>
@@ -8517,7 +8525,7 @@
     </row>
     <row r="82" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A82" s="5" t="s">
-        <v>120</v>
+        <v>127</v>
       </c>
       <c r="B82" s="3" t="s">
         <v>44</v>
@@ -8529,7 +8537,7 @@
     </row>
     <row r="83" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A83" s="5" t="s">
-        <v>120</v>
+        <v>127</v>
       </c>
       <c r="B83" s="3" t="s">
         <v>51</v>
@@ -8541,7 +8549,7 @@
     </row>
     <row r="84" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A84" s="5" t="s">
-        <v>120</v>
+        <v>127</v>
       </c>
       <c r="B84" s="3" t="s">
         <v>52</v>
@@ -8553,7 +8561,7 @@
     </row>
     <row r="85" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A85" s="5" t="s">
-        <v>120</v>
+        <v>127</v>
       </c>
       <c r="B85" s="3" t="s">
         <v>55</v>
@@ -8565,7 +8573,7 @@
     </row>
     <row r="86" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A86" s="5" t="s">
-        <v>120</v>
+        <v>127</v>
       </c>
       <c r="B86" s="3" t="s">
         <v>58</v>
@@ -8577,7 +8585,7 @@
     </row>
     <row r="87" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A87" s="5" t="s">
-        <v>120</v>
+        <v>127</v>
       </c>
       <c r="B87" s="3" t="s">
         <v>50</v>
@@ -8589,7 +8597,7 @@
     </row>
     <row r="88" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A88" s="5" t="s">
-        <v>120</v>
+        <v>127</v>
       </c>
       <c r="B88" s="3" t="s">
         <v>56</v>
@@ -8601,7 +8609,7 @@
     </row>
     <row r="89" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A89" s="5" t="s">
-        <v>120</v>
+        <v>127</v>
       </c>
       <c r="B89" s="3" t="s">
         <v>54</v>
@@ -8613,7 +8621,7 @@
     </row>
     <row r="90" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A90" s="5" t="s">
-        <v>120</v>
+        <v>127</v>
       </c>
       <c r="B90" s="3" t="s">
         <v>53</v>
@@ -8625,7 +8633,7 @@
     </row>
     <row r="91" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A91" s="5" t="s">
-        <v>120</v>
+        <v>127</v>
       </c>
       <c r="B91" s="3" t="s">
         <v>57</v>
@@ -8637,7 +8645,7 @@
     </row>
     <row r="92" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A92" s="5" t="s">
-        <v>120</v>
+        <v>127</v>
       </c>
       <c r="B92" s="3" t="s">
         <v>33</v>
@@ -8649,7 +8657,7 @@
     </row>
     <row r="93" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A93" s="5" t="s">
-        <v>120</v>
+        <v>127</v>
       </c>
       <c r="B93" s="3" t="s">
         <v>34</v>
@@ -8661,7 +8669,7 @@
     </row>
     <row r="94" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A94" s="5" t="s">
-        <v>120</v>
+        <v>127</v>
       </c>
       <c r="B94" s="3" t="s">
         <v>70</v>
@@ -8673,7 +8681,7 @@
     </row>
     <row r="95" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A95" s="5" t="s">
-        <v>120</v>
+        <v>127</v>
       </c>
       <c r="B95" s="3" t="s">
         <v>69</v>
@@ -8685,7 +8693,7 @@
     </row>
     <row r="96" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A96" s="5" t="s">
-        <v>120</v>
+        <v>127</v>
       </c>
       <c r="B96" s="3" t="s">
         <v>68</v>
@@ -8697,7 +8705,7 @@
     </row>
     <row r="97" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A97" s="5" t="s">
-        <v>120</v>
+        <v>127</v>
       </c>
       <c r="B97" s="3" t="s">
         <v>37</v>
@@ -8709,7 +8717,7 @@
     </row>
     <row r="98" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A98" s="5" t="s">
-        <v>120</v>
+        <v>127</v>
       </c>
       <c r="B98" s="3" t="s">
         <v>38</v>
@@ -8721,7 +8729,7 @@
     </row>
     <row r="99" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A99" s="5" t="s">
-        <v>120</v>
+        <v>127</v>
       </c>
       <c r="B99" s="3" t="s">
         <v>98</v>
@@ -8733,7 +8741,7 @@
     </row>
     <row r="100" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A100" s="5" t="s">
-        <v>120</v>
+        <v>127</v>
       </c>
       <c r="B100" s="3" t="s">
         <v>97</v>
@@ -8745,7 +8753,7 @@
     </row>
     <row r="101" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A101" s="5" t="s">
-        <v>120</v>
+        <v>127</v>
       </c>
       <c r="B101" s="3" t="s">
         <v>39</v>
@@ -8757,7 +8765,7 @@
     </row>
     <row r="102" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A102" s="4" t="s">
-        <v>123</v>
+        <v>128</v>
       </c>
       <c r="B102" s="3" t="s">
         <v>29</v>
@@ -8769,7 +8777,7 @@
     </row>
     <row r="103" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A103" s="4" t="s">
-        <v>123</v>
+        <v>128</v>
       </c>
       <c r="B103" s="3" t="s">
         <v>83</v>
@@ -8781,7 +8789,7 @@
     </row>
     <row r="104" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A104" s="4" t="s">
-        <v>123</v>
+        <v>128</v>
       </c>
       <c r="B104" s="3" t="s">
         <v>84</v>
@@ -8793,7 +8801,7 @@
     </row>
     <row r="105" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A105" s="4" t="s">
-        <v>123</v>
+        <v>128</v>
       </c>
       <c r="B105" s="3" t="s">
         <v>85</v>
@@ -8805,7 +8813,7 @@
     </row>
     <row r="106" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A106" s="4" t="s">
-        <v>123</v>
+        <v>128</v>
       </c>
       <c r="B106" s="3" t="s">
         <v>86</v>
@@ -8817,7 +8825,7 @@
     </row>
     <row r="107" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A107" s="4" t="s">
-        <v>123</v>
+        <v>128</v>
       </c>
       <c r="B107" s="3" t="s">
         <v>87</v>
@@ -8829,7 +8837,7 @@
     </row>
     <row r="108" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A108" s="4" t="s">
-        <v>123</v>
+        <v>128</v>
       </c>
       <c r="B108" s="3" t="s">
         <v>88</v>
@@ -8841,7 +8849,7 @@
     </row>
     <row r="109" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A109" s="4" t="s">
-        <v>123</v>
+        <v>128</v>
       </c>
       <c r="B109" s="3" t="s">
         <v>25</v>
@@ -8853,7 +8861,7 @@
     </row>
     <row r="110" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A110" s="4" t="s">
-        <v>123</v>
+        <v>128</v>
       </c>
       <c r="B110" s="3" t="s">
         <v>27</v>
@@ -8865,7 +8873,7 @@
     </row>
     <row r="111" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A111" s="4" t="s">
-        <v>123</v>
+        <v>128</v>
       </c>
       <c r="B111" s="3" t="s">
         <v>28</v>
@@ -8877,7 +8885,7 @@
     </row>
     <row r="112" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A112" s="4" t="s">
-        <v>123</v>
+        <v>128</v>
       </c>
       <c r="B112" s="3" t="s">
         <v>26</v>
@@ -8889,7 +8897,7 @@
     </row>
     <row r="113" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A113" s="4" t="s">
-        <v>123</v>
+        <v>128</v>
       </c>
       <c r="B113" s="3" t="s">
         <v>36</v>
@@ -8901,7 +8909,7 @@
     </row>
     <row r="114" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A114" s="4" t="s">
-        <v>123</v>
+        <v>128</v>
       </c>
       <c r="B114" s="3" t="s">
         <v>35</v>
@@ -8913,7 +8921,7 @@
     </row>
     <row r="115" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A115" s="4" t="s">
-        <v>123</v>
+        <v>128</v>
       </c>
       <c r="B115" s="3" t="s">
         <v>5</v>
@@ -8925,7 +8933,7 @@
     </row>
     <row r="116" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A116" s="4" t="s">
-        <v>123</v>
+        <v>128</v>
       </c>
       <c r="B116" s="3" t="s">
         <v>6</v>
@@ -8937,7 +8945,7 @@
     </row>
     <row r="117" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A117" s="4" t="s">
-        <v>123</v>
+        <v>128</v>
       </c>
       <c r="B117" s="3" t="s">
         <v>7</v>
@@ -8949,7 +8957,7 @@
     </row>
     <row r="118" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A118" s="4" t="s">
-        <v>123</v>
+        <v>128</v>
       </c>
       <c r="B118" s="3" t="s">
         <v>31</v>
@@ -8961,7 +8969,7 @@
     </row>
     <row r="119" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A119" s="4" t="s">
-        <v>123</v>
+        <v>128</v>
       </c>
       <c r="B119" s="3" t="s">
         <v>32</v>
@@ -8973,7 +8981,7 @@
     </row>
     <row r="120" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A120" s="4" t="s">
-        <v>123</v>
+        <v>128</v>
       </c>
       <c r="B120" s="3" t="s">
         <v>30</v>
@@ -8985,7 +8993,7 @@
     </row>
     <row r="121" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A121" s="4" t="s">
-        <v>123</v>
+        <v>128</v>
       </c>
       <c r="B121" s="3" t="s">
         <v>100</v>
@@ -8997,7 +9005,7 @@
     </row>
     <row r="122" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A122" s="4" t="s">
-        <v>123</v>
+        <v>128</v>
       </c>
       <c r="B122" s="3" t="s">
         <v>67</v>
@@ -9009,7 +9017,7 @@
     </row>
     <row r="123" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A123" s="4" t="s">
-        <v>123</v>
+        <v>128</v>
       </c>
       <c r="B123" s="3" t="s">
         <v>66</v>
@@ -9021,7 +9029,7 @@
     </row>
     <row r="124" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A124" s="4" t="s">
-        <v>123</v>
+        <v>128</v>
       </c>
       <c r="B124" s="3" t="s">
         <v>78</v>
@@ -9033,7 +9041,7 @@
     </row>
     <row r="125" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A125" s="4" t="s">
-        <v>123</v>
+        <v>128</v>
       </c>
       <c r="B125" s="3" t="s">
         <v>79</v>
@@ -9045,7 +9053,7 @@
     </row>
     <row r="126" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A126" s="4" t="s">
-        <v>123</v>
+        <v>128</v>
       </c>
       <c r="B126" s="3" t="s">
         <v>71</v>
@@ -9057,7 +9065,7 @@
     </row>
     <row r="127" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A127" s="4" t="s">
-        <v>123</v>
+        <v>128</v>
       </c>
       <c r="B127" s="3" t="s">
         <v>72</v>
@@ -9069,7 +9077,7 @@
     </row>
     <row r="128" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A128" s="4" t="s">
-        <v>123</v>
+        <v>128</v>
       </c>
       <c r="B128" s="3" t="s">
         <v>81</v>
@@ -9081,7 +9089,7 @@
     </row>
     <row r="129" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A129" s="4" t="s">
-        <v>123</v>
+        <v>128</v>
       </c>
       <c r="B129" s="3" t="s">
         <v>74</v>
@@ -9093,7 +9101,7 @@
     </row>
     <row r="130" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A130" s="4" t="s">
-        <v>123</v>
+        <v>128</v>
       </c>
       <c r="B130" s="3" t="s">
         <v>73</v>
@@ -9105,7 +9113,7 @@
     </row>
     <row r="131" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A131" s="4" t="s">
-        <v>123</v>
+        <v>128</v>
       </c>
       <c r="B131" s="3" t="s">
         <v>75</v>
@@ -9117,7 +9125,7 @@
     </row>
     <row r="132" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A132" s="4" t="s">
-        <v>123</v>
+        <v>128</v>
       </c>
       <c r="B132" s="3" t="s">
         <v>82</v>
@@ -9129,7 +9137,7 @@
     </row>
     <row r="133" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A133" s="4" t="s">
-        <v>123</v>
+        <v>128</v>
       </c>
       <c r="B133" s="3" t="s">
         <v>80</v>
@@ -9141,7 +9149,7 @@
     </row>
     <row r="134" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A134" s="4" t="s">
-        <v>123</v>
+        <v>128</v>
       </c>
       <c r="B134" s="3" t="s">
         <v>76</v>
@@ -9153,7 +9161,7 @@
     </row>
     <row r="135" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A135" s="4" t="s">
-        <v>123</v>
+        <v>128</v>
       </c>
       <c r="B135" s="3" t="s">
         <v>77</v>
@@ -9165,7 +9173,7 @@
     </row>
     <row r="136" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A136" s="4" t="s">
-        <v>123</v>
+        <v>128</v>
       </c>
       <c r="B136" s="3" t="s">
         <v>15</v>
@@ -9177,7 +9185,7 @@
     </row>
     <row r="137" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A137" s="4" t="s">
-        <v>123</v>
+        <v>128</v>
       </c>
       <c r="B137" s="3" t="s">
         <v>17</v>
@@ -9189,7 +9197,7 @@
     </row>
     <row r="138" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A138" s="4" t="s">
-        <v>123</v>
+        <v>128</v>
       </c>
       <c r="B138" s="3" t="s">
         <v>16</v>
@@ -9201,7 +9209,7 @@
     </row>
     <row r="139" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A139" s="4" t="s">
-        <v>123</v>
+        <v>128</v>
       </c>
       <c r="B139" s="3" t="s">
         <v>19</v>
@@ -9213,7 +9221,7 @@
     </row>
     <row r="140" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A140" s="4" t="s">
-        <v>123</v>
+        <v>128</v>
       </c>
       <c r="B140" s="3" t="s">
         <v>18</v>
@@ -9225,7 +9233,7 @@
     </row>
     <row r="141" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A141" s="4" t="s">
-        <v>123</v>
+        <v>128</v>
       </c>
       <c r="B141" s="3" t="s">
         <v>20</v>
@@ -9237,7 +9245,7 @@
     </row>
     <row r="142" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A142" s="4" t="s">
-        <v>123</v>
+        <v>128</v>
       </c>
       <c r="B142" s="3" t="s">
         <v>90</v>
@@ -9249,7 +9257,7 @@
     </row>
     <row r="143" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A143" s="4" t="s">
-        <v>123</v>
+        <v>128</v>
       </c>
       <c r="B143" s="3" t="s">
         <v>89</v>
@@ -9261,7 +9269,7 @@
     </row>
     <row r="144" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A144" s="4" t="s">
-        <v>123</v>
+        <v>128</v>
       </c>
       <c r="B144" s="3" t="s">
         <v>93</v>
@@ -9273,7 +9281,7 @@
     </row>
     <row r="145" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A145" s="4" t="s">
-        <v>123</v>
+        <v>128</v>
       </c>
       <c r="B145" s="3" t="s">
         <v>94</v>
@@ -9285,7 +9293,7 @@
     </row>
     <row r="146" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A146" s="4" t="s">
-        <v>123</v>
+        <v>128</v>
       </c>
       <c r="B146" s="3" t="s">
         <v>91</v>
@@ -9297,7 +9305,7 @@
     </row>
     <row r="147" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A147" s="4" t="s">
-        <v>123</v>
+        <v>128</v>
       </c>
       <c r="B147" s="3" t="s">
         <v>96</v>
@@ -9309,7 +9317,7 @@
     </row>
     <row r="148" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A148" s="4" t="s">
-        <v>123</v>
+        <v>128</v>
       </c>
       <c r="B148" s="3" t="s">
         <v>95</v>
@@ -9321,7 +9329,7 @@
     </row>
     <row r="149" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A149" s="4" t="s">
-        <v>123</v>
+        <v>128</v>
       </c>
       <c r="B149" s="3" t="s">
         <v>92</v>
@@ -9333,7 +9341,7 @@
     </row>
     <row r="150" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A150" s="4" t="s">
-        <v>123</v>
+        <v>128</v>
       </c>
       <c r="B150" s="3" t="s">
         <v>99</v>
@@ -9345,7 +9353,7 @@
     </row>
     <row r="151" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A151" s="4" t="s">
-        <v>123</v>
+        <v>128</v>
       </c>
       <c r="B151" s="3" t="s">
         <v>64</v>
@@ -9357,7 +9365,7 @@
     </row>
     <row r="152" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A152" s="4" t="s">
-        <v>123</v>
+        <v>128</v>
       </c>
       <c r="B152" s="3" t="s">
         <v>65</v>
@@ -9369,7 +9377,7 @@
     </row>
     <row r="153" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A153" s="4" t="s">
-        <v>123</v>
+        <v>128</v>
       </c>
       <c r="B153" s="3" t="s">
         <v>63</v>
@@ -9381,7 +9389,7 @@
     </row>
     <row r="154" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A154" s="4" t="s">
-        <v>123</v>
+        <v>128</v>
       </c>
       <c r="B154" s="3" t="s">
         <v>11</v>
@@ -9393,7 +9401,7 @@
     </row>
     <row r="155" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A155" s="4" t="s">
-        <v>123</v>
+        <v>128</v>
       </c>
       <c r="B155" s="3" t="s">
         <v>13</v>
@@ -9405,7 +9413,7 @@
     </row>
     <row r="156" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A156" s="4" t="s">
-        <v>123</v>
+        <v>128</v>
       </c>
       <c r="B156" s="3" t="s">
         <v>9</v>
@@ -9417,7 +9425,7 @@
     </row>
     <row r="157" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A157" s="4" t="s">
-        <v>123</v>
+        <v>128</v>
       </c>
       <c r="B157" s="3" t="s">
         <v>10</v>
@@ -9429,7 +9437,7 @@
     </row>
     <row r="158" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A158" s="4" t="s">
-        <v>123</v>
+        <v>128</v>
       </c>
       <c r="B158" s="3" t="s">
         <v>14</v>
@@ -9441,7 +9449,7 @@
     </row>
     <row r="159" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A159" s="4" t="s">
-        <v>123</v>
+        <v>128</v>
       </c>
       <c r="B159" s="3" t="s">
         <v>12</v>
@@ -9453,7 +9461,7 @@
     </row>
     <row r="160" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A160" s="4" t="s">
-        <v>123</v>
+        <v>128</v>
       </c>
       <c r="B160" s="3" t="s">
         <v>8</v>
@@ -9465,7 +9473,7 @@
     </row>
     <row r="161" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A161" s="4" t="s">
-        <v>123</v>
+        <v>128</v>
       </c>
       <c r="B161" s="3" t="s">
         <v>60</v>
@@ -9477,7 +9485,7 @@
     </row>
     <row r="162" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A162" s="4" t="s">
-        <v>123</v>
+        <v>128</v>
       </c>
       <c r="B162" s="3" t="s">
         <v>62</v>
@@ -9489,7 +9497,7 @@
     </row>
     <row r="163" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A163" s="4" t="s">
-        <v>123</v>
+        <v>128</v>
       </c>
       <c r="B163" s="3" t="s">
         <v>61</v>
@@ -9501,7 +9509,7 @@
     </row>
     <row r="164" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A164" s="4" t="s">
-        <v>123</v>
+        <v>128</v>
       </c>
       <c r="B164" s="3" t="s">
         <v>59</v>
@@ -9513,7 +9521,7 @@
     </row>
     <row r="165" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A165" s="4" t="s">
-        <v>123</v>
+        <v>128</v>
       </c>
       <c r="B165" s="3" t="s">
         <v>2</v>
@@ -9525,7 +9533,7 @@
     </row>
     <row r="166" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A166" s="4" t="s">
-        <v>123</v>
+        <v>128</v>
       </c>
       <c r="B166" s="3" t="s">
         <v>1</v>
@@ -9537,7 +9545,7 @@
     </row>
     <row r="167" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A167" s="4" t="s">
-        <v>123</v>
+        <v>128</v>
       </c>
       <c r="B167" s="3" t="s">
         <v>3</v>
@@ -9549,7 +9557,7 @@
     </row>
     <row r="168" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A168" s="4" t="s">
-        <v>123</v>
+        <v>128</v>
       </c>
       <c r="B168" s="3" t="s">
         <v>4</v>
@@ -9561,7 +9569,7 @@
     </row>
     <row r="169" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A169" s="4" t="s">
-        <v>123</v>
+        <v>128</v>
       </c>
       <c r="B169" s="3" t="s">
         <v>21</v>
@@ -9573,7 +9581,7 @@
     </row>
     <row r="170" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A170" s="4" t="s">
-        <v>123</v>
+        <v>128</v>
       </c>
       <c r="B170" s="3" t="s">
         <v>23</v>
@@ -9585,7 +9593,7 @@
     </row>
     <row r="171" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A171" s="4" t="s">
-        <v>123</v>
+        <v>128</v>
       </c>
       <c r="B171" s="3" t="s">
         <v>24</v>
@@ -9597,7 +9605,7 @@
     </row>
     <row r="172" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A172" s="4" t="s">
-        <v>123</v>
+        <v>128</v>
       </c>
       <c r="B172" s="3" t="s">
         <v>22</v>
@@ -9609,7 +9617,7 @@
     </row>
     <row r="173" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A173" s="4" t="s">
-        <v>123</v>
+        <v>128</v>
       </c>
       <c r="B173" s="3" t="s">
         <v>40</v>
@@ -9621,7 +9629,7 @@
     </row>
     <row r="174" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A174" s="4" t="s">
-        <v>123</v>
+        <v>128</v>
       </c>
       <c r="B174" s="3" t="s">
         <v>41</v>
@@ -9633,7 +9641,7 @@
     </row>
     <row r="175" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A175" s="4" t="s">
-        <v>123</v>
+        <v>128</v>
       </c>
       <c r="B175" s="3" t="s">
         <v>45</v>
@@ -9645,7 +9653,7 @@
     </row>
     <row r="176" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A176" s="4" t="s">
-        <v>123</v>
+        <v>128</v>
       </c>
       <c r="B176" s="3" t="s">
         <v>42</v>
@@ -9657,7 +9665,7 @@
     </row>
     <row r="177" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A177" s="4" t="s">
-        <v>123</v>
+        <v>128</v>
       </c>
       <c r="B177" s="3" t="s">
         <v>43</v>
@@ -9669,7 +9677,7 @@
     </row>
     <row r="178" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A178" s="4" t="s">
-        <v>123</v>
+        <v>128</v>
       </c>
       <c r="B178" s="3" t="s">
         <v>46</v>
@@ -9681,7 +9689,7 @@
     </row>
     <row r="179" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A179" s="4" t="s">
-        <v>123</v>
+        <v>128</v>
       </c>
       <c r="B179" s="3" t="s">
         <v>48</v>
@@ -9693,7 +9701,7 @@
     </row>
     <row r="180" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A180" s="4" t="s">
-        <v>123</v>
+        <v>128</v>
       </c>
       <c r="B180" s="3" t="s">
         <v>49</v>
@@ -9705,7 +9713,7 @@
     </row>
     <row r="181" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A181" s="4" t="s">
-        <v>123</v>
+        <v>128</v>
       </c>
       <c r="B181" s="3" t="s">
         <v>47</v>
@@ -9717,7 +9725,7 @@
     </row>
     <row r="182" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A182" s="4" t="s">
-        <v>123</v>
+        <v>128</v>
       </c>
       <c r="B182" s="3" t="s">
         <v>44</v>
@@ -9729,7 +9737,7 @@
     </row>
     <row r="183" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A183" s="4" t="s">
-        <v>123</v>
+        <v>128</v>
       </c>
       <c r="B183" s="3" t="s">
         <v>51</v>
@@ -9741,7 +9749,7 @@
     </row>
     <row r="184" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A184" s="4" t="s">
-        <v>123</v>
+        <v>128</v>
       </c>
       <c r="B184" s="3" t="s">
         <v>52</v>
@@ -9753,7 +9761,7 @@
     </row>
     <row r="185" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A185" s="4" t="s">
-        <v>123</v>
+        <v>128</v>
       </c>
       <c r="B185" s="3" t="s">
         <v>55</v>
@@ -9765,7 +9773,7 @@
     </row>
     <row r="186" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A186" s="4" t="s">
-        <v>123</v>
+        <v>128</v>
       </c>
       <c r="B186" s="3" t="s">
         <v>58</v>
@@ -9777,7 +9785,7 @@
     </row>
     <row r="187" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A187" s="4" t="s">
-        <v>123</v>
+        <v>128</v>
       </c>
       <c r="B187" s="3" t="s">
         <v>50</v>
@@ -9789,7 +9797,7 @@
     </row>
     <row r="188" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A188" s="4" t="s">
-        <v>123</v>
+        <v>128</v>
       </c>
       <c r="B188" s="3" t="s">
         <v>56</v>
@@ -9801,7 +9809,7 @@
     </row>
     <row r="189" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A189" s="4" t="s">
-        <v>123</v>
+        <v>128</v>
       </c>
       <c r="B189" s="3" t="s">
         <v>54</v>
@@ -9813,7 +9821,7 @@
     </row>
     <row r="190" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A190" s="4" t="s">
-        <v>123</v>
+        <v>128</v>
       </c>
       <c r="B190" s="3" t="s">
         <v>53</v>
@@ -9825,7 +9833,7 @@
     </row>
     <row r="191" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A191" s="4" t="s">
-        <v>123</v>
+        <v>128</v>
       </c>
       <c r="B191" s="3" t="s">
         <v>57</v>
@@ -9837,7 +9845,7 @@
     </row>
     <row r="192" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A192" s="4" t="s">
-        <v>123</v>
+        <v>128</v>
       </c>
       <c r="B192" s="3" t="s">
         <v>33</v>
@@ -9849,7 +9857,7 @@
     </row>
     <row r="193" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A193" s="4" t="s">
-        <v>123</v>
+        <v>128</v>
       </c>
       <c r="B193" s="3" t="s">
         <v>34</v>
@@ -9861,7 +9869,7 @@
     </row>
     <row r="194" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A194" s="4" t="s">
-        <v>123</v>
+        <v>128</v>
       </c>
       <c r="B194" s="3" t="s">
         <v>70</v>
@@ -9873,7 +9881,7 @@
     </row>
     <row r="195" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A195" s="4" t="s">
-        <v>123</v>
+        <v>128</v>
       </c>
       <c r="B195" s="3" t="s">
         <v>69</v>
@@ -9885,7 +9893,7 @@
     </row>
     <row r="196" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A196" s="4" t="s">
-        <v>123</v>
+        <v>128</v>
       </c>
       <c r="B196" s="3" t="s">
         <v>68</v>
@@ -9897,7 +9905,7 @@
     </row>
     <row r="197" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A197" s="4" t="s">
-        <v>123</v>
+        <v>128</v>
       </c>
       <c r="B197" s="3" t="s">
         <v>37</v>
@@ -9909,7 +9917,7 @@
     </row>
     <row r="198" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A198" s="4" t="s">
-        <v>123</v>
+        <v>128</v>
       </c>
       <c r="B198" s="3" t="s">
         <v>38</v>
@@ -9921,7 +9929,7 @@
     </row>
     <row r="199" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A199" s="4" t="s">
-        <v>123</v>
+        <v>128</v>
       </c>
       <c r="B199" s="3" t="s">
         <v>98</v>
@@ -9933,7 +9941,7 @@
     </row>
     <row r="200" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A200" s="4" t="s">
-        <v>123</v>
+        <v>128</v>
       </c>
       <c r="B200" s="3" t="s">
         <v>97</v>
@@ -9945,7 +9953,7 @@
     </row>
     <row r="201" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A201" s="4" t="s">
-        <v>123</v>
+        <v>128</v>
       </c>
       <c r="B201" s="3" t="s">
         <v>39</v>
@@ -13557,7 +13565,7 @@
     </row>
     <row r="502" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A502" s="3" t="s">
-        <v>128</v>
+        <v>120</v>
       </c>
       <c r="B502" s="3" t="s">
         <v>29</v>
@@ -13569,7 +13577,7 @@
     </row>
     <row r="503" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A503" s="3" t="s">
-        <v>128</v>
+        <v>120</v>
       </c>
       <c r="B503" s="3" t="s">
         <v>83</v>
@@ -13581,7 +13589,7 @@
     </row>
     <row r="504" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A504" s="3" t="s">
-        <v>128</v>
+        <v>120</v>
       </c>
       <c r="B504" s="3" t="s">
         <v>84</v>
@@ -13593,7 +13601,7 @@
     </row>
     <row r="505" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A505" s="3" t="s">
-        <v>128</v>
+        <v>120</v>
       </c>
       <c r="B505" s="3" t="s">
         <v>85</v>
@@ -13605,7 +13613,7 @@
     </row>
     <row r="506" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A506" s="3" t="s">
-        <v>128</v>
+        <v>120</v>
       </c>
       <c r="B506" s="3" t="s">
         <v>86</v>
@@ -13617,7 +13625,7 @@
     </row>
     <row r="507" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A507" s="3" t="s">
-        <v>128</v>
+        <v>120</v>
       </c>
       <c r="B507" s="3" t="s">
         <v>87</v>
@@ -13629,7 +13637,7 @@
     </row>
     <row r="508" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A508" s="3" t="s">
-        <v>128</v>
+        <v>120</v>
       </c>
       <c r="B508" s="3" t="s">
         <v>88</v>
@@ -13641,7 +13649,7 @@
     </row>
     <row r="509" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A509" s="3" t="s">
-        <v>128</v>
+        <v>120</v>
       </c>
       <c r="B509" s="3" t="s">
         <v>25</v>
@@ -13653,7 +13661,7 @@
     </row>
     <row r="510" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A510" s="3" t="s">
-        <v>128</v>
+        <v>120</v>
       </c>
       <c r="B510" s="3" t="s">
         <v>27</v>
@@ -13665,7 +13673,7 @@
     </row>
     <row r="511" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A511" s="3" t="s">
-        <v>128</v>
+        <v>120</v>
       </c>
       <c r="B511" s="3" t="s">
         <v>28</v>
@@ -13677,7 +13685,7 @@
     </row>
     <row r="512" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A512" s="3" t="s">
-        <v>128</v>
+        <v>120</v>
       </c>
       <c r="B512" s="3" t="s">
         <v>26</v>
@@ -13689,7 +13697,7 @@
     </row>
     <row r="513" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A513" s="3" t="s">
-        <v>128</v>
+        <v>120</v>
       </c>
       <c r="B513" s="3" t="s">
         <v>36</v>
@@ -13701,7 +13709,7 @@
     </row>
     <row r="514" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A514" s="3" t="s">
-        <v>128</v>
+        <v>120</v>
       </c>
       <c r="B514" s="3" t="s">
         <v>35</v>
@@ -13713,7 +13721,7 @@
     </row>
     <row r="515" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A515" s="3" t="s">
-        <v>128</v>
+        <v>120</v>
       </c>
       <c r="B515" s="3" t="s">
         <v>5</v>
@@ -13725,7 +13733,7 @@
     </row>
     <row r="516" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A516" s="3" t="s">
-        <v>128</v>
+        <v>120</v>
       </c>
       <c r="B516" s="3" t="s">
         <v>6</v>
@@ -13737,7 +13745,7 @@
     </row>
     <row r="517" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A517" s="3" t="s">
-        <v>128</v>
+        <v>120</v>
       </c>
       <c r="B517" s="3" t="s">
         <v>7</v>
@@ -13749,7 +13757,7 @@
     </row>
     <row r="518" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A518" s="3" t="s">
-        <v>128</v>
+        <v>120</v>
       </c>
       <c r="B518" s="3" t="s">
         <v>31</v>
@@ -13761,7 +13769,7 @@
     </row>
     <row r="519" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A519" s="3" t="s">
-        <v>128</v>
+        <v>120</v>
       </c>
       <c r="B519" s="3" t="s">
         <v>32</v>
@@ -13773,7 +13781,7 @@
     </row>
     <row r="520" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A520" s="3" t="s">
-        <v>128</v>
+        <v>120</v>
       </c>
       <c r="B520" s="3" t="s">
         <v>30</v>
@@ -13785,7 +13793,7 @@
     </row>
     <row r="521" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A521" s="3" t="s">
-        <v>128</v>
+        <v>120</v>
       </c>
       <c r="B521" s="3" t="s">
         <v>100</v>
@@ -13797,7 +13805,7 @@
     </row>
     <row r="522" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A522" s="3" t="s">
-        <v>128</v>
+        <v>120</v>
       </c>
       <c r="B522" s="3" t="s">
         <v>67</v>
@@ -13809,7 +13817,7 @@
     </row>
     <row r="523" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A523" s="3" t="s">
-        <v>128</v>
+        <v>120</v>
       </c>
       <c r="B523" s="3" t="s">
         <v>66</v>
@@ -13821,7 +13829,7 @@
     </row>
     <row r="524" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A524" s="3" t="s">
-        <v>128</v>
+        <v>120</v>
       </c>
       <c r="B524" s="3" t="s">
         <v>78</v>
@@ -13833,7 +13841,7 @@
     </row>
     <row r="525" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A525" s="3" t="s">
-        <v>128</v>
+        <v>120</v>
       </c>
       <c r="B525" s="3" t="s">
         <v>79</v>
@@ -13845,7 +13853,7 @@
     </row>
     <row r="526" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A526" s="3" t="s">
-        <v>128</v>
+        <v>120</v>
       </c>
       <c r="B526" s="3" t="s">
         <v>71</v>
@@ -13857,7 +13865,7 @@
     </row>
     <row r="527" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A527" s="3" t="s">
-        <v>128</v>
+        <v>120</v>
       </c>
       <c r="B527" s="3" t="s">
         <v>72</v>
@@ -13869,7 +13877,7 @@
     </row>
     <row r="528" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A528" s="3" t="s">
-        <v>128</v>
+        <v>120</v>
       </c>
       <c r="B528" s="3" t="s">
         <v>81</v>
@@ -13881,7 +13889,7 @@
     </row>
     <row r="529" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A529" s="3" t="s">
-        <v>128</v>
+        <v>120</v>
       </c>
       <c r="B529" s="3" t="s">
         <v>74</v>
@@ -13893,7 +13901,7 @@
     </row>
     <row r="530" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A530" s="3" t="s">
-        <v>128</v>
+        <v>120</v>
       </c>
       <c r="B530" s="3" t="s">
         <v>73</v>
@@ -13905,7 +13913,7 @@
     </row>
     <row r="531" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A531" s="3" t="s">
-        <v>128</v>
+        <v>120</v>
       </c>
       <c r="B531" s="3" t="s">
         <v>75</v>
@@ -13917,7 +13925,7 @@
     </row>
     <row r="532" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A532" s="3" t="s">
-        <v>128</v>
+        <v>120</v>
       </c>
       <c r="B532" s="3" t="s">
         <v>82</v>
@@ -13929,7 +13937,7 @@
     </row>
     <row r="533" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A533" s="3" t="s">
-        <v>128</v>
+        <v>120</v>
       </c>
       <c r="B533" s="3" t="s">
         <v>80</v>
@@ -13941,7 +13949,7 @@
     </row>
     <row r="534" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A534" s="3" t="s">
-        <v>128</v>
+        <v>120</v>
       </c>
       <c r="B534" s="3" t="s">
         <v>76</v>
@@ -13953,7 +13961,7 @@
     </row>
     <row r="535" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A535" s="3" t="s">
-        <v>128</v>
+        <v>120</v>
       </c>
       <c r="B535" s="3" t="s">
         <v>77</v>
@@ -13965,7 +13973,7 @@
     </row>
     <row r="536" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A536" s="3" t="s">
-        <v>128</v>
+        <v>120</v>
       </c>
       <c r="B536" s="3" t="s">
         <v>15</v>
@@ -13977,7 +13985,7 @@
     </row>
     <row r="537" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A537" s="3" t="s">
-        <v>128</v>
+        <v>120</v>
       </c>
       <c r="B537" s="3" t="s">
         <v>17</v>
@@ -13989,7 +13997,7 @@
     </row>
     <row r="538" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A538" s="3" t="s">
-        <v>128</v>
+        <v>120</v>
       </c>
       <c r="B538" s="3" t="s">
         <v>16</v>
@@ -14001,7 +14009,7 @@
     </row>
     <row r="539" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A539" s="3" t="s">
-        <v>128</v>
+        <v>120</v>
       </c>
       <c r="B539" s="3" t="s">
         <v>19</v>
@@ -14013,7 +14021,7 @@
     </row>
     <row r="540" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A540" s="3" t="s">
-        <v>128</v>
+        <v>120</v>
       </c>
       <c r="B540" s="3" t="s">
         <v>18</v>
@@ -14025,7 +14033,7 @@
     </row>
     <row r="541" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A541" s="3" t="s">
-        <v>128</v>
+        <v>120</v>
       </c>
       <c r="B541" s="3" t="s">
         <v>20</v>
@@ -14037,7 +14045,7 @@
     </row>
     <row r="542" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A542" s="3" t="s">
-        <v>128</v>
+        <v>120</v>
       </c>
       <c r="B542" s="3" t="s">
         <v>90</v>
@@ -14049,7 +14057,7 @@
     </row>
     <row r="543" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A543" s="3" t="s">
-        <v>128</v>
+        <v>120</v>
       </c>
       <c r="B543" s="3" t="s">
         <v>89</v>
@@ -14061,7 +14069,7 @@
     </row>
     <row r="544" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A544" s="3" t="s">
-        <v>128</v>
+        <v>120</v>
       </c>
       <c r="B544" s="3" t="s">
         <v>93</v>
@@ -14073,7 +14081,7 @@
     </row>
     <row r="545" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A545" s="3" t="s">
-        <v>128</v>
+        <v>120</v>
       </c>
       <c r="B545" s="3" t="s">
         <v>94</v>
@@ -14085,7 +14093,7 @@
     </row>
     <row r="546" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A546" s="3" t="s">
-        <v>128</v>
+        <v>120</v>
       </c>
       <c r="B546" s="3" t="s">
         <v>91</v>
@@ -14097,7 +14105,7 @@
     </row>
     <row r="547" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A547" s="3" t="s">
-        <v>128</v>
+        <v>120</v>
       </c>
       <c r="B547" s="3" t="s">
         <v>96</v>
@@ -14109,7 +14117,7 @@
     </row>
     <row r="548" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A548" s="3" t="s">
-        <v>128</v>
+        <v>120</v>
       </c>
       <c r="B548" s="3" t="s">
         <v>95</v>
@@ -14121,7 +14129,7 @@
     </row>
     <row r="549" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A549" s="3" t="s">
-        <v>128</v>
+        <v>120</v>
       </c>
       <c r="B549" s="3" t="s">
         <v>92</v>
@@ -14133,7 +14141,7 @@
     </row>
     <row r="550" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A550" s="3" t="s">
-        <v>128</v>
+        <v>120</v>
       </c>
       <c r="B550" s="3" t="s">
         <v>99</v>
@@ -14145,7 +14153,7 @@
     </row>
     <row r="551" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A551" s="3" t="s">
-        <v>128</v>
+        <v>120</v>
       </c>
       <c r="B551" s="3" t="s">
         <v>64</v>
@@ -14157,7 +14165,7 @@
     </row>
     <row r="552" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A552" s="3" t="s">
-        <v>128</v>
+        <v>120</v>
       </c>
       <c r="B552" s="3" t="s">
         <v>65</v>
@@ -14169,7 +14177,7 @@
     </row>
     <row r="553" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A553" s="3" t="s">
-        <v>128</v>
+        <v>120</v>
       </c>
       <c r="B553" s="3" t="s">
         <v>63</v>
@@ -14181,7 +14189,7 @@
     </row>
     <row r="554" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A554" s="3" t="s">
-        <v>128</v>
+        <v>120</v>
       </c>
       <c r="B554" s="3" t="s">
         <v>11</v>
@@ -14193,7 +14201,7 @@
     </row>
     <row r="555" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A555" s="3" t="s">
-        <v>128</v>
+        <v>120</v>
       </c>
       <c r="B555" s="3" t="s">
         <v>13</v>
@@ -14205,7 +14213,7 @@
     </row>
     <row r="556" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A556" s="3" t="s">
-        <v>128</v>
+        <v>120</v>
       </c>
       <c r="B556" s="3" t="s">
         <v>9</v>
@@ -14217,7 +14225,7 @@
     </row>
     <row r="557" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A557" s="3" t="s">
-        <v>128</v>
+        <v>120</v>
       </c>
       <c r="B557" s="3" t="s">
         <v>10</v>
@@ -14229,7 +14237,7 @@
     </row>
     <row r="558" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A558" s="3" t="s">
-        <v>128</v>
+        <v>120</v>
       </c>
       <c r="B558" s="3" t="s">
         <v>14</v>
@@ -14241,7 +14249,7 @@
     </row>
     <row r="559" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A559" s="3" t="s">
-        <v>128</v>
+        <v>120</v>
       </c>
       <c r="B559" s="3" t="s">
         <v>12</v>
@@ -14253,7 +14261,7 @@
     </row>
     <row r="560" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A560" s="3" t="s">
-        <v>128</v>
+        <v>120</v>
       </c>
       <c r="B560" s="3" t="s">
         <v>8</v>
@@ -14265,7 +14273,7 @@
     </row>
     <row r="561" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A561" s="3" t="s">
-        <v>128</v>
+        <v>120</v>
       </c>
       <c r="B561" s="3" t="s">
         <v>60</v>
@@ -14277,7 +14285,7 @@
     </row>
     <row r="562" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A562" s="3" t="s">
-        <v>128</v>
+        <v>120</v>
       </c>
       <c r="B562" s="3" t="s">
         <v>62</v>
@@ -14289,7 +14297,7 @@
     </row>
     <row r="563" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A563" s="3" t="s">
-        <v>128</v>
+        <v>120</v>
       </c>
       <c r="B563" s="3" t="s">
         <v>61</v>
@@ -14301,7 +14309,7 @@
     </row>
     <row r="564" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A564" s="3" t="s">
-        <v>128</v>
+        <v>120</v>
       </c>
       <c r="B564" s="3" t="s">
         <v>59</v>
@@ -14313,7 +14321,7 @@
     </row>
     <row r="565" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A565" s="3" t="s">
-        <v>128</v>
+        <v>120</v>
       </c>
       <c r="B565" s="3" t="s">
         <v>2</v>
@@ -14325,7 +14333,7 @@
     </row>
     <row r="566" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A566" s="3" t="s">
-        <v>128</v>
+        <v>120</v>
       </c>
       <c r="B566" s="3" t="s">
         <v>1</v>
@@ -14337,7 +14345,7 @@
     </row>
     <row r="567" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A567" s="3" t="s">
-        <v>128</v>
+        <v>120</v>
       </c>
       <c r="B567" s="3" t="s">
         <v>3</v>
@@ -14349,7 +14357,7 @@
     </row>
     <row r="568" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A568" s="3" t="s">
-        <v>128</v>
+        <v>120</v>
       </c>
       <c r="B568" s="3" t="s">
         <v>4</v>
@@ -14361,7 +14369,7 @@
     </row>
     <row r="569" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A569" s="3" t="s">
-        <v>128</v>
+        <v>120</v>
       </c>
       <c r="B569" s="3" t="s">
         <v>21</v>
@@ -14373,7 +14381,7 @@
     </row>
     <row r="570" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A570" s="3" t="s">
-        <v>128</v>
+        <v>120</v>
       </c>
       <c r="B570" s="3" t="s">
         <v>23</v>
@@ -14385,7 +14393,7 @@
     </row>
     <row r="571" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A571" s="3" t="s">
-        <v>128</v>
+        <v>120</v>
       </c>
       <c r="B571" s="3" t="s">
         <v>24</v>
@@ -14397,7 +14405,7 @@
     </row>
     <row r="572" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A572" s="3" t="s">
-        <v>128</v>
+        <v>120</v>
       </c>
       <c r="B572" s="3" t="s">
         <v>22</v>
@@ -14409,7 +14417,7 @@
     </row>
     <row r="573" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A573" s="3" t="s">
-        <v>128</v>
+        <v>120</v>
       </c>
       <c r="B573" s="3" t="s">
         <v>40</v>
@@ -14421,7 +14429,7 @@
     </row>
     <row r="574" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A574" s="3" t="s">
-        <v>128</v>
+        <v>120</v>
       </c>
       <c r="B574" s="3" t="s">
         <v>41</v>
@@ -14433,7 +14441,7 @@
     </row>
     <row r="575" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A575" s="3" t="s">
-        <v>128</v>
+        <v>120</v>
       </c>
       <c r="B575" s="3" t="s">
         <v>45</v>
@@ -14445,7 +14453,7 @@
     </row>
     <row r="576" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A576" s="3" t="s">
-        <v>128</v>
+        <v>120</v>
       </c>
       <c r="B576" s="3" t="s">
         <v>42</v>
@@ -14457,7 +14465,7 @@
     </row>
     <row r="577" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A577" s="3" t="s">
-        <v>128</v>
+        <v>120</v>
       </c>
       <c r="B577" s="3" t="s">
         <v>43</v>
@@ -14469,7 +14477,7 @@
     </row>
     <row r="578" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A578" s="3" t="s">
-        <v>128</v>
+        <v>120</v>
       </c>
       <c r="B578" s="3" t="s">
         <v>46</v>
@@ -14481,7 +14489,7 @@
     </row>
     <row r="579" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A579" s="3" t="s">
-        <v>128</v>
+        <v>120</v>
       </c>
       <c r="B579" s="3" t="s">
         <v>48</v>
@@ -14493,7 +14501,7 @@
     </row>
     <row r="580" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A580" s="3" t="s">
-        <v>128</v>
+        <v>120</v>
       </c>
       <c r="B580" s="3" t="s">
         <v>49</v>
@@ -14505,7 +14513,7 @@
     </row>
     <row r="581" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A581" s="3" t="s">
-        <v>128</v>
+        <v>120</v>
       </c>
       <c r="B581" s="3" t="s">
         <v>47</v>
@@ -14517,7 +14525,7 @@
     </row>
     <row r="582" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A582" s="3" t="s">
-        <v>128</v>
+        <v>120</v>
       </c>
       <c r="B582" s="3" t="s">
         <v>44</v>
@@ -14529,7 +14537,7 @@
     </row>
     <row r="583" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A583" s="3" t="s">
-        <v>128</v>
+        <v>120</v>
       </c>
       <c r="B583" s="3" t="s">
         <v>51</v>
@@ -14541,7 +14549,7 @@
     </row>
     <row r="584" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A584" s="3" t="s">
-        <v>128</v>
+        <v>120</v>
       </c>
       <c r="B584" s="3" t="s">
         <v>52</v>
@@ -14553,7 +14561,7 @@
     </row>
     <row r="585" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A585" s="3" t="s">
-        <v>128</v>
+        <v>120</v>
       </c>
       <c r="B585" s="3" t="s">
         <v>55</v>
@@ -14565,7 +14573,7 @@
     </row>
     <row r="586" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A586" s="3" t="s">
-        <v>128</v>
+        <v>120</v>
       </c>
       <c r="B586" s="3" t="s">
         <v>58</v>
@@ -14577,7 +14585,7 @@
     </row>
     <row r="587" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A587" s="3" t="s">
-        <v>128</v>
+        <v>120</v>
       </c>
       <c r="B587" s="3" t="s">
         <v>50</v>
@@ -14589,7 +14597,7 @@
     </row>
     <row r="588" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A588" s="3" t="s">
-        <v>128</v>
+        <v>120</v>
       </c>
       <c r="B588" s="3" t="s">
         <v>56</v>
@@ -14601,7 +14609,7 @@
     </row>
     <row r="589" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A589" s="3" t="s">
-        <v>128</v>
+        <v>120</v>
       </c>
       <c r="B589" s="3" t="s">
         <v>54</v>
@@ -14613,7 +14621,7 @@
     </row>
     <row r="590" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A590" s="3" t="s">
-        <v>128</v>
+        <v>120</v>
       </c>
       <c r="B590" s="3" t="s">
         <v>53</v>
@@ -14625,7 +14633,7 @@
     </row>
     <row r="591" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A591" s="3" t="s">
-        <v>128</v>
+        <v>120</v>
       </c>
       <c r="B591" s="3" t="s">
         <v>57</v>
@@ -14637,7 +14645,7 @@
     </row>
     <row r="592" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A592" s="3" t="s">
-        <v>128</v>
+        <v>120</v>
       </c>
       <c r="B592" s="3" t="s">
         <v>33</v>
@@ -14649,7 +14657,7 @@
     </row>
     <row r="593" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A593" s="3" t="s">
-        <v>128</v>
+        <v>120</v>
       </c>
       <c r="B593" s="3" t="s">
         <v>34</v>
@@ -14661,7 +14669,7 @@
     </row>
     <row r="594" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A594" s="3" t="s">
-        <v>128</v>
+        <v>120</v>
       </c>
       <c r="B594" s="3" t="s">
         <v>70</v>
@@ -14673,7 +14681,7 @@
     </row>
     <row r="595" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A595" s="3" t="s">
-        <v>128</v>
+        <v>120</v>
       </c>
       <c r="B595" s="3" t="s">
         <v>69</v>
@@ -14685,7 +14693,7 @@
     </row>
     <row r="596" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A596" s="3" t="s">
-        <v>128</v>
+        <v>120</v>
       </c>
       <c r="B596" s="3" t="s">
         <v>68</v>
@@ -14697,7 +14705,7 @@
     </row>
     <row r="597" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A597" s="3" t="s">
-        <v>128</v>
+        <v>120</v>
       </c>
       <c r="B597" s="3" t="s">
         <v>37</v>
@@ -14709,7 +14717,7 @@
     </row>
     <row r="598" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A598" s="3" t="s">
-        <v>128</v>
+        <v>120</v>
       </c>
       <c r="B598" s="3" t="s">
         <v>38</v>
@@ -14721,7 +14729,7 @@
     </row>
     <row r="599" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A599" s="3" t="s">
-        <v>128</v>
+        <v>120</v>
       </c>
       <c r="B599" s="3" t="s">
         <v>98</v>
@@ -14733,7 +14741,7 @@
     </row>
     <row r="600" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A600" s="3" t="s">
-        <v>128</v>
+        <v>120</v>
       </c>
       <c r="B600" s="3" t="s">
         <v>97</v>
@@ -14745,7 +14753,7 @@
     </row>
     <row r="601" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A601" s="3" t="s">
-        <v>128</v>
+        <v>120</v>
       </c>
       <c r="B601" s="3" t="s">
         <v>39</v>
@@ -14756,7 +14764,7 @@
       </c>
     </row>
   </sheetData>
-  <phoneticPr fontId="8" type="noConversion"/>
+  <phoneticPr fontId="9" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -14783,12 +14791,12 @@
         <v>0</v>
       </c>
       <c r="C1" s="2" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
     </row>
     <row r="2" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A2" s="5" t="s">
-        <v>120</v>
+        <v>127</v>
       </c>
       <c r="B2" s="1" t="s">
         <v>29</v>
@@ -14800,7 +14808,7 @@
     </row>
     <row r="3" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A3" s="5" t="s">
-        <v>120</v>
+        <v>127</v>
       </c>
       <c r="B3" s="1" t="s">
         <v>83</v>
@@ -14812,7 +14820,7 @@
     </row>
     <row r="4" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A4" s="5" t="s">
-        <v>120</v>
+        <v>127</v>
       </c>
       <c r="B4" s="1" t="s">
         <v>84</v>
@@ -14824,7 +14832,7 @@
     </row>
     <row r="5" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A5" s="5" t="s">
-        <v>120</v>
+        <v>127</v>
       </c>
       <c r="B5" s="1" t="s">
         <v>85</v>
@@ -14836,7 +14844,7 @@
     </row>
     <row r="6" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A6" s="5" t="s">
-        <v>120</v>
+        <v>127</v>
       </c>
       <c r="B6" s="1" t="s">
         <v>86</v>
@@ -14848,7 +14856,7 @@
     </row>
     <row r="7" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A7" s="5" t="s">
-        <v>120</v>
+        <v>127</v>
       </c>
       <c r="B7" s="1" t="s">
         <v>87</v>
@@ -14860,7 +14868,7 @@
     </row>
     <row r="8" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A8" s="5" t="s">
-        <v>120</v>
+        <v>127</v>
       </c>
       <c r="B8" s="1" t="s">
         <v>88</v>
@@ -14872,7 +14880,7 @@
     </row>
     <row r="9" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A9" s="5" t="s">
-        <v>120</v>
+        <v>127</v>
       </c>
       <c r="B9" s="1" t="s">
         <v>25</v>
@@ -14884,7 +14892,7 @@
     </row>
     <row r="10" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A10" s="5" t="s">
-        <v>120</v>
+        <v>127</v>
       </c>
       <c r="B10" s="1" t="s">
         <v>27</v>
@@ -14896,7 +14904,7 @@
     </row>
     <row r="11" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A11" s="5" t="s">
-        <v>120</v>
+        <v>127</v>
       </c>
       <c r="B11" s="1" t="s">
         <v>28</v>
@@ -14908,7 +14916,7 @@
     </row>
     <row r="12" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A12" s="5" t="s">
-        <v>120</v>
+        <v>127</v>
       </c>
       <c r="B12" s="1" t="s">
         <v>26</v>
@@ -14920,7 +14928,7 @@
     </row>
     <row r="13" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A13" s="5" t="s">
-        <v>120</v>
+        <v>127</v>
       </c>
       <c r="B13" s="1" t="s">
         <v>36</v>
@@ -14932,7 +14940,7 @@
     </row>
     <row r="14" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A14" s="5" t="s">
-        <v>120</v>
+        <v>127</v>
       </c>
       <c r="B14" s="1" t="s">
         <v>35</v>
@@ -14944,7 +14952,7 @@
     </row>
     <row r="15" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A15" s="5" t="s">
-        <v>120</v>
+        <v>127</v>
       </c>
       <c r="B15" s="1" t="s">
         <v>5</v>
@@ -14956,7 +14964,7 @@
     </row>
     <row r="16" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A16" s="5" t="s">
-        <v>120</v>
+        <v>127</v>
       </c>
       <c r="B16" s="1" t="s">
         <v>6</v>
@@ -14968,7 +14976,7 @@
     </row>
     <row r="17" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A17" s="5" t="s">
-        <v>120</v>
+        <v>127</v>
       </c>
       <c r="B17" s="1" t="s">
         <v>7</v>
@@ -14980,7 +14988,7 @@
     </row>
     <row r="18" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A18" s="5" t="s">
-        <v>120</v>
+        <v>127</v>
       </c>
       <c r="B18" s="1" t="s">
         <v>31</v>
@@ -14992,7 +15000,7 @@
     </row>
     <row r="19" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A19" s="5" t="s">
-        <v>120</v>
+        <v>127</v>
       </c>
       <c r="B19" s="1" t="s">
         <v>32</v>
@@ -15004,7 +15012,7 @@
     </row>
     <row r="20" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A20" s="5" t="s">
-        <v>120</v>
+        <v>127</v>
       </c>
       <c r="B20" s="1" t="s">
         <v>30</v>
@@ -15016,7 +15024,7 @@
     </row>
     <row r="21" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A21" s="5" t="s">
-        <v>120</v>
+        <v>127</v>
       </c>
       <c r="B21" s="1" t="s">
         <v>100</v>
@@ -15028,7 +15036,7 @@
     </row>
     <row r="22" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A22" s="5" t="s">
-        <v>120</v>
+        <v>127</v>
       </c>
       <c r="B22" s="1" t="s">
         <v>67</v>
@@ -15040,7 +15048,7 @@
     </row>
     <row r="23" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A23" s="5" t="s">
-        <v>120</v>
+        <v>127</v>
       </c>
       <c r="B23" s="1" t="s">
         <v>66</v>
@@ -15052,7 +15060,7 @@
     </row>
     <row r="24" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A24" s="5" t="s">
-        <v>120</v>
+        <v>127</v>
       </c>
       <c r="B24" s="1" t="s">
         <v>78</v>
@@ -15064,7 +15072,7 @@
     </row>
     <row r="25" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A25" s="5" t="s">
-        <v>120</v>
+        <v>127</v>
       </c>
       <c r="B25" s="1" t="s">
         <v>79</v>
@@ -15076,7 +15084,7 @@
     </row>
     <row r="26" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A26" s="5" t="s">
-        <v>120</v>
+        <v>127</v>
       </c>
       <c r="B26" s="1" t="s">
         <v>71</v>
@@ -15088,7 +15096,7 @@
     </row>
     <row r="27" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A27" s="5" t="s">
-        <v>120</v>
+        <v>127</v>
       </c>
       <c r="B27" s="1" t="s">
         <v>72</v>
@@ -15100,7 +15108,7 @@
     </row>
     <row r="28" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A28" s="5" t="s">
-        <v>120</v>
+        <v>127</v>
       </c>
       <c r="B28" s="1" t="s">
         <v>81</v>
@@ -15112,7 +15120,7 @@
     </row>
     <row r="29" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A29" s="5" t="s">
-        <v>120</v>
+        <v>127</v>
       </c>
       <c r="B29" s="1" t="s">
         <v>74</v>
@@ -15124,7 +15132,7 @@
     </row>
     <row r="30" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A30" s="5" t="s">
-        <v>120</v>
+        <v>127</v>
       </c>
       <c r="B30" s="1" t="s">
         <v>73</v>
@@ -15136,7 +15144,7 @@
     </row>
     <row r="31" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A31" s="5" t="s">
-        <v>120</v>
+        <v>127</v>
       </c>
       <c r="B31" s="1" t="s">
         <v>75</v>
@@ -15148,7 +15156,7 @@
     </row>
     <row r="32" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A32" s="5" t="s">
-        <v>120</v>
+        <v>127</v>
       </c>
       <c r="B32" s="1" t="s">
         <v>82</v>
@@ -15160,7 +15168,7 @@
     </row>
     <row r="33" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A33" s="5" t="s">
-        <v>120</v>
+        <v>127</v>
       </c>
       <c r="B33" s="1" t="s">
         <v>80</v>
@@ -15172,7 +15180,7 @@
     </row>
     <row r="34" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A34" s="5" t="s">
-        <v>120</v>
+        <v>127</v>
       </c>
       <c r="B34" s="1" t="s">
         <v>76</v>
@@ -15184,7 +15192,7 @@
     </row>
     <row r="35" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A35" s="5" t="s">
-        <v>120</v>
+        <v>127</v>
       </c>
       <c r="B35" s="1" t="s">
         <v>77</v>
@@ -15196,7 +15204,7 @@
     </row>
     <row r="36" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A36" s="5" t="s">
-        <v>120</v>
+        <v>127</v>
       </c>
       <c r="B36" s="1" t="s">
         <v>15</v>
@@ -15208,7 +15216,7 @@
     </row>
     <row r="37" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A37" s="5" t="s">
-        <v>120</v>
+        <v>127</v>
       </c>
       <c r="B37" s="1" t="s">
         <v>17</v>
@@ -15220,7 +15228,7 @@
     </row>
     <row r="38" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A38" s="5" t="s">
-        <v>120</v>
+        <v>127</v>
       </c>
       <c r="B38" s="1" t="s">
         <v>16</v>
@@ -15232,7 +15240,7 @@
     </row>
     <row r="39" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A39" s="5" t="s">
-        <v>120</v>
+        <v>127</v>
       </c>
       <c r="B39" s="1" t="s">
         <v>19</v>
@@ -15244,7 +15252,7 @@
     </row>
     <row r="40" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A40" s="5" t="s">
-        <v>120</v>
+        <v>127</v>
       </c>
       <c r="B40" s="1" t="s">
         <v>18</v>
@@ -15256,7 +15264,7 @@
     </row>
     <row r="41" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A41" s="5" t="s">
-        <v>120</v>
+        <v>127</v>
       </c>
       <c r="B41" s="1" t="s">
         <v>20</v>
@@ -15268,7 +15276,7 @@
     </row>
     <row r="42" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A42" s="5" t="s">
-        <v>120</v>
+        <v>127</v>
       </c>
       <c r="B42" s="1" t="s">
         <v>90</v>
@@ -15280,7 +15288,7 @@
     </row>
     <row r="43" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A43" s="5" t="s">
-        <v>120</v>
+        <v>127</v>
       </c>
       <c r="B43" s="1" t="s">
         <v>89</v>
@@ -15292,7 +15300,7 @@
     </row>
     <row r="44" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A44" s="5" t="s">
-        <v>120</v>
+        <v>127</v>
       </c>
       <c r="B44" s="1" t="s">
         <v>93</v>
@@ -15304,7 +15312,7 @@
     </row>
     <row r="45" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A45" s="5" t="s">
-        <v>120</v>
+        <v>127</v>
       </c>
       <c r="B45" s="1" t="s">
         <v>94</v>
@@ -15316,7 +15324,7 @@
     </row>
     <row r="46" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A46" s="5" t="s">
-        <v>120</v>
+        <v>127</v>
       </c>
       <c r="B46" s="1" t="s">
         <v>91</v>
@@ -15328,7 +15336,7 @@
     </row>
     <row r="47" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A47" s="5" t="s">
-        <v>120</v>
+        <v>127</v>
       </c>
       <c r="B47" s="1" t="s">
         <v>96</v>
@@ -15340,7 +15348,7 @@
     </row>
     <row r="48" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A48" s="5" t="s">
-        <v>120</v>
+        <v>127</v>
       </c>
       <c r="B48" s="1" t="s">
         <v>95</v>
@@ -15352,7 +15360,7 @@
     </row>
     <row r="49" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A49" s="5" t="s">
-        <v>120</v>
+        <v>127</v>
       </c>
       <c r="B49" s="1" t="s">
         <v>92</v>
@@ -15364,7 +15372,7 @@
     </row>
     <row r="50" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A50" s="5" t="s">
-        <v>120</v>
+        <v>127</v>
       </c>
       <c r="B50" s="1" t="s">
         <v>99</v>
@@ -15376,7 +15384,7 @@
     </row>
     <row r="51" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A51" s="5" t="s">
-        <v>120</v>
+        <v>127</v>
       </c>
       <c r="B51" s="1" t="s">
         <v>64</v>
@@ -15388,7 +15396,7 @@
     </row>
     <row r="52" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A52" s="5" t="s">
-        <v>120</v>
+        <v>127</v>
       </c>
       <c r="B52" s="1" t="s">
         <v>65</v>
@@ -15400,7 +15408,7 @@
     </row>
     <row r="53" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A53" s="5" t="s">
-        <v>120</v>
+        <v>127</v>
       </c>
       <c r="B53" s="1" t="s">
         <v>63</v>
@@ -15412,7 +15420,7 @@
     </row>
     <row r="54" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A54" s="5" t="s">
-        <v>120</v>
+        <v>127</v>
       </c>
       <c r="B54" s="1" t="s">
         <v>11</v>
@@ -15424,7 +15432,7 @@
     </row>
     <row r="55" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A55" s="5" t="s">
-        <v>120</v>
+        <v>127</v>
       </c>
       <c r="B55" s="1" t="s">
         <v>13</v>
@@ -15436,7 +15444,7 @@
     </row>
     <row r="56" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A56" s="5" t="s">
-        <v>120</v>
+        <v>127</v>
       </c>
       <c r="B56" s="1" t="s">
         <v>9</v>
@@ -15448,7 +15456,7 @@
     </row>
     <row r="57" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A57" s="5" t="s">
-        <v>120</v>
+        <v>127</v>
       </c>
       <c r="B57" s="1" t="s">
         <v>10</v>
@@ -15460,7 +15468,7 @@
     </row>
     <row r="58" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A58" s="5" t="s">
-        <v>120</v>
+        <v>127</v>
       </c>
       <c r="B58" s="1" t="s">
         <v>14</v>
@@ -15472,7 +15480,7 @@
     </row>
     <row r="59" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A59" s="5" t="s">
-        <v>120</v>
+        <v>127</v>
       </c>
       <c r="B59" s="1" t="s">
         <v>12</v>
@@ -15484,7 +15492,7 @@
     </row>
     <row r="60" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A60" s="5" t="s">
-        <v>120</v>
+        <v>127</v>
       </c>
       <c r="B60" s="1" t="s">
         <v>8</v>
@@ -15496,7 +15504,7 @@
     </row>
     <row r="61" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A61" s="5" t="s">
-        <v>120</v>
+        <v>127</v>
       </c>
       <c r="B61" s="1" t="s">
         <v>60</v>
@@ -15508,7 +15516,7 @@
     </row>
     <row r="62" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A62" s="5" t="s">
-        <v>120</v>
+        <v>127</v>
       </c>
       <c r="B62" s="1" t="s">
         <v>62</v>
@@ -15520,7 +15528,7 @@
     </row>
     <row r="63" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A63" s="5" t="s">
-        <v>120</v>
+        <v>127</v>
       </c>
       <c r="B63" s="1" t="s">
         <v>61</v>
@@ -15532,7 +15540,7 @@
     </row>
     <row r="64" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A64" s="5" t="s">
-        <v>120</v>
+        <v>127</v>
       </c>
       <c r="B64" s="1" t="s">
         <v>59</v>
@@ -15544,7 +15552,7 @@
     </row>
     <row r="65" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A65" s="5" t="s">
-        <v>120</v>
+        <v>127</v>
       </c>
       <c r="B65" s="1" t="s">
         <v>2</v>
@@ -15556,7 +15564,7 @@
     </row>
     <row r="66" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A66" s="5" t="s">
-        <v>120</v>
+        <v>127</v>
       </c>
       <c r="B66" s="1" t="s">
         <v>1</v>
@@ -15568,7 +15576,7 @@
     </row>
     <row r="67" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A67" s="5" t="s">
-        <v>120</v>
+        <v>127</v>
       </c>
       <c r="B67" s="1" t="s">
         <v>3</v>
@@ -15580,7 +15588,7 @@
     </row>
     <row r="68" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A68" s="5" t="s">
-        <v>120</v>
+        <v>127</v>
       </c>
       <c r="B68" s="1" t="s">
         <v>4</v>
@@ -15592,7 +15600,7 @@
     </row>
     <row r="69" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A69" s="5" t="s">
-        <v>120</v>
+        <v>127</v>
       </c>
       <c r="B69" s="1" t="s">
         <v>21</v>
@@ -15604,7 +15612,7 @@
     </row>
     <row r="70" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A70" s="5" t="s">
-        <v>120</v>
+        <v>127</v>
       </c>
       <c r="B70" s="1" t="s">
         <v>23</v>
@@ -15616,7 +15624,7 @@
     </row>
     <row r="71" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A71" s="5" t="s">
-        <v>120</v>
+        <v>127</v>
       </c>
       <c r="B71" s="1" t="s">
         <v>24</v>
@@ -15628,7 +15636,7 @@
     </row>
     <row r="72" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A72" s="5" t="s">
-        <v>120</v>
+        <v>127</v>
       </c>
       <c r="B72" s="1" t="s">
         <v>22</v>
@@ -15640,7 +15648,7 @@
     </row>
     <row r="73" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A73" s="5" t="s">
-        <v>120</v>
+        <v>127</v>
       </c>
       <c r="B73" s="1" t="s">
         <v>40</v>
@@ -15652,7 +15660,7 @@
     </row>
     <row r="74" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A74" s="5" t="s">
-        <v>120</v>
+        <v>127</v>
       </c>
       <c r="B74" s="1" t="s">
         <v>41</v>
@@ -15664,7 +15672,7 @@
     </row>
     <row r="75" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A75" s="5" t="s">
-        <v>120</v>
+        <v>127</v>
       </c>
       <c r="B75" s="1" t="s">
         <v>45</v>
@@ -15676,7 +15684,7 @@
     </row>
     <row r="76" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A76" s="5" t="s">
-        <v>120</v>
+        <v>127</v>
       </c>
       <c r="B76" s="1" t="s">
         <v>42</v>
@@ -15688,7 +15696,7 @@
     </row>
     <row r="77" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A77" s="5" t="s">
-        <v>120</v>
+        <v>127</v>
       </c>
       <c r="B77" s="1" t="s">
         <v>43</v>
@@ -15700,7 +15708,7 @@
     </row>
     <row r="78" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A78" s="5" t="s">
-        <v>120</v>
+        <v>127</v>
       </c>
       <c r="B78" s="1" t="s">
         <v>46</v>
@@ -15712,7 +15720,7 @@
     </row>
     <row r="79" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A79" s="5" t="s">
-        <v>120</v>
+        <v>127</v>
       </c>
       <c r="B79" s="1" t="s">
         <v>48</v>
@@ -15724,7 +15732,7 @@
     </row>
     <row r="80" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A80" s="5" t="s">
-        <v>120</v>
+        <v>127</v>
       </c>
       <c r="B80" s="1" t="s">
         <v>49</v>
@@ -15736,7 +15744,7 @@
     </row>
     <row r="81" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A81" s="5" t="s">
-        <v>120</v>
+        <v>127</v>
       </c>
       <c r="B81" s="1" t="s">
         <v>47</v>
@@ -15748,7 +15756,7 @@
     </row>
     <row r="82" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A82" s="5" t="s">
-        <v>120</v>
+        <v>127</v>
       </c>
       <c r="B82" s="1" t="s">
         <v>44</v>
@@ -15760,7 +15768,7 @@
     </row>
     <row r="83" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A83" s="5" t="s">
-        <v>120</v>
+        <v>127</v>
       </c>
       <c r="B83" s="1" t="s">
         <v>51</v>
@@ -15772,7 +15780,7 @@
     </row>
     <row r="84" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A84" s="5" t="s">
-        <v>120</v>
+        <v>127</v>
       </c>
       <c r="B84" s="1" t="s">
         <v>52</v>
@@ -15784,7 +15792,7 @@
     </row>
     <row r="85" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A85" s="5" t="s">
-        <v>120</v>
+        <v>127</v>
       </c>
       <c r="B85" s="1" t="s">
         <v>55</v>
@@ -15796,7 +15804,7 @@
     </row>
     <row r="86" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A86" s="5" t="s">
-        <v>120</v>
+        <v>127</v>
       </c>
       <c r="B86" s="1" t="s">
         <v>58</v>
@@ -15808,7 +15816,7 @@
     </row>
     <row r="87" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A87" s="5" t="s">
-        <v>120</v>
+        <v>127</v>
       </c>
       <c r="B87" s="1" t="s">
         <v>50</v>
@@ -15820,7 +15828,7 @@
     </row>
     <row r="88" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A88" s="5" t="s">
-        <v>120</v>
+        <v>127</v>
       </c>
       <c r="B88" s="1" t="s">
         <v>56</v>
@@ -15832,7 +15840,7 @@
     </row>
     <row r="89" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A89" s="5" t="s">
-        <v>120</v>
+        <v>127</v>
       </c>
       <c r="B89" s="1" t="s">
         <v>54</v>
@@ -15844,7 +15852,7 @@
     </row>
     <row r="90" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A90" s="5" t="s">
-        <v>120</v>
+        <v>127</v>
       </c>
       <c r="B90" s="1" t="s">
         <v>53</v>
@@ -15856,7 +15864,7 @@
     </row>
     <row r="91" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A91" s="5" t="s">
-        <v>120</v>
+        <v>127</v>
       </c>
       <c r="B91" s="1" t="s">
         <v>57</v>
@@ -15868,7 +15876,7 @@
     </row>
     <row r="92" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A92" s="5" t="s">
-        <v>120</v>
+        <v>127</v>
       </c>
       <c r="B92" s="1" t="s">
         <v>33</v>
@@ -15880,7 +15888,7 @@
     </row>
     <row r="93" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A93" s="5" t="s">
-        <v>120</v>
+        <v>127</v>
       </c>
       <c r="B93" s="1" t="s">
         <v>34</v>
@@ -15892,7 +15900,7 @@
     </row>
     <row r="94" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A94" s="5" t="s">
-        <v>120</v>
+        <v>127</v>
       </c>
       <c r="B94" s="1" t="s">
         <v>70</v>
@@ -15904,7 +15912,7 @@
     </row>
     <row r="95" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A95" s="5" t="s">
-        <v>120</v>
+        <v>127</v>
       </c>
       <c r="B95" s="1" t="s">
         <v>69</v>
@@ -15916,7 +15924,7 @@
     </row>
     <row r="96" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A96" s="5" t="s">
-        <v>120</v>
+        <v>127</v>
       </c>
       <c r="B96" s="1" t="s">
         <v>68</v>
@@ -15928,7 +15936,7 @@
     </row>
     <row r="97" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A97" s="5" t="s">
-        <v>120</v>
+        <v>127</v>
       </c>
       <c r="B97" s="1" t="s">
         <v>37</v>
@@ -15940,7 +15948,7 @@
     </row>
     <row r="98" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A98" s="5" t="s">
-        <v>120</v>
+        <v>127</v>
       </c>
       <c r="B98" s="1" t="s">
         <v>38</v>
@@ -15952,7 +15960,7 @@
     </row>
     <row r="99" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A99" s="5" t="s">
-        <v>120</v>
+        <v>127</v>
       </c>
       <c r="B99" s="1" t="s">
         <v>98</v>
@@ -15964,7 +15972,7 @@
     </row>
     <row r="100" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A100" s="5" t="s">
-        <v>120</v>
+        <v>127</v>
       </c>
       <c r="B100" s="1" t="s">
         <v>97</v>
@@ -15976,7 +15984,7 @@
     </row>
     <row r="101" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A101" s="5" t="s">
-        <v>120</v>
+        <v>127</v>
       </c>
       <c r="B101" s="1" t="s">
         <v>39</v>
@@ -15988,7 +15996,7 @@
     </row>
     <row r="102" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A102" s="8" t="s">
-        <v>123</v>
+        <v>128</v>
       </c>
       <c r="B102" s="1" t="s">
         <v>29</v>
@@ -16000,7 +16008,7 @@
     </row>
     <row r="103" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A103" s="4" t="s">
-        <v>123</v>
+        <v>128</v>
       </c>
       <c r="B103" s="1" t="s">
         <v>83</v>
@@ -16012,7 +16020,7 @@
     </row>
     <row r="104" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A104" s="4" t="s">
-        <v>123</v>
+        <v>128</v>
       </c>
       <c r="B104" s="1" t="s">
         <v>84</v>
@@ -16024,7 +16032,7 @@
     </row>
     <row r="105" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A105" s="4" t="s">
-        <v>123</v>
+        <v>128</v>
       </c>
       <c r="B105" s="1" t="s">
         <v>85</v>
@@ -16036,7 +16044,7 @@
     </row>
     <row r="106" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A106" s="4" t="s">
-        <v>123</v>
+        <v>128</v>
       </c>
       <c r="B106" s="1" t="s">
         <v>86</v>
@@ -16048,7 +16056,7 @@
     </row>
     <row r="107" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A107" s="4" t="s">
-        <v>123</v>
+        <v>128</v>
       </c>
       <c r="B107" s="1" t="s">
         <v>87</v>
@@ -16060,7 +16068,7 @@
     </row>
     <row r="108" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A108" s="4" t="s">
-        <v>123</v>
+        <v>128</v>
       </c>
       <c r="B108" s="1" t="s">
         <v>88</v>
@@ -16072,7 +16080,7 @@
     </row>
     <row r="109" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A109" s="4" t="s">
-        <v>123</v>
+        <v>128</v>
       </c>
       <c r="B109" s="1" t="s">
         <v>25</v>
@@ -16084,7 +16092,7 @@
     </row>
     <row r="110" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A110" s="4" t="s">
-        <v>123</v>
+        <v>128</v>
       </c>
       <c r="B110" s="1" t="s">
         <v>27</v>
@@ -16096,7 +16104,7 @@
     </row>
     <row r="111" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A111" s="4" t="s">
-        <v>123</v>
+        <v>128</v>
       </c>
       <c r="B111" s="1" t="s">
         <v>28</v>
@@ -16108,7 +16116,7 @@
     </row>
     <row r="112" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A112" s="4" t="s">
-        <v>123</v>
+        <v>128</v>
       </c>
       <c r="B112" s="1" t="s">
         <v>26</v>
@@ -16120,7 +16128,7 @@
     </row>
     <row r="113" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A113" s="4" t="s">
-        <v>123</v>
+        <v>128</v>
       </c>
       <c r="B113" s="1" t="s">
         <v>36</v>
@@ -16132,7 +16140,7 @@
     </row>
     <row r="114" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A114" s="4" t="s">
-        <v>123</v>
+        <v>128</v>
       </c>
       <c r="B114" s="1" t="s">
         <v>35</v>
@@ -16144,7 +16152,7 @@
     </row>
     <row r="115" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A115" s="4" t="s">
-        <v>123</v>
+        <v>128</v>
       </c>
       <c r="B115" s="1" t="s">
         <v>5</v>
@@ -16156,7 +16164,7 @@
     </row>
     <row r="116" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A116" s="4" t="s">
-        <v>123</v>
+        <v>128</v>
       </c>
       <c r="B116" s="1" t="s">
         <v>6</v>
@@ -16168,7 +16176,7 @@
     </row>
     <row r="117" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A117" s="4" t="s">
-        <v>123</v>
+        <v>128</v>
       </c>
       <c r="B117" s="1" t="s">
         <v>7</v>
@@ -16180,7 +16188,7 @@
     </row>
     <row r="118" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A118" s="4" t="s">
-        <v>123</v>
+        <v>128</v>
       </c>
       <c r="B118" s="1" t="s">
         <v>31</v>
@@ -16192,7 +16200,7 @@
     </row>
     <row r="119" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A119" s="4" t="s">
-        <v>123</v>
+        <v>128</v>
       </c>
       <c r="B119" s="1" t="s">
         <v>32</v>
@@ -16204,7 +16212,7 @@
     </row>
     <row r="120" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A120" s="4" t="s">
-        <v>123</v>
+        <v>128</v>
       </c>
       <c r="B120" s="1" t="s">
         <v>30</v>
@@ -16216,7 +16224,7 @@
     </row>
     <row r="121" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A121" s="4" t="s">
-        <v>123</v>
+        <v>128</v>
       </c>
       <c r="B121" s="1" t="s">
         <v>100</v>
@@ -16228,7 +16236,7 @@
     </row>
     <row r="122" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A122" s="4" t="s">
-        <v>123</v>
+        <v>128</v>
       </c>
       <c r="B122" s="1" t="s">
         <v>67</v>
@@ -16240,7 +16248,7 @@
     </row>
     <row r="123" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A123" s="4" t="s">
-        <v>123</v>
+        <v>128</v>
       </c>
       <c r="B123" s="1" t="s">
         <v>66</v>
@@ -16252,7 +16260,7 @@
     </row>
     <row r="124" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A124" s="4" t="s">
-        <v>123</v>
+        <v>128</v>
       </c>
       <c r="B124" s="1" t="s">
         <v>78</v>
@@ -16264,7 +16272,7 @@
     </row>
     <row r="125" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A125" s="4" t="s">
-        <v>123</v>
+        <v>128</v>
       </c>
       <c r="B125" s="1" t="s">
         <v>79</v>
@@ -16276,7 +16284,7 @@
     </row>
     <row r="126" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A126" s="4" t="s">
-        <v>123</v>
+        <v>128</v>
       </c>
       <c r="B126" s="1" t="s">
         <v>71</v>
@@ -16288,7 +16296,7 @@
     </row>
     <row r="127" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A127" s="4" t="s">
-        <v>123</v>
+        <v>128</v>
       </c>
       <c r="B127" s="1" t="s">
         <v>72</v>
@@ -16300,7 +16308,7 @@
     </row>
     <row r="128" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A128" s="4" t="s">
-        <v>123</v>
+        <v>128</v>
       </c>
       <c r="B128" s="1" t="s">
         <v>81</v>
@@ -16312,7 +16320,7 @@
     </row>
     <row r="129" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A129" s="4" t="s">
-        <v>123</v>
+        <v>128</v>
       </c>
       <c r="B129" s="1" t="s">
         <v>74</v>
@@ -16324,7 +16332,7 @@
     </row>
     <row r="130" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A130" s="4" t="s">
-        <v>123</v>
+        <v>128</v>
       </c>
       <c r="B130" s="1" t="s">
         <v>73</v>
@@ -16336,7 +16344,7 @@
     </row>
     <row r="131" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A131" s="4" t="s">
-        <v>123</v>
+        <v>128</v>
       </c>
       <c r="B131" s="1" t="s">
         <v>75</v>
@@ -16348,7 +16356,7 @@
     </row>
     <row r="132" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A132" s="4" t="s">
-        <v>123</v>
+        <v>128</v>
       </c>
       <c r="B132" s="1" t="s">
         <v>82</v>
@@ -16360,7 +16368,7 @@
     </row>
     <row r="133" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A133" s="4" t="s">
-        <v>123</v>
+        <v>128</v>
       </c>
       <c r="B133" s="1" t="s">
         <v>80</v>
@@ -16372,7 +16380,7 @@
     </row>
     <row r="134" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A134" s="4" t="s">
-        <v>123</v>
+        <v>128</v>
       </c>
       <c r="B134" s="1" t="s">
         <v>76</v>
@@ -16384,7 +16392,7 @@
     </row>
     <row r="135" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A135" s="4" t="s">
-        <v>123</v>
+        <v>128</v>
       </c>
       <c r="B135" s="1" t="s">
         <v>77</v>
@@ -16396,7 +16404,7 @@
     </row>
     <row r="136" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A136" s="4" t="s">
-        <v>123</v>
+        <v>128</v>
       </c>
       <c r="B136" s="1" t="s">
         <v>15</v>
@@ -16408,7 +16416,7 @@
     </row>
     <row r="137" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A137" s="4" t="s">
-        <v>123</v>
+        <v>128</v>
       </c>
       <c r="B137" s="1" t="s">
         <v>17</v>
@@ -16420,7 +16428,7 @@
     </row>
     <row r="138" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A138" s="4" t="s">
-        <v>123</v>
+        <v>128</v>
       </c>
       <c r="B138" s="1" t="s">
         <v>16</v>
@@ -16432,7 +16440,7 @@
     </row>
     <row r="139" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A139" s="4" t="s">
-        <v>123</v>
+        <v>128</v>
       </c>
       <c r="B139" s="1" t="s">
         <v>19</v>
@@ -16444,7 +16452,7 @@
     </row>
     <row r="140" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A140" s="4" t="s">
-        <v>123</v>
+        <v>128</v>
       </c>
       <c r="B140" s="1" t="s">
         <v>18</v>
@@ -16456,7 +16464,7 @@
     </row>
     <row r="141" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A141" s="4" t="s">
-        <v>123</v>
+        <v>128</v>
       </c>
       <c r="B141" s="1" t="s">
         <v>20</v>
@@ -16468,7 +16476,7 @@
     </row>
     <row r="142" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A142" s="4" t="s">
-        <v>123</v>
+        <v>128</v>
       </c>
       <c r="B142" s="1" t="s">
         <v>90</v>
@@ -16480,7 +16488,7 @@
     </row>
     <row r="143" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A143" s="4" t="s">
-        <v>123</v>
+        <v>128</v>
       </c>
       <c r="B143" s="1" t="s">
         <v>89</v>
@@ -16492,7 +16500,7 @@
     </row>
     <row r="144" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A144" s="4" t="s">
-        <v>123</v>
+        <v>128</v>
       </c>
       <c r="B144" s="1" t="s">
         <v>93</v>
@@ -16504,7 +16512,7 @@
     </row>
     <row r="145" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A145" s="4" t="s">
-        <v>123</v>
+        <v>128</v>
       </c>
       <c r="B145" s="1" t="s">
         <v>94</v>
@@ -16516,7 +16524,7 @@
     </row>
     <row r="146" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A146" s="4" t="s">
-        <v>123</v>
+        <v>128</v>
       </c>
       <c r="B146" s="1" t="s">
         <v>91</v>
@@ -16528,7 +16536,7 @@
     </row>
     <row r="147" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A147" s="4" t="s">
-        <v>123</v>
+        <v>128</v>
       </c>
       <c r="B147" s="1" t="s">
         <v>96</v>
@@ -16540,7 +16548,7 @@
     </row>
     <row r="148" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A148" s="4" t="s">
-        <v>123</v>
+        <v>128</v>
       </c>
       <c r="B148" s="1" t="s">
         <v>95</v>
@@ -16552,7 +16560,7 @@
     </row>
     <row r="149" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A149" s="4" t="s">
-        <v>123</v>
+        <v>128</v>
       </c>
       <c r="B149" s="1" t="s">
         <v>92</v>
@@ -16564,7 +16572,7 @@
     </row>
     <row r="150" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A150" s="4" t="s">
-        <v>123</v>
+        <v>128</v>
       </c>
       <c r="B150" s="1" t="s">
         <v>99</v>
@@ -16576,7 +16584,7 @@
     </row>
     <row r="151" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A151" s="4" t="s">
-        <v>123</v>
+        <v>128</v>
       </c>
       <c r="B151" s="1" t="s">
         <v>64</v>
@@ -16588,7 +16596,7 @@
     </row>
     <row r="152" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A152" s="4" t="s">
-        <v>123</v>
+        <v>128</v>
       </c>
       <c r="B152" s="1" t="s">
         <v>65</v>
@@ -16600,7 +16608,7 @@
     </row>
     <row r="153" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A153" s="4" t="s">
-        <v>123</v>
+        <v>128</v>
       </c>
       <c r="B153" s="1" t="s">
         <v>63</v>
@@ -16612,7 +16620,7 @@
     </row>
     <row r="154" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A154" s="4" t="s">
-        <v>123</v>
+        <v>128</v>
       </c>
       <c r="B154" s="1" t="s">
         <v>11</v>
@@ -16624,7 +16632,7 @@
     </row>
     <row r="155" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A155" s="4" t="s">
-        <v>123</v>
+        <v>128</v>
       </c>
       <c r="B155" s="1" t="s">
         <v>13</v>
@@ -16636,7 +16644,7 @@
     </row>
     <row r="156" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A156" s="4" t="s">
-        <v>123</v>
+        <v>128</v>
       </c>
       <c r="B156" s="1" t="s">
         <v>9</v>
@@ -16648,7 +16656,7 @@
     </row>
     <row r="157" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A157" s="4" t="s">
-        <v>123</v>
+        <v>128</v>
       </c>
       <c r="B157" s="1" t="s">
         <v>10</v>
@@ -16660,7 +16668,7 @@
     </row>
     <row r="158" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A158" s="4" t="s">
-        <v>123</v>
+        <v>128</v>
       </c>
       <c r="B158" s="1" t="s">
         <v>14</v>
@@ -16672,7 +16680,7 @@
     </row>
     <row r="159" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A159" s="4" t="s">
-        <v>123</v>
+        <v>128</v>
       </c>
       <c r="B159" s="1" t="s">
         <v>12</v>
@@ -16684,7 +16692,7 @@
     </row>
     <row r="160" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A160" s="4" t="s">
-        <v>123</v>
+        <v>128</v>
       </c>
       <c r="B160" s="1" t="s">
         <v>8</v>
@@ -16696,7 +16704,7 @@
     </row>
     <row r="161" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A161" s="4" t="s">
-        <v>123</v>
+        <v>128</v>
       </c>
       <c r="B161" s="1" t="s">
         <v>60</v>
@@ -16708,7 +16716,7 @@
     </row>
     <row r="162" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A162" s="4" t="s">
-        <v>123</v>
+        <v>128</v>
       </c>
       <c r="B162" s="1" t="s">
         <v>62</v>
@@ -16720,7 +16728,7 @@
     </row>
     <row r="163" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A163" s="4" t="s">
-        <v>123</v>
+        <v>128</v>
       </c>
       <c r="B163" s="1" t="s">
         <v>61</v>
@@ -16732,7 +16740,7 @@
     </row>
     <row r="164" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A164" s="4" t="s">
-        <v>123</v>
+        <v>128</v>
       </c>
       <c r="B164" s="1" t="s">
         <v>59</v>
@@ -16744,7 +16752,7 @@
     </row>
     <row r="165" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A165" s="4" t="s">
-        <v>123</v>
+        <v>128</v>
       </c>
       <c r="B165" s="1" t="s">
         <v>2</v>
@@ -16756,7 +16764,7 @@
     </row>
     <row r="166" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A166" s="4" t="s">
-        <v>123</v>
+        <v>128</v>
       </c>
       <c r="B166" s="1" t="s">
         <v>1</v>
@@ -16768,7 +16776,7 @@
     </row>
     <row r="167" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A167" s="4" t="s">
-        <v>123</v>
+        <v>128</v>
       </c>
       <c r="B167" s="1" t="s">
         <v>3</v>
@@ -16780,7 +16788,7 @@
     </row>
     <row r="168" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A168" s="4" t="s">
-        <v>123</v>
+        <v>128</v>
       </c>
       <c r="B168" s="1" t="s">
         <v>4</v>
@@ -16792,7 +16800,7 @@
     </row>
     <row r="169" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A169" s="4" t="s">
-        <v>123</v>
+        <v>128</v>
       </c>
       <c r="B169" s="1" t="s">
         <v>21</v>
@@ -16804,7 +16812,7 @@
     </row>
     <row r="170" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A170" s="4" t="s">
-        <v>123</v>
+        <v>128</v>
       </c>
       <c r="B170" s="1" t="s">
         <v>23</v>
@@ -16816,7 +16824,7 @@
     </row>
     <row r="171" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A171" s="4" t="s">
-        <v>123</v>
+        <v>128</v>
       </c>
       <c r="B171" s="1" t="s">
         <v>24</v>
@@ -16828,7 +16836,7 @@
     </row>
     <row r="172" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A172" s="4" t="s">
-        <v>123</v>
+        <v>128</v>
       </c>
       <c r="B172" s="1" t="s">
         <v>22</v>
@@ -16840,7 +16848,7 @@
     </row>
     <row r="173" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A173" s="4" t="s">
-        <v>123</v>
+        <v>128</v>
       </c>
       <c r="B173" s="1" t="s">
         <v>40</v>
@@ -16852,7 +16860,7 @@
     </row>
     <row r="174" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A174" s="4" t="s">
-        <v>123</v>
+        <v>128</v>
       </c>
       <c r="B174" s="1" t="s">
         <v>41</v>
@@ -16864,7 +16872,7 @@
     </row>
     <row r="175" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A175" s="4" t="s">
-        <v>123</v>
+        <v>128</v>
       </c>
       <c r="B175" s="1" t="s">
         <v>45</v>
@@ -16876,7 +16884,7 @@
     </row>
     <row r="176" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A176" s="4" t="s">
-        <v>123</v>
+        <v>128</v>
       </c>
       <c r="B176" s="1" t="s">
         <v>42</v>
@@ -16888,7 +16896,7 @@
     </row>
     <row r="177" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A177" s="4" t="s">
-        <v>123</v>
+        <v>128</v>
       </c>
       <c r="B177" s="1" t="s">
         <v>43</v>
@@ -16900,7 +16908,7 @@
     </row>
     <row r="178" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A178" s="4" t="s">
-        <v>123</v>
+        <v>128</v>
       </c>
       <c r="B178" s="1" t="s">
         <v>46</v>
@@ -16912,7 +16920,7 @@
     </row>
     <row r="179" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A179" s="4" t="s">
-        <v>123</v>
+        <v>128</v>
       </c>
       <c r="B179" s="1" t="s">
         <v>48</v>
@@ -16924,7 +16932,7 @@
     </row>
     <row r="180" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A180" s="4" t="s">
-        <v>123</v>
+        <v>128</v>
       </c>
       <c r="B180" s="1" t="s">
         <v>49</v>
@@ -16936,7 +16944,7 @@
     </row>
     <row r="181" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A181" s="4" t="s">
-        <v>123</v>
+        <v>128</v>
       </c>
       <c r="B181" s="1" t="s">
         <v>47</v>
@@ -16948,7 +16956,7 @@
     </row>
     <row r="182" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A182" s="4" t="s">
-        <v>123</v>
+        <v>128</v>
       </c>
       <c r="B182" s="1" t="s">
         <v>44</v>
@@ -16960,7 +16968,7 @@
     </row>
     <row r="183" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A183" s="4" t="s">
-        <v>123</v>
+        <v>128</v>
       </c>
       <c r="B183" s="1" t="s">
         <v>51</v>
@@ -16972,7 +16980,7 @@
     </row>
     <row r="184" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A184" s="4" t="s">
-        <v>123</v>
+        <v>128</v>
       </c>
       <c r="B184" s="1" t="s">
         <v>52</v>
@@ -16984,7 +16992,7 @@
     </row>
     <row r="185" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A185" s="4" t="s">
-        <v>123</v>
+        <v>128</v>
       </c>
       <c r="B185" s="1" t="s">
         <v>55</v>
@@ -16996,7 +17004,7 @@
     </row>
     <row r="186" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A186" s="4" t="s">
-        <v>123</v>
+        <v>128</v>
       </c>
       <c r="B186" s="1" t="s">
         <v>58</v>
@@ -17008,7 +17016,7 @@
     </row>
     <row r="187" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A187" s="4" t="s">
-        <v>123</v>
+        <v>128</v>
       </c>
       <c r="B187" s="1" t="s">
         <v>50</v>
@@ -17020,7 +17028,7 @@
     </row>
     <row r="188" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A188" s="4" t="s">
-        <v>123</v>
+        <v>128</v>
       </c>
       <c r="B188" s="1" t="s">
         <v>56</v>
@@ -17032,7 +17040,7 @@
     </row>
     <row r="189" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A189" s="4" t="s">
-        <v>123</v>
+        <v>128</v>
       </c>
       <c r="B189" s="1" t="s">
         <v>54</v>
@@ -17044,7 +17052,7 @@
     </row>
     <row r="190" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A190" s="4" t="s">
-        <v>123</v>
+        <v>128</v>
       </c>
       <c r="B190" s="1" t="s">
         <v>53</v>
@@ -17056,7 +17064,7 @@
     </row>
     <row r="191" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A191" s="4" t="s">
-        <v>123</v>
+        <v>128</v>
       </c>
       <c r="B191" s="1" t="s">
         <v>57</v>
@@ -17068,7 +17076,7 @@
     </row>
     <row r="192" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A192" s="4" t="s">
-        <v>123</v>
+        <v>128</v>
       </c>
       <c r="B192" s="1" t="s">
         <v>33</v>
@@ -17080,7 +17088,7 @@
     </row>
     <row r="193" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A193" s="4" t="s">
-        <v>123</v>
+        <v>128</v>
       </c>
       <c r="B193" s="1" t="s">
         <v>34</v>
@@ -17092,7 +17100,7 @@
     </row>
     <row r="194" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A194" s="4" t="s">
-        <v>123</v>
+        <v>128</v>
       </c>
       <c r="B194" s="1" t="s">
         <v>70</v>
@@ -17104,7 +17112,7 @@
     </row>
     <row r="195" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A195" s="4" t="s">
-        <v>123</v>
+        <v>128</v>
       </c>
       <c r="B195" s="1" t="s">
         <v>69</v>
@@ -17116,7 +17124,7 @@
     </row>
     <row r="196" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A196" s="4" t="s">
-        <v>123</v>
+        <v>128</v>
       </c>
       <c r="B196" s="1" t="s">
         <v>68</v>
@@ -17128,7 +17136,7 @@
     </row>
     <row r="197" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A197" s="4" t="s">
-        <v>123</v>
+        <v>128</v>
       </c>
       <c r="B197" s="1" t="s">
         <v>37</v>
@@ -17140,7 +17148,7 @@
     </row>
     <row r="198" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A198" s="4" t="s">
-        <v>123</v>
+        <v>128</v>
       </c>
       <c r="B198" s="1" t="s">
         <v>38</v>
@@ -17152,7 +17160,7 @@
     </row>
     <row r="199" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A199" s="4" t="s">
-        <v>123</v>
+        <v>128</v>
       </c>
       <c r="B199" s="1" t="s">
         <v>98</v>
@@ -17164,7 +17172,7 @@
     </row>
     <row r="200" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A200" s="4" t="s">
-        <v>123</v>
+        <v>128</v>
       </c>
       <c r="B200" s="1" t="s">
         <v>97</v>
@@ -17176,7 +17184,7 @@
     </row>
     <row r="201" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A201" s="4" t="s">
-        <v>123</v>
+        <v>128</v>
       </c>
       <c r="B201" s="1" t="s">
         <v>39</v>
